--- a/tools/myCustomBlockly/製作積木教學/iMi/完整ino程式依積木分割/ESP32Car/ESP32Car3產生積木程式碼.xlsx
+++ b/tools/myCustomBlockly/製作積木教學/iMi/完整ino程式依積木分割/ESP32Car/ESP32Car3產生積木程式碼.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\maker\ArduinoMaster\tools\myCustomBlockly\製作積木教學\iMi\完整ino程式依積木分割\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\Maker\ArduinoSample\tools\myCustomBlockly\製作積木教學\iMi\完整ino程式依積木分割\ESP32Car\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{892235E5-A978-46D3-9DEE-7CC4A445A6BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" tabRatio="737" firstSheet="11" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" tabRatio="737" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="變數" sheetId="5" r:id="rId1"/>
@@ -52,7 +51,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">SETUP!$A$2:$K$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'SETUP(1次會變動)'!$A$2:$G$3</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -71,12 +70,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>AMANI</author>
   </authors>
   <commentList>
-    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="H2" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -96,12 +95,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>AMANI</author>
   </authors>
   <commentList>
-    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
+    <comment ref="E2" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -121,12 +120,12 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>user</author>
   </authors>
   <commentList>
-    <comment ref="H4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
+    <comment ref="H4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -146,12 +145,12 @@
 </file>
 
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>AMANI</author>
   </authors>
   <commentList>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
+    <comment ref="A2" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -171,12 +170,12 @@
 </file>
 
 <file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>AMANI</author>
   </authors>
   <commentList>
-    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000001000000}">
+    <comment ref="D2" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -196,7 +195,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="252">
   <si>
     <t>DEFINITION區 連N拉N</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -453,9 +452,6 @@
   </si>
   <si>
     <t>PubSubClient client(espClient);</t>
-  </si>
-  <si>
-    <t>// HiveMQ Cloud Let's Encrypt CA certificate</t>
   </si>
   <si>
     <t>static const char* root_ca PROGMEM = R"EOF(</t>
@@ -2976,12 +2972,20 @@
       <t>'</t>
     </r>
   </si>
+  <si>
+    <t>// HiveMQ Cloud</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刪除最後面+號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="30">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="31">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3187,6 +3191,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="20"/>
+      <color rgb="FFFF0000"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -3284,7 +3296,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3420,6 +3432,9 @@
     <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -3466,8 +3481,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9877425" y="1447800"/>
-          <a:ext cx="2342515" cy="421640"/>
+          <a:off x="8888730" y="1424940"/>
+          <a:ext cx="2140585" cy="414020"/>
           <a:chOff x="0" y="0"/>
           <a:chExt cx="1860550" cy="421640"/>
         </a:xfrm>
@@ -5941,8 +5956,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="12102353" y="414617"/>
-          <a:ext cx="1536700" cy="263525"/>
+          <a:off x="10880912" y="407893"/>
+          <a:ext cx="1388783" cy="250079"/>
           <a:chOff x="0" y="0"/>
           <a:chExt cx="1536700" cy="263525"/>
         </a:xfrm>
@@ -6633,8 +6648,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="11934265" y="1064559"/>
-          <a:ext cx="1836420" cy="263525"/>
+          <a:off x="10712824" y="1030941"/>
+          <a:ext cx="1688503" cy="256801"/>
           <a:chOff x="0" y="0"/>
           <a:chExt cx="1837045" cy="263525"/>
         </a:xfrm>
@@ -7391,8 +7406,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="11934265" y="1916206"/>
-          <a:ext cx="873125" cy="263525"/>
+          <a:off x="10712824" y="1855694"/>
+          <a:ext cx="799166" cy="256801"/>
           <a:chOff x="0" y="0"/>
           <a:chExt cx="873404" cy="263525"/>
         </a:xfrm>
@@ -7976,8 +7991,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="11934265" y="2554941"/>
-          <a:ext cx="2760345" cy="263525"/>
+          <a:off x="10712824" y="2474259"/>
+          <a:ext cx="2464510" cy="256801"/>
           <a:chOff x="0" y="0"/>
           <a:chExt cx="2760790" cy="263525"/>
         </a:xfrm>
@@ -10758,8 +10773,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1622611" y="2317378"/>
-          <a:ext cx="2109694" cy="276971"/>
+          <a:off x="1622611" y="2250142"/>
+          <a:ext cx="1892300" cy="263525"/>
           <a:chOff x="0" y="0"/>
           <a:chExt cx="1892300" cy="263525"/>
         </a:xfrm>
@@ -11573,15 +11588,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
-    <col min="2" max="2" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="17.25" thickBot="1">
+    <row r="1" spans="1:3" ht="16.8" thickBot="1">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -11589,10 +11604,10 @@
         <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="17.25" thickBot="1">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="16.8" thickBot="1">
       <c r="A2" s="17" t="s">
         <v>19</v>
       </c>
@@ -11600,111 +11615,111 @@
         <v>20</v>
       </c>
       <c r="C2" s="42" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="17.25" thickBot="1">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="16.8" thickBot="1">
       <c r="A3" s="28" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B3" s="20" t="s">
         <v>21</v>
       </c>
       <c r="C3" s="42" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="17.25" thickBot="1">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="16.8" thickBot="1">
       <c r="A4" s="28" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="42" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="16.8" thickBot="1">
+      <c r="A5" s="28" t="s">
+        <v>231</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>241</v>
+      </c>
+      <c r="C5" s="42" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A5" s="28" t="s">
+    <row r="6" spans="1:3" ht="16.8" thickBot="1">
+      <c r="A6" s="28" t="s">
         <v>232</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B6" s="21" t="s">
         <v>242</v>
-      </c>
-      <c r="C5" s="42" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="17.25" thickBot="1">
-      <c r="A6" s="28" t="s">
-        <v>233</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="28" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="28" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="28" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="28" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="28" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="28" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="28" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="28" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="28" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -11715,49 +11730,49 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D11B851-F053-408E-AA0E-8B712B07D6FE}">
-  <dimension ref="A1:K88"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L88"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
-    <col min="1" max="1" width="25.875" customWidth="1"/>
-    <col min="2" max="2" width="10.125" customWidth="1"/>
-    <col min="4" max="4" width="2.5" style="38" customWidth="1"/>
-    <col min="5" max="5" width="26.875" customWidth="1"/>
-    <col min="6" max="6" width="7.25" customWidth="1"/>
-    <col min="8" max="8" width="2.625" style="38" customWidth="1"/>
-    <col min="9" max="9" width="34.375" customWidth="1"/>
+    <col min="1" max="1" width="25.88671875" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" customWidth="1"/>
+    <col min="4" max="4" width="2.44140625" style="38" customWidth="1"/>
+    <col min="5" max="5" width="26.88671875" customWidth="1"/>
+    <col min="6" max="6" width="7.21875" customWidth="1"/>
+    <col min="8" max="8" width="2.6640625" style="38" customWidth="1"/>
+    <col min="9" max="9" width="34.33203125" customWidth="1"/>
     <col min="10" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B1" s="41" t="s">
         <v>173</v>
-      </c>
-      <c r="B1" s="41" t="s">
-        <v>174</v>
       </c>
       <c r="C1" s="7" t="str">
         <f>"var code ="&amp;B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88&amp;";"</f>
         <v>var code =;</v>
       </c>
       <c r="D1" s="38" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F1" s="41" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G1" s="7" t="str">
         <f>"var code ='"&amp;F2&amp;F3&amp;F4&amp;F5&amp;F6&amp;F7&amp;F8&amp;F9&amp;F10&amp;F11&amp;F12&amp;F13&amp;F14&amp;F15&amp;F16&amp;F17&amp;F18&amp;F19&amp;F20&amp;F21&amp;F22&amp;F23&amp;F24&amp;F25&amp;F26&amp;F27&amp;F28&amp;F29&amp;F30&amp;F31&amp;F32&amp;F33&amp;F34&amp;F35&amp;F36&amp;F37&amp;F38&amp;F39&amp;F40&amp;F41&amp;F42&amp;F43&amp;F44&amp;F45&amp;F46&amp;F47&amp;F48&amp;F49&amp;F50&amp;F51&amp;F52&amp;F53&amp;F54&amp;F55&amp;F56&amp;F57&amp;F58&amp;F59&amp;F60&amp;F61&amp;F62&amp;F63&amp;F64&amp;F65&amp;F66&amp;F67&amp;F68&amp;F69&amp;F70&amp;F71&amp;F72&amp;F73&amp;F74&amp;F75&amp;F76&amp;F77&amp;F78&amp;F79&amp;F80&amp;F81&amp;F82&amp;F83&amp;F84&amp;F85&amp;F86&amp;F87&amp;F88&amp;"';"</f>
         <v>var code ='';</v>
       </c>
       <c r="I1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J1" s="41" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="K1" s="7" t="str">
         <f>"var code ="&amp;J2&amp;J3&amp;";"</f>
@@ -11777,7 +11792,7 @@
         <v/>
       </c>
       <c r="I2" s="14" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J2" s="27" t="str">
         <f>IF(NOT(ISBLANK(I2)),I2&amp;"+'\n '+","")</f>
@@ -11797,7 +11812,7 @@
         <v/>
       </c>
       <c r="I3" s="14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J3" s="27" t="str">
         <f t="shared" ref="J3:J66" si="2">IF(NOT(ISBLANK(I3)),I3&amp;"+'\n '+","")</f>
@@ -11857,7 +11872,7 @@
         <v/>
       </c>
       <c r="I6" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J6" s="27" t="str">
         <f t="shared" si="2"/>
@@ -11877,7 +11892,7 @@
         <v/>
       </c>
       <c r="I7" s="14" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J7" s="27" t="str">
         <f t="shared" si="2"/>
@@ -11897,7 +11912,7 @@
         <v/>
       </c>
       <c r="I8" s="14" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J8" s="27" t="str">
         <f t="shared" si="2"/>
@@ -11939,7 +11954,7 @@
         <v/>
       </c>
       <c r="I10" s="14" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J10" s="27" t="str">
         <f t="shared" si="2"/>
@@ -11959,7 +11974,7 @@
         <v/>
       </c>
       <c r="I11" s="14" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J11" s="27" t="str">
         <f t="shared" si="2"/>
@@ -12001,7 +12016,7 @@
         <v/>
       </c>
       <c r="I13" s="14" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J13" s="27" t="str">
         <f t="shared" si="2"/>
@@ -12021,7 +12036,7 @@
         <v/>
       </c>
       <c r="I14" s="14" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J14" s="27" t="str">
         <f t="shared" si="2"/>
@@ -12040,7 +12055,7 @@
         <v/>
       </c>
       <c r="I15" s="14" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J15" s="27" t="str">
         <f t="shared" si="2"/>
@@ -12059,14 +12074,14 @@
         <v/>
       </c>
       <c r="I16" s="14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J16" s="27" t="str">
         <f t="shared" si="2"/>
         <v>'const char* mqtt_password ="' +value_mqtt_pwd+'";'+'\n '+</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:12">
       <c r="A17" s="23"/>
       <c r="B17" s="27" t="str">
         <f t="shared" si="0"/>
@@ -12078,14 +12093,14 @@
         <v/>
       </c>
       <c r="I17" s="14" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J17" s="27" t="str">
         <f t="shared" si="2"/>
         <v>'const int mqtt_port =' +value_mqtt_port+';'+'\n '+</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:12">
       <c r="A18" s="23"/>
       <c r="B18" s="27" t="str">
         <f t="shared" si="0"/>
@@ -12102,7 +12117,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:12">
       <c r="A19" s="23"/>
       <c r="B19" s="27" t="str">
         <f t="shared" si="0"/>
@@ -12119,7 +12134,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:12">
       <c r="A20" s="23"/>
       <c r="B20" s="27" t="str">
         <f t="shared" si="0"/>
@@ -12140,7 +12155,7 @@
         <v>var code =;</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:12">
       <c r="A21" s="23"/>
       <c r="B21" s="27" t="str">
         <f t="shared" si="0"/>
@@ -12157,7 +12172,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:12">
       <c r="A22" s="23"/>
       <c r="B22" s="27" t="str">
         <f t="shared" si="0"/>
@@ -12174,7 +12189,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:12" ht="28.2">
       <c r="A23" s="23"/>
       <c r="B23" s="27" t="str">
         <f t="shared" si="0"/>
@@ -12190,8 +12205,11 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-    </row>
-    <row r="24" spans="1:11">
+      <c r="L23" s="45" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24" s="23"/>
       <c r="B24" s="27" t="str">
         <f t="shared" si="0"/>
@@ -12208,7 +12226,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:12">
       <c r="A25" s="23"/>
       <c r="B25" s="27" t="str">
         <f t="shared" si="0"/>
@@ -12225,7 +12243,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:12">
       <c r="A26" s="23"/>
       <c r="B26" s="27" t="str">
         <f t="shared" si="0"/>
@@ -12242,7 +12260,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:12">
       <c r="A27" s="23"/>
       <c r="B27" s="27" t="str">
         <f t="shared" si="0"/>
@@ -12259,7 +12277,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:12">
       <c r="A28" s="23"/>
       <c r="B28" s="27" t="str">
         <f t="shared" si="0"/>
@@ -12276,7 +12294,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:12">
       <c r="A29" s="23"/>
       <c r="B29" s="27" t="str">
         <f t="shared" si="0"/>
@@ -12293,7 +12311,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:12">
       <c r="A30" s="23"/>
       <c r="B30" s="27" t="str">
         <f t="shared" si="0"/>
@@ -12310,7 +12328,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:12">
       <c r="A31" s="23"/>
       <c r="B31" s="27" t="str">
         <f t="shared" si="0"/>
@@ -12327,7 +12345,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:12">
       <c r="A32" s="23"/>
       <c r="B32" s="27" t="str">
         <f t="shared" si="0"/>
@@ -13305,36 +13323,36 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G88"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
-    <col min="2" max="2" width="23.75" customWidth="1"/>
-    <col min="4" max="4" width="6.5" style="38" customWidth="1"/>
-    <col min="5" max="5" width="34.375" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" customWidth="1"/>
+    <col min="4" max="4" width="6.44140625" style="38" customWidth="1"/>
+    <col min="5" max="5" width="34.33203125" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B1" t="s">
         <v>173</v>
-      </c>
-      <c r="B1" t="s">
-        <v>174</v>
       </c>
       <c r="C1" s="7" t="str">
         <f>"var code ="&amp;B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88&amp;";"</f>
         <v>var code ='String(topic) ==' +dropdown_mqtt_topic;</v>
       </c>
       <c r="D1" s="38" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G1" s="7" t="str">
         <f>"var code ='"&amp;F2&amp;F3&amp;F4&amp;F5&amp;F6&amp;F7&amp;F8&amp;F9&amp;F10&amp;F11&amp;F12&amp;F13&amp;F14&amp;F15&amp;F16&amp;F17&amp;F18&amp;F19&amp;F20&amp;F21&amp;F22&amp;F23&amp;F24&amp;F25&amp;F26&amp;F27&amp;F28&amp;F29&amp;F30&amp;F31&amp;F32&amp;F33&amp;F34&amp;F35&amp;F36&amp;F37&amp;F38&amp;F39&amp;F40&amp;F41&amp;F42&amp;F43&amp;F44&amp;F45&amp;F46&amp;F47&amp;F48&amp;F49&amp;F50&amp;F51&amp;F52&amp;F53&amp;F54&amp;F55&amp;F56&amp;F57&amp;F58&amp;F59&amp;F60&amp;F61&amp;F62&amp;F63&amp;F64&amp;F65&amp;F66&amp;F67&amp;F68&amp;F69&amp;F70&amp;F71&amp;F72&amp;F73&amp;F74&amp;F75&amp;F76&amp;F77&amp;F78&amp;F79&amp;F80&amp;F81&amp;F82&amp;F83&amp;F84&amp;F85&amp;F86&amp;F87&amp;F88&amp;"';"</f>
@@ -13343,7 +13361,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B2" s="27" t="str">
         <f>IF(NOT(ISBLANK(A2)),A2,"")</f>
@@ -14409,36 +14427,36 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G88"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
-    <col min="2" max="2" width="23.75" customWidth="1"/>
-    <col min="4" max="4" width="6.5" style="38" customWidth="1"/>
-    <col min="5" max="5" width="34.375" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" customWidth="1"/>
+    <col min="4" max="4" width="6.44140625" style="38" customWidth="1"/>
+    <col min="5" max="5" width="34.33203125" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B1" t="s">
         <v>173</v>
-      </c>
-      <c r="B1" t="s">
-        <v>174</v>
       </c>
       <c r="C1" s="7" t="str">
         <f>"var code ="&amp;B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88&amp;";"</f>
         <v>var code =;</v>
       </c>
       <c r="D1" s="38" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G1" s="7" t="str">
         <f>"var code ='"&amp;F2&amp;F3&amp;F4&amp;F5&amp;F6&amp;F7&amp;F8&amp;F9&amp;F10&amp;F11&amp;F12&amp;F13&amp;F14&amp;F15&amp;F16&amp;F17&amp;F18&amp;F19&amp;F20&amp;F21&amp;F22&amp;F23&amp;F24&amp;F25&amp;F26&amp;F27&amp;F28&amp;F29&amp;F30&amp;F31&amp;F32&amp;F33&amp;F34&amp;F35&amp;F36&amp;F37&amp;F38&amp;F39&amp;F40&amp;F41&amp;F42&amp;F43&amp;F44&amp;F45&amp;F46&amp;F47&amp;F48&amp;F49&amp;F50&amp;F51&amp;F52&amp;F53&amp;F54&amp;F55&amp;F56&amp;F57&amp;F58&amp;F59&amp;F60&amp;F61&amp;F62&amp;F63&amp;F64&amp;F65&amp;F66&amp;F67&amp;F68&amp;F69&amp;F70&amp;F71&amp;F72&amp;F73&amp;F74&amp;F75&amp;F76&amp;F77&amp;F78&amp;F79&amp;F80&amp;F81&amp;F82&amp;F83&amp;F84&amp;F85&amp;F86&amp;F87&amp;F88&amp;"';"</f>
@@ -14453,7 +14471,7 @@
       </c>
       <c r="D2" s="39"/>
       <c r="E2" s="24" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F2" s="27" t="str">
         <f>IF(NOT(ISBLANK(E2)),E2&amp;"\n ","")</f>
@@ -14468,7 +14486,7 @@
       </c>
       <c r="D3" s="40"/>
       <c r="E3" s="24" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F3" s="27" t="str">
         <f t="shared" ref="F3:F66" si="1">IF(NOT(ISBLANK(E3)),E3&amp;"\n ","")</f>
@@ -14483,7 +14501,7 @@
       </c>
       <c r="D4" s="39"/>
       <c r="E4" s="24" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F4" s="27" t="str">
         <f t="shared" si="1"/>
@@ -15517,36 +15535,36 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G88"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
-    <col min="2" max="2" width="23.75" customWidth="1"/>
-    <col min="4" max="4" width="6.5" style="38" customWidth="1"/>
-    <col min="5" max="5" width="34.375" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" customWidth="1"/>
+    <col min="4" max="4" width="6.44140625" style="38" customWidth="1"/>
+    <col min="5" max="5" width="34.33203125" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B1" t="s">
         <v>173</v>
-      </c>
-      <c r="B1" t="s">
-        <v>174</v>
       </c>
       <c r="C1" s="7" t="str">
         <f>"var code ="&amp;B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88&amp;";"</f>
         <v>var code =;</v>
       </c>
       <c r="D1" s="38" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G1" s="7" t="str">
         <f>"var code ='"&amp;F2&amp;F3&amp;F4&amp;F5&amp;F6&amp;F7&amp;F8&amp;F9&amp;F10&amp;F11&amp;F12&amp;F13&amp;F14&amp;F15&amp;F16&amp;F17&amp;F18&amp;F19&amp;F20&amp;F21&amp;F22&amp;F23&amp;F24&amp;F25&amp;F26&amp;F27&amp;F28&amp;F29&amp;F30&amp;F31&amp;F32&amp;F33&amp;F34&amp;F35&amp;F36&amp;F37&amp;F38&amp;F39&amp;F40&amp;F41&amp;F42&amp;F43&amp;F44&amp;F45&amp;F46&amp;F47&amp;F48&amp;F49&amp;F50&amp;F51&amp;F52&amp;F53&amp;F54&amp;F55&amp;F56&amp;F57&amp;F58&amp;F59&amp;F60&amp;F61&amp;F62&amp;F63&amp;F64&amp;F65&amp;F66&amp;F67&amp;F68&amp;F69&amp;F70&amp;F71&amp;F72&amp;F73&amp;F74&amp;F75&amp;F76&amp;F77&amp;F78&amp;F79&amp;F80&amp;F81&amp;F82&amp;F83&amp;F84&amp;F85&amp;F86&amp;F87&amp;F88&amp;"';"</f>
@@ -15561,7 +15579,7 @@
       </c>
       <c r="D2" s="39"/>
       <c r="E2" s="24" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F2" s="27" t="str">
         <f>IF(NOT(ISBLANK(E2)),E2&amp;"\n ","")</f>
@@ -15576,7 +15594,7 @@
       </c>
       <c r="D3" s="40"/>
       <c r="E3" s="24" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F3" s="27" t="str">
         <f t="shared" ref="F3:F66" si="1">IF(NOT(ISBLANK(E3)),E3&amp;"\n ","")</f>
@@ -15591,7 +15609,7 @@
       </c>
       <c r="D4" s="39"/>
       <c r="E4" s="24" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F4" s="27" t="str">
         <f t="shared" si="1"/>
@@ -16625,36 +16643,36 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G88"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
-    <col min="2" max="2" width="23.75" customWidth="1"/>
-    <col min="4" max="4" width="6.5" style="38" customWidth="1"/>
-    <col min="5" max="5" width="34.375" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" customWidth="1"/>
+    <col min="4" max="4" width="6.44140625" style="38" customWidth="1"/>
+    <col min="5" max="5" width="34.33203125" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B1" t="s">
         <v>173</v>
-      </c>
-      <c r="B1" t="s">
-        <v>174</v>
       </c>
       <c r="C1" s="7" t="str">
         <f>"var code ="&amp;B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88&amp;";"</f>
         <v>var code =;</v>
       </c>
       <c r="D1" s="38" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G1" s="7" t="str">
         <f>"var code ='"&amp;F2&amp;F3&amp;F4&amp;F5&amp;F6&amp;F7&amp;F8&amp;F9&amp;F10&amp;F11&amp;F12&amp;F13&amp;F14&amp;F15&amp;F16&amp;F17&amp;F18&amp;F19&amp;F20&amp;F21&amp;F22&amp;F23&amp;F24&amp;F25&amp;F26&amp;F27&amp;F28&amp;F29&amp;F30&amp;F31&amp;F32&amp;F33&amp;F34&amp;F35&amp;F36&amp;F37&amp;F38&amp;F39&amp;F40&amp;F41&amp;F42&amp;F43&amp;F44&amp;F45&amp;F46&amp;F47&amp;F48&amp;F49&amp;F50&amp;F51&amp;F52&amp;F53&amp;F54&amp;F55&amp;F56&amp;F57&amp;F58&amp;F59&amp;F60&amp;F61&amp;F62&amp;F63&amp;F64&amp;F65&amp;F66&amp;F67&amp;F68&amp;F69&amp;F70&amp;F71&amp;F72&amp;F73&amp;F74&amp;F75&amp;F76&amp;F77&amp;F78&amp;F79&amp;F80&amp;F81&amp;F82&amp;F83&amp;F84&amp;F85&amp;F86&amp;F87&amp;F88&amp;"';"</f>
@@ -16669,7 +16687,7 @@
       </c>
       <c r="D2" s="39"/>
       <c r="E2" s="24" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F2" s="27" t="str">
         <f>IF(NOT(ISBLANK(E2)),E2&amp;"\n ","")</f>
@@ -16684,7 +16702,7 @@
       </c>
       <c r="D3" s="40"/>
       <c r="E3" s="24" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F3" s="27" t="str">
         <f t="shared" ref="F3:F66" si="1">IF(NOT(ISBLANK(E3)),E3&amp;"\n ","")</f>
@@ -17731,36 +17749,36 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G88"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
-    <col min="2" max="2" width="23.75" customWidth="1"/>
-    <col min="4" max="4" width="6.5" style="38" customWidth="1"/>
-    <col min="5" max="5" width="34.375" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" customWidth="1"/>
+    <col min="4" max="4" width="6.44140625" style="38" customWidth="1"/>
+    <col min="5" max="5" width="34.33203125" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B1" t="s">
         <v>173</v>
-      </c>
-      <c r="B1" t="s">
-        <v>174</v>
       </c>
       <c r="C1" s="7" t="str">
         <f>"var code ="&amp;B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88&amp;";"</f>
         <v>var code ='str.indexOf('+dropdown_uart_topic+') != -1';</v>
       </c>
       <c r="D1" s="38" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G1" s="7" t="str">
         <f>"var code ='"&amp;F2&amp;F3&amp;F4&amp;F5&amp;F6&amp;F7&amp;F8&amp;F9&amp;F10&amp;F11&amp;F12&amp;F13&amp;F14&amp;F15&amp;F16&amp;F17&amp;F18&amp;F19&amp;F20&amp;F21&amp;F22&amp;F23&amp;F24&amp;F25&amp;F26&amp;F27&amp;F28&amp;F29&amp;F30&amp;F31&amp;F32&amp;F33&amp;F34&amp;F35&amp;F36&amp;F37&amp;F38&amp;F39&amp;F40&amp;F41&amp;F42&amp;F43&amp;F44&amp;F45&amp;F46&amp;F47&amp;F48&amp;F49&amp;F50&amp;F51&amp;F52&amp;F53&amp;F54&amp;F55&amp;F56&amp;F57&amp;F58&amp;F59&amp;F60&amp;F61&amp;F62&amp;F63&amp;F64&amp;F65&amp;F66&amp;F67&amp;F68&amp;F69&amp;F70&amp;F71&amp;F72&amp;F73&amp;F74&amp;F75&amp;F76&amp;F77&amp;F78&amp;F79&amp;F80&amp;F81&amp;F82&amp;F83&amp;F84&amp;F85&amp;F86&amp;F87&amp;F88&amp;"';"</f>
@@ -17769,7 +17787,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="14" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B2" s="27" t="str">
         <f>IF(NOT(ISBLANK(A2)),A2,"")</f>
@@ -18835,36 +18853,36 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G88"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
-    <col min="2" max="2" width="23.75" customWidth="1"/>
-    <col min="4" max="4" width="6.5" style="38" customWidth="1"/>
-    <col min="5" max="5" width="34.375" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" customWidth="1"/>
+    <col min="4" max="4" width="6.44140625" style="38" customWidth="1"/>
+    <col min="5" max="5" width="34.33203125" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B1" t="s">
         <v>173</v>
-      </c>
-      <c r="B1" t="s">
-        <v>174</v>
       </c>
       <c r="C1" s="7" t="str">
         <f>"var code ="&amp;B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88&amp;";"</f>
         <v>var code =;</v>
       </c>
       <c r="D1" s="38" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G1" s="7" t="str">
         <f>"var code ='"&amp;F2&amp;F3&amp;F4&amp;F5&amp;F6&amp;F7&amp;F8&amp;F9&amp;F10&amp;F11&amp;F12&amp;F13&amp;F14&amp;F15&amp;F16&amp;F17&amp;F18&amp;F19&amp;F20&amp;F21&amp;F22&amp;F23&amp;F24&amp;F25&amp;F26&amp;F27&amp;F28&amp;F29&amp;F30&amp;F31&amp;F32&amp;F33&amp;F34&amp;F35&amp;F36&amp;F37&amp;F38&amp;F39&amp;F40&amp;F41&amp;F42&amp;F43&amp;F44&amp;F45&amp;F46&amp;F47&amp;F48&amp;F49&amp;F50&amp;F51&amp;F52&amp;F53&amp;F54&amp;F55&amp;F56&amp;F57&amp;F58&amp;F59&amp;F60&amp;F61&amp;F62&amp;F63&amp;F64&amp;F65&amp;F66&amp;F67&amp;F68&amp;F69&amp;F70&amp;F71&amp;F72&amp;F73&amp;F74&amp;F75&amp;F76&amp;F77&amp;F78&amp;F79&amp;F80&amp;F81&amp;F82&amp;F83&amp;F84&amp;F85&amp;F86&amp;F87&amp;F88&amp;"';"</f>
@@ -18879,7 +18897,7 @@
       </c>
       <c r="D2" s="39"/>
       <c r="E2" s="24" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F2" s="27" t="str">
         <f>IF(NOT(ISBLANK(E2)),E2&amp;"\n ","")</f>
@@ -18894,7 +18912,7 @@
       </c>
       <c r="D3" s="40"/>
       <c r="E3" s="24" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F3" s="27" t="str">
         <f t="shared" ref="F3:F66" si="1">IF(NOT(ISBLANK(E3)),E3&amp;"\n ","")</f>
@@ -18909,7 +18927,7 @@
       </c>
       <c r="D4" s="39"/>
       <c r="E4" s="24" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F4" s="27" t="str">
         <f t="shared" si="1"/>
@@ -18924,7 +18942,7 @@
       </c>
       <c r="D5" s="40"/>
       <c r="E5" s="24" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F5" s="27" t="str">
         <f t="shared" si="1"/>
@@ -18939,7 +18957,7 @@
       </c>
       <c r="D6" s="40"/>
       <c r="E6" s="24" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F6" s="27" t="str">
         <f t="shared" si="1"/>
@@ -18954,7 +18972,7 @@
       </c>
       <c r="D7" s="40"/>
       <c r="E7" s="24" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F7" s="27" t="str">
         <f t="shared" si="1"/>
@@ -18969,7 +18987,7 @@
       </c>
       <c r="D8" s="40"/>
       <c r="E8" s="24" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F8" s="27" t="str">
         <f t="shared" si="1"/>
@@ -18984,7 +19002,7 @@
       </c>
       <c r="D9" s="40"/>
       <c r="E9" s="24" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F9" s="27" t="str">
         <f t="shared" si="1"/>
@@ -18999,7 +19017,7 @@
       </c>
       <c r="D10" s="40"/>
       <c r="E10" s="24" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F10" s="27" t="str">
         <f t="shared" si="1"/>
@@ -19955,36 +19973,36 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G88"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
-    <col min="2" max="2" width="23.75" customWidth="1"/>
-    <col min="4" max="4" width="6.5" style="38" customWidth="1"/>
-    <col min="5" max="5" width="34.375" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" customWidth="1"/>
+    <col min="4" max="4" width="6.44140625" style="38" customWidth="1"/>
+    <col min="5" max="5" width="34.33203125" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B1" t="s">
         <v>173</v>
-      </c>
-      <c r="B1" t="s">
-        <v>174</v>
       </c>
       <c r="C1" s="7" t="str">
         <f>"var code ="&amp;B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88&amp;";"</f>
         <v>var code =;</v>
       </c>
       <c r="D1" s="38" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G1" s="7" t="str">
         <f>"var code ='"&amp;F2&amp;F3&amp;F4&amp;F5&amp;F6&amp;F7&amp;F8&amp;F9&amp;F10&amp;F11&amp;F12&amp;F13&amp;F14&amp;F15&amp;F16&amp;F17&amp;F18&amp;F19&amp;F20&amp;F21&amp;F22&amp;F23&amp;F24&amp;F25&amp;F26&amp;F27&amp;F28&amp;F29&amp;F30&amp;F31&amp;F32&amp;F33&amp;F34&amp;F35&amp;F36&amp;F37&amp;F38&amp;F39&amp;F40&amp;F41&amp;F42&amp;F43&amp;F44&amp;F45&amp;F46&amp;F47&amp;F48&amp;F49&amp;F50&amp;F51&amp;F52&amp;F53&amp;F54&amp;F55&amp;F56&amp;F57&amp;F58&amp;F59&amp;F60&amp;F61&amp;F62&amp;F63&amp;F64&amp;F65&amp;F66&amp;F67&amp;F68&amp;F69&amp;F70&amp;F71&amp;F72&amp;F73&amp;F74&amp;F75&amp;F76&amp;F77&amp;F78&amp;F79&amp;F80&amp;F81&amp;F82&amp;F83&amp;F84&amp;F85&amp;F86&amp;F87&amp;F88&amp;"';"</f>
@@ -19999,7 +20017,7 @@
       </c>
       <c r="D2" s="39"/>
       <c r="E2" s="24" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F2" s="27" t="str">
         <f>IF(NOT(ISBLANK(E2)),E2&amp;"\n ","")</f>
@@ -20014,7 +20032,7 @@
       </c>
       <c r="D3" s="40"/>
       <c r="E3" s="24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F3" s="27" t="str">
         <f t="shared" ref="F3:F66" si="1">IF(NOT(ISBLANK(E3)),E3&amp;"\n ","")</f>
@@ -21061,36 +21079,36 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G88"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
-    <col min="2" max="2" width="23.75" customWidth="1"/>
-    <col min="4" max="4" width="6.5" style="38" customWidth="1"/>
-    <col min="5" max="5" width="34.375" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" customWidth="1"/>
+    <col min="4" max="4" width="6.44140625" style="38" customWidth="1"/>
+    <col min="5" max="5" width="34.33203125" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B1" t="s">
         <v>173</v>
-      </c>
-      <c r="B1" t="s">
-        <v>174</v>
       </c>
       <c r="C1" s="7" t="str">
         <f>"var code ="&amp;B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88&amp;";"</f>
         <v>var code =;</v>
       </c>
       <c r="D1" s="38" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G1" s="7" t="str">
         <f>"var code ='"&amp;F2&amp;F3&amp;F4&amp;F5&amp;F6&amp;F7&amp;F8&amp;F9&amp;F10&amp;F11&amp;F12&amp;F13&amp;F14&amp;F15&amp;F16&amp;F17&amp;F18&amp;F19&amp;F20&amp;F21&amp;F22&amp;F23&amp;F24&amp;F25&amp;F26&amp;F27&amp;F28&amp;F29&amp;F30&amp;F31&amp;F32&amp;F33&amp;F34&amp;F35&amp;F36&amp;F37&amp;F38&amp;F39&amp;F40&amp;F41&amp;F42&amp;F43&amp;F44&amp;F45&amp;F46&amp;F47&amp;F48&amp;F49&amp;F50&amp;F51&amp;F52&amp;F53&amp;F54&amp;F55&amp;F56&amp;F57&amp;F58&amp;F59&amp;F60&amp;F61&amp;F62&amp;F63&amp;F64&amp;F65&amp;F66&amp;F67&amp;F68&amp;F69&amp;F70&amp;F71&amp;F72&amp;F73&amp;F74&amp;F75&amp;F76&amp;F77&amp;F78&amp;F79&amp;F80&amp;F81&amp;F82&amp;F83&amp;F84&amp;F85&amp;F86&amp;F87&amp;F88&amp;"';"</f>
@@ -21105,7 +21123,7 @@
       </c>
       <c r="D2" s="39"/>
       <c r="E2" s="24" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F2" s="27" t="str">
         <f>IF(NOT(ISBLANK(E2)),E2&amp;"\n ","")</f>
@@ -21120,7 +21138,7 @@
       </c>
       <c r="D3" s="40"/>
       <c r="E3" s="24" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F3" s="27" t="str">
         <f t="shared" ref="F3:F66" si="1">IF(NOT(ISBLANK(E3)),E3&amp;"\n ","")</f>
@@ -21135,7 +21153,7 @@
       </c>
       <c r="D4" s="39"/>
       <c r="E4" s="24" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F4" s="27" t="str">
         <f t="shared" si="1"/>
@@ -21150,7 +21168,7 @@
       </c>
       <c r="D5" s="40"/>
       <c r="E5" s="24" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F5" s="27" t="str">
         <f t="shared" si="1"/>
@@ -21165,7 +21183,7 @@
       </c>
       <c r="D6" s="40"/>
       <c r="E6" s="24" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F6" s="27" t="str">
         <f t="shared" si="1"/>
@@ -21180,7 +21198,7 @@
       </c>
       <c r="D7" s="40"/>
       <c r="E7" s="24" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F7" s="27" t="str">
         <f t="shared" si="1"/>
@@ -21195,7 +21213,7 @@
       </c>
       <c r="D8" s="40"/>
       <c r="E8" s="24" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F8" s="27" t="str">
         <f t="shared" si="1"/>
@@ -21210,7 +21228,7 @@
       </c>
       <c r="D9" s="40"/>
       <c r="E9" s="24" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F9" s="27" t="str">
         <f t="shared" si="1"/>
@@ -21225,7 +21243,7 @@
       </c>
       <c r="D10" s="40"/>
       <c r="E10" s="24" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F10" s="27" t="str">
         <f t="shared" si="1"/>
@@ -22181,36 +22199,36 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G88"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
-    <col min="2" max="2" width="23.75" customWidth="1"/>
-    <col min="4" max="4" width="6.5" style="38" customWidth="1"/>
-    <col min="5" max="5" width="34.375" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" customWidth="1"/>
+    <col min="4" max="4" width="6.44140625" style="38" customWidth="1"/>
+    <col min="5" max="5" width="34.33203125" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B1" t="s">
         <v>173</v>
-      </c>
-      <c r="B1" t="s">
-        <v>174</v>
       </c>
       <c r="C1" s="7" t="str">
         <f>"var code ="&amp;B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88&amp;";"</f>
         <v>var code =;</v>
       </c>
       <c r="D1" s="38" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G1" s="7" t="str">
         <f>"var code ='"&amp;F2&amp;F3&amp;F4&amp;F5&amp;F6&amp;F7&amp;F8&amp;F9&amp;F10&amp;F11&amp;F12&amp;F13&amp;F14&amp;F15&amp;F16&amp;F17&amp;F18&amp;F19&amp;F20&amp;F21&amp;F22&amp;F23&amp;F24&amp;F25&amp;F26&amp;F27&amp;F28&amp;F29&amp;F30&amp;F31&amp;F32&amp;F33&amp;F34&amp;F35&amp;F36&amp;F37&amp;F38&amp;F39&amp;F40&amp;F41&amp;F42&amp;F43&amp;F44&amp;F45&amp;F46&amp;F47&amp;F48&amp;F49&amp;F50&amp;F51&amp;F52&amp;F53&amp;F54&amp;F55&amp;F56&amp;F57&amp;F58&amp;F59&amp;F60&amp;F61&amp;F62&amp;F63&amp;F64&amp;F65&amp;F66&amp;F67&amp;F68&amp;F69&amp;F70&amp;F71&amp;F72&amp;F73&amp;F74&amp;F75&amp;F76&amp;F77&amp;F78&amp;F79&amp;F80&amp;F81&amp;F82&amp;F83&amp;F84&amp;F85&amp;F86&amp;F87&amp;F88&amp;"';"</f>
@@ -22225,7 +22243,7 @@
       </c>
       <c r="D2" s="39"/>
       <c r="E2" s="24" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F2" s="27" t="str">
         <f>IF(NOT(ISBLANK(E2)),E2&amp;"\n ","")</f>
@@ -22240,7 +22258,7 @@
       </c>
       <c r="D3" s="40"/>
       <c r="E3" s="24" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F3" s="27" t="str">
         <f t="shared" ref="F3:F66" si="1">IF(NOT(ISBLANK(E3)),E3&amp;"\n ","")</f>
@@ -22255,7 +22273,7 @@
       </c>
       <c r="D4" s="39"/>
       <c r="E4" s="24" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F4" s="27" t="str">
         <f t="shared" si="1"/>
@@ -22270,7 +22288,7 @@
       </c>
       <c r="D5" s="40"/>
       <c r="E5" s="24" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F5" s="27" t="str">
         <f t="shared" si="1"/>
@@ -22285,7 +22303,7 @@
       </c>
       <c r="D6" s="40"/>
       <c r="E6" s="24" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F6" s="27" t="str">
         <f t="shared" si="1"/>
@@ -22300,7 +22318,7 @@
       </c>
       <c r="D7" s="40"/>
       <c r="E7" s="24" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F7" s="27" t="str">
         <f t="shared" si="1"/>
@@ -22315,7 +22333,7 @@
       </c>
       <c r="D8" s="40"/>
       <c r="E8" s="24" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F8" s="27" t="str">
         <f t="shared" si="1"/>
@@ -22343,7 +22361,7 @@
       </c>
       <c r="D10" s="40"/>
       <c r="E10" s="24" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F10" s="27" t="str">
         <f t="shared" si="1"/>
@@ -23299,18 +23317,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I88"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="47" customWidth="1"/>
-    <col min="2" max="2" width="33.25" style="25" customWidth="1"/>
-    <col min="3" max="3" width="17.375" customWidth="1"/>
-    <col min="4" max="4" width="10.125" customWidth="1"/>
-    <col min="5" max="5" width="21.875" customWidth="1"/>
-    <col min="6" max="6" width="10.125" customWidth="1"/>
-    <col min="7" max="7" width="3.25" style="38" customWidth="1"/>
-    <col min="8" max="8" width="32.75" customWidth="1"/>
+    <col min="2" max="2" width="33.21875" style="25" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" customWidth="1"/>
+    <col min="5" max="5" width="21.88671875" customWidth="1"/>
+    <col min="6" max="6" width="10.109375" customWidth="1"/>
+    <col min="7" max="7" width="3.21875" style="38" customWidth="1"/>
+    <col min="8" max="8" width="32.77734375" customWidth="1"/>
     <col min="9" max="9" width="25" customWidth="1"/>
   </cols>
   <sheetData>
@@ -23323,14 +23341,14 @@
       </c>
       <c r="D1" s="8" t="str">
         <f>"Blockly.Arduino.definitions_['"&amp;D2&amp;"'] = '"&amp;D3&amp;"';"</f>
-        <v>Blockly.Arduino.definitions_['imi_esp32car_init'] = '#include &lt;SoftwareSerial.h&gt;\n#include &lt;WiFi.h&gt;\n#include &lt;PubSubClient.h&gt;\n#include &lt;WiFiClientSecure.h&gt;\n//與Mega通訊\nconst char* MAP_SET = "mapSet";\nconst char* GOODS_LOAD = "goodsLoad";\nconst char* LINE_NOTIFY = "lineNotify";\nconst char* CAR_GPS = "carGps";\n//===設定程式碼input Start===\n//===設定程式碼input End===\n//Topic主題\nconst char* TOPIC_MAP_SET = "imiRobot/map/set";\nconst char* TOPIC_CAR_STANDBY = "imiRobot/car/standby";\nconst char* TOPIC_CAR_GPS = "imiRobot/car/gps";\nconst char* TOPIC_GOODS_LOAD = "imiRobot/goods/load";\nconst char* TOPIC_CAR_LOWPOWER = "imiRobot/car/lowPower";\n//發佈者 傳送的消息內容\nchar* mqttSendMsg = "";\n//訂閱者 接收的消息內容\nString mqttGetMsg = "";\nWiFiClientSecure espClient;\nPubSubClient client(espClient);\n// HiveMQ Cloud Let's Encrypt CA certificate\nstatic const char* root_ca PROGMEM = R"EOF(\n-----BEGIN CERTIFICATE-----\nMIIFazCCA1OgAwIBAgIRAIIQz7DSQONZRGPgu2OCiwAwDQYJKoZIhvcNAQELBQAw\nTzELMAkGA1UEBhMCVVMxKTAnBgNVBAoTIEludGVybmV0IFNlY3VyaXR5IFJlc2Vh\ncmNoIEdyb3VwMRUwEwYDVQQDEwxJU1JHIFJvb3QgWDEwHhcNMTUwNjA0MTEwNDM4\nWhcNMzUwNjA0MTEwNDM4WjBPMQswCQYDVQQGEwJVUzEpMCcGA1UEChMgSW50ZXJu\nZXQgU2VjdXJpdHkgUmVzZWFyY2ggR3JvdXAxFTATBgNVBAMTDElTUkcgUm9vdCBY\nMTCCAiIwDQYJKoZIhvcNAQEBBQADggIPADCCAgoCggIBAK3oJHP0FDfzm54rVygc\nh77ct984kIxuPOZXoHj3dcKi/vVqbvYATyjb3miGbESTtrFj/RQSa78f0uoxmyF+\n0TM8ukj13Xnfs7j/EvEhmkvBioZxaUpmZmyPfjxwv60pIgbz5MDmgK7iS4+3mX6U\nA5/TR5d8mUgjU+g4rk8Kb4Mu0UlXjIB0ttov0DiNewNwIRt18jA8+o+u3dpjq+sW\nT8KOEUt+zwvo/7V3LvSye0rgTBIlDHCNAymg4VMk7BPZ7hm/ELNKjD+Jo2FR3qyH\nB5T0Y3HsLuJvW5iB4YlcNHlsdu87kGJ55tukmi8mxdAQ4Q7e2RCOFvu396j3x+UC\nB5iPNgiV5+I3lg02dZ77DnKxHZu8A/lJBdiB3QW0KtZB6awBdpUKD9jf1b0SHzUv\nKBds0pjBqAlkd25HN7rOrFleaJ1/ctaJxQZBKT5ZPt0m9STJEadao0xAH0ahmbWn\nOlFuhjuefXKnEgV4We0+UXgVCwOPjdAvBbI+e0ocS3MFEvzG6uBQE3xDk3SzynTn\njh8BCNAw1FtxNrQHusEwMFxIt4I7mKZ9YIqioymCzLq9gwQbooMDQaHWBfEbwrbw\nqHyGO0aoSCqI3Haadr8faqU9GY/rOPNk3sgrDQoo//fb4hVC1CLQJ13hef4Y53CI\nrU7m2Ys6xt0nUW7/vGT1M0NPAgMBAAGjQjBAMA4GA1UdDwEB/wQEAwIBBjAPBgNV\nHRMBAf8EBTADAQH/MB0GA1UdDgQWBBR5tFnme7bl5AFzgAiIyBpY9umbbjANBgkq\nhkiG9w0BAQsFAAOCAgEAVR9YqbyyqFDQDLHYGmkgJykIrGF1XIpu+ILlaS/V9lZL\nubhzEFnTIZd+50xx+7LSYK05qAvqFyFWhfFQDlnrzuBZ6brJFe+GnY+EgPbk6ZGQ\n3BebYhtF8GaV0nxvwuo77x/Py9auJ/GpsMiu/X1+mvoiBOv/2X/qkSsisRcOj/KK\nNFtY2PwByVS5uCbMiogziUwthDyC3+6WVwW6LLv3xLfHTjuCvjHIInNzktHCgKQ5\nORAzI4JMPJ+GslWYHb4phowim57iaztXOoJwTdwJx4nLCgdNbOhdjsnvzqvHu7Ur\nTkXWStAmzOVyyghqpZXjFaH3pO3JLF+l+/+sKAIuvtd7u+Nxe5AW0wdeRlN8NwdC\njNPElpzVmbUq4JUagEiuTDkHzsxHpFKVK7q4+63SM1N95R1NbdWhscdCb+ZAJzVc\noyi3B43njTOQ5yOf+1CceWxG1bQVs5ZufpsMljq4Ui0/1lvh+wjChP4kqKOJ2qxq\n4RgqsahDYVvTH9w7jXbyLeiNdd8XM2w9U/t7y0Ff/9yi0GE44Za4rF2LN9d11TPA\nmRGunUHBcnWEvgJBQl9nJEiU0Zsnvgc/ubhPgXRR4Xq37Z0j4r7g1SgEEzwxA57d\nemyPxgcYxn/eR44/KJ4EBs+lVDR3veyJm+kXQ99b21/+jh5Xos1AnX5iItreGCc=\n-----END CERTIFICATE-----\n)EOF";\n';</v>
+        <v>Blockly.Arduino.definitions_['imi_esp32car_init'] = '#include &lt;SoftwareSerial.h&gt;\n#include &lt;WiFi.h&gt;\n#include &lt;PubSubClient.h&gt;\n#include &lt;WiFiClientSecure.h&gt;\n//與Mega通訊\nconst char* MAP_SET = "mapSet";\nconst char* GOODS_LOAD = "goodsLoad";\nconst char* LINE_NOTIFY = "lineNotify";\nconst char* CAR_GPS = "carGps";\n//===設定程式碼input Start===\n//===設定程式碼input End===\n//Topic主題\nconst char* TOPIC_MAP_SET = "imiRobot/map/set";\nconst char* TOPIC_CAR_STANDBY = "imiRobot/car/standby";\nconst char* TOPIC_CAR_GPS = "imiRobot/car/gps";\nconst char* TOPIC_GOODS_LOAD = "imiRobot/goods/load";\nconst char* TOPIC_CAR_LOWPOWER = "imiRobot/car/lowPower";\n//發佈者 傳送的消息內容\nchar* mqttSendMsg = "";\n//訂閱者 接收的消息內容\nString mqttGetMsg = "";\nWiFiClientSecure espClient;\nPubSubClient client(espClient);\n// HiveMQ Cloud\nstatic const char* root_ca PROGMEM = R"EOF(\n-----BEGIN CERTIFICATE-----\nMIIFazCCA1OgAwIBAgIRAIIQz7DSQONZRGPgu2OCiwAwDQYJKoZIhvcNAQELBQAw\nTzELMAkGA1UEBhMCVVMxKTAnBgNVBAoTIEludGVybmV0IFNlY3VyaXR5IFJlc2Vh\ncmNoIEdyb3VwMRUwEwYDVQQDEwxJU1JHIFJvb3QgWDEwHhcNMTUwNjA0MTEwNDM4\nWhcNMzUwNjA0MTEwNDM4WjBPMQswCQYDVQQGEwJVUzEpMCcGA1UEChMgSW50ZXJu\nZXQgU2VjdXJpdHkgUmVzZWFyY2ggR3JvdXAxFTATBgNVBAMTDElTUkcgUm9vdCBY\nMTCCAiIwDQYJKoZIhvcNAQEBBQADggIPADCCAgoCggIBAK3oJHP0FDfzm54rVygc\nh77ct984kIxuPOZXoHj3dcKi/vVqbvYATyjb3miGbESTtrFj/RQSa78f0uoxmyF+\n0TM8ukj13Xnfs7j/EvEhmkvBioZxaUpmZmyPfjxwv60pIgbz5MDmgK7iS4+3mX6U\nA5/TR5d8mUgjU+g4rk8Kb4Mu0UlXjIB0ttov0DiNewNwIRt18jA8+o+u3dpjq+sW\nT8KOEUt+zwvo/7V3LvSye0rgTBIlDHCNAymg4VMk7BPZ7hm/ELNKjD+Jo2FR3qyH\nB5T0Y3HsLuJvW5iB4YlcNHlsdu87kGJ55tukmi8mxdAQ4Q7e2RCOFvu396j3x+UC\nB5iPNgiV5+I3lg02dZ77DnKxHZu8A/lJBdiB3QW0KtZB6awBdpUKD9jf1b0SHzUv\nKBds0pjBqAlkd25HN7rOrFleaJ1/ctaJxQZBKT5ZPt0m9STJEadao0xAH0ahmbWn\nOlFuhjuefXKnEgV4We0+UXgVCwOPjdAvBbI+e0ocS3MFEvzG6uBQE3xDk3SzynTn\njh8BCNAw1FtxNrQHusEwMFxIt4I7mKZ9YIqioymCzLq9gwQbooMDQaHWBfEbwrbw\nqHyGO0aoSCqI3Haadr8faqU9GY/rOPNk3sgrDQoo//fb4hVC1CLQJ13hef4Y53CI\nrU7m2Ys6xt0nUW7/vGT1M0NPAgMBAAGjQjBAMA4GA1UdDwEB/wQEAwIBBjAPBgNV\nHRMBAf8EBTADAQH/MB0GA1UdDgQWBBR5tFnme7bl5AFzgAiIyBpY9umbbjANBgkq\nhkiG9w0BAQsFAAOCAgEAVR9YqbyyqFDQDLHYGmkgJykIrGF1XIpu+ILlaS/V9lZL\nubhzEFnTIZd+50xx+7LSYK05qAvqFyFWhfFQDlnrzuBZ6brJFe+GnY+EgPbk6ZGQ\n3BebYhtF8GaV0nxvwuo77x/Py9auJ/GpsMiu/X1+mvoiBOv/2X/qkSsisRcOj/KK\nNFtY2PwByVS5uCbMiogziUwthDyC3+6WVwW6LLv3xLfHTjuCvjHIInNzktHCgKQ5\nORAzI4JMPJ+GslWYHb4phowim57iaztXOoJwTdwJx4nLCgdNbOhdjsnvzqvHu7Ur\nTkXWStAmzOVyyghqpZXjFaH3pO3JLF+l+/+sKAIuvtd7u+Nxe5AW0wdeRlN8NwdC\njNPElpzVmbUq4JUagEiuTDkHzsxHpFKVK7q4+63SM1N95R1NbdWhscdCb+ZAJzVc\noyi3B43njTOQ5yOf+1CceWxG1bQVs5ZufpsMljq4Ui0/1lvh+wjChP4kqKOJ2qxq\n4RgqsahDYVvTH9w7jXbyLeiNdd8XM2w9U/t7y0Ff/9yi0GE44Za4rF2LN9d11TPA\nmRGunUHBcnWEvgJBQl9nJEiU0Zsnvgc/ubhPgXRR4Xq37Z0j4r7g1SgEEzwxA57d\nemyPxgcYxn/eR44/KJ4EBs+lVDR3veyJm+kXQ99b21/+jh5Xos1AnX5iItreGCc=\n-----END CERTIFICATE-----\n)EOF";\n';</v>
       </c>
       <c r="E1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F1" s="8" t="str">
         <f>"Blockly.Arduino.definitions_['"&amp;D2&amp;"'] = '"&amp;D3&amp;"'"&amp;"+"&amp;D4&amp;"+"&amp;D5&amp;"+"&amp;D6&amp;"+"&amp;D7&amp;";"</f>
-        <v>Blockly.Arduino.definitions_['imi_esp32car_init'] = '#include &lt;SoftwareSerial.h&gt;\n#include &lt;WiFi.h&gt;\n#include &lt;PubSubClient.h&gt;\n#include &lt;WiFiClientSecure.h&gt;\n//與Mega通訊\nconst char* MAP_SET = "mapSet";\nconst char* GOODS_LOAD = "goodsLoad";\nconst char* LINE_NOTIFY = "lineNotify";\nconst char* CAR_GPS = "carGps";\n//===設定程式碼input Start===\n//===設定程式碼input End===\n//Topic主題\nconst char* TOPIC_MAP_SET = "imiRobot/map/set";\nconst char* TOPIC_CAR_STANDBY = "imiRobot/car/standby";\nconst char* TOPIC_CAR_GPS = "imiRobot/car/gps";\nconst char* TOPIC_GOODS_LOAD = "imiRobot/goods/load";\nconst char* TOPIC_CAR_LOWPOWER = "imiRobot/car/lowPower";\n//發佈者 傳送的消息內容\nchar* mqttSendMsg = "";\n//訂閱者 接收的消息內容\nString mqttGetMsg = "";\nWiFiClientSecure espClient;\nPubSubClient client(espClient);\n// HiveMQ Cloud Let's Encrypt CA certificate\nstatic const char* root_ca PROGMEM = R"EOF(\n-----BEGIN CERTIFICATE-----\nMIIFazCCA1OgAwIBAgIRAIIQz7DSQONZRGPgu2OCiwAwDQYJKoZIhvcNAQELBQAw\nTzELMAkGA1UEBhMCVVMxKTAnBgNVBAoTIEludGVybmV0IFNlY3VyaXR5IFJlc2Vh\ncmNoIEdyb3VwMRUwEwYDVQQDEwxJU1JHIFJvb3QgWDEwHhcNMTUwNjA0MTEwNDM4\nWhcNMzUwNjA0MTEwNDM4WjBPMQswCQYDVQQGEwJVUzEpMCcGA1UEChMgSW50ZXJu\nZXQgU2VjdXJpdHkgUmVzZWFyY2ggR3JvdXAxFTATBgNVBAMTDElTUkcgUm9vdCBY\nMTCCAiIwDQYJKoZIhvcNAQEBBQADggIPADCCAgoCggIBAK3oJHP0FDfzm54rVygc\nh77ct984kIxuPOZXoHj3dcKi/vVqbvYATyjb3miGbESTtrFj/RQSa78f0uoxmyF+\n0TM8ukj13Xnfs7j/EvEhmkvBioZxaUpmZmyPfjxwv60pIgbz5MDmgK7iS4+3mX6U\nA5/TR5d8mUgjU+g4rk8Kb4Mu0UlXjIB0ttov0DiNewNwIRt18jA8+o+u3dpjq+sW\nT8KOEUt+zwvo/7V3LvSye0rgTBIlDHCNAymg4VMk7BPZ7hm/ELNKjD+Jo2FR3qyH\nB5T0Y3HsLuJvW5iB4YlcNHlsdu87kGJ55tukmi8mxdAQ4Q7e2RCOFvu396j3x+UC\nB5iPNgiV5+I3lg02dZ77DnKxHZu8A/lJBdiB3QW0KtZB6awBdpUKD9jf1b0SHzUv\nKBds0pjBqAlkd25HN7rOrFleaJ1/ctaJxQZBKT5ZPt0m9STJEadao0xAH0ahmbWn\nOlFuhjuefXKnEgV4We0+UXgVCwOPjdAvBbI+e0ocS3MFEvzG6uBQE3xDk3SzynTn\njh8BCNAw1FtxNrQHusEwMFxIt4I7mKZ9YIqioymCzLq9gwQbooMDQaHWBfEbwrbw\nqHyGO0aoSCqI3Haadr8faqU9GY/rOPNk3sgrDQoo//fb4hVC1CLQJ13hef4Y53CI\nrU7m2Ys6xt0nUW7/vGT1M0NPAgMBAAGjQjBAMA4GA1UdDwEB/wQEAwIBBjAPBgNV\nHRMBAf8EBTADAQH/MB0GA1UdDgQWBBR5tFnme7bl5AFzgAiIyBpY9umbbjANBgkq\nhkiG9w0BAQsFAAOCAgEAVR9YqbyyqFDQDLHYGmkgJykIrGF1XIpu+ILlaS/V9lZL\nubhzEFnTIZd+50xx+7LSYK05qAvqFyFWhfFQDlnrzuBZ6brJFe+GnY+EgPbk6ZGQ\n3BebYhtF8GaV0nxvwuo77x/Py9auJ/GpsMiu/X1+mvoiBOv/2X/qkSsisRcOj/KK\nNFtY2PwByVS5uCbMiogziUwthDyC3+6WVwW6LLv3xLfHTjuCvjHIInNzktHCgKQ5\nORAzI4JMPJ+GslWYHb4phowim57iaztXOoJwTdwJx4nLCgdNbOhdjsnvzqvHu7Ur\nTkXWStAmzOVyyghqpZXjFaH3pO3JLF+l+/+sKAIuvtd7u+Nxe5AW0wdeRlN8NwdC\njNPElpzVmbUq4JUagEiuTDkHzsxHpFKVK7q4+63SM1N95R1NbdWhscdCb+ZAJzVc\noyi3B43njTOQ5yOf+1CceWxG1bQVs5ZufpsMljq4Ui0/1lvh+wjChP4kqKOJ2qxq\n4RgqsahDYVvTH9w7jXbyLeiNdd8XM2w9U/t7y0Ff/9yi0GE44Za4rF2LN9d11TPA\nmRGunUHBcnWEvgJBQl9nJEiU0Zsnvgc/ubhPgXRR4Xq37Z0j4r7g1SgEEzwxA57d\nemyPxgcYxn/eR44/KJ4EBs+lVDR3veyJm+kXQ99b21/+jh5Xos1AnX5iItreGCc=\n-----END CERTIFICATE-----\n)EOF";\n'+value_uart +value_wifi +value_line +value_mqtt ;</v>
+        <v>Blockly.Arduino.definitions_['imi_esp32car_init'] = '#include &lt;SoftwareSerial.h&gt;\n#include &lt;WiFi.h&gt;\n#include &lt;PubSubClient.h&gt;\n#include &lt;WiFiClientSecure.h&gt;\n//與Mega通訊\nconst char* MAP_SET = "mapSet";\nconst char* GOODS_LOAD = "goodsLoad";\nconst char* LINE_NOTIFY = "lineNotify";\nconst char* CAR_GPS = "carGps";\n//===設定程式碼input Start===\n//===設定程式碼input End===\n//Topic主題\nconst char* TOPIC_MAP_SET = "imiRobot/map/set";\nconst char* TOPIC_CAR_STANDBY = "imiRobot/car/standby";\nconst char* TOPIC_CAR_GPS = "imiRobot/car/gps";\nconst char* TOPIC_GOODS_LOAD = "imiRobot/goods/load";\nconst char* TOPIC_CAR_LOWPOWER = "imiRobot/car/lowPower";\n//發佈者 傳送的消息內容\nchar* mqttSendMsg = "";\n//訂閱者 接收的消息內容\nString mqttGetMsg = "";\nWiFiClientSecure espClient;\nPubSubClient client(espClient);\n// HiveMQ Cloud\nstatic const char* root_ca PROGMEM = R"EOF(\n-----BEGIN CERTIFICATE-----\nMIIFazCCA1OgAwIBAgIRAIIQz7DSQONZRGPgu2OCiwAwDQYJKoZIhvcNAQELBQAw\nTzELMAkGA1UEBhMCVVMxKTAnBgNVBAoTIEludGVybmV0IFNlY3VyaXR5IFJlc2Vh\ncmNoIEdyb3VwMRUwEwYDVQQDEwxJU1JHIFJvb3QgWDEwHhcNMTUwNjA0MTEwNDM4\nWhcNMzUwNjA0MTEwNDM4WjBPMQswCQYDVQQGEwJVUzEpMCcGA1UEChMgSW50ZXJu\nZXQgU2VjdXJpdHkgUmVzZWFyY2ggR3JvdXAxFTATBgNVBAMTDElTUkcgUm9vdCBY\nMTCCAiIwDQYJKoZIhvcNAQEBBQADggIPADCCAgoCggIBAK3oJHP0FDfzm54rVygc\nh77ct984kIxuPOZXoHj3dcKi/vVqbvYATyjb3miGbESTtrFj/RQSa78f0uoxmyF+\n0TM8ukj13Xnfs7j/EvEhmkvBioZxaUpmZmyPfjxwv60pIgbz5MDmgK7iS4+3mX6U\nA5/TR5d8mUgjU+g4rk8Kb4Mu0UlXjIB0ttov0DiNewNwIRt18jA8+o+u3dpjq+sW\nT8KOEUt+zwvo/7V3LvSye0rgTBIlDHCNAymg4VMk7BPZ7hm/ELNKjD+Jo2FR3qyH\nB5T0Y3HsLuJvW5iB4YlcNHlsdu87kGJ55tukmi8mxdAQ4Q7e2RCOFvu396j3x+UC\nB5iPNgiV5+I3lg02dZ77DnKxHZu8A/lJBdiB3QW0KtZB6awBdpUKD9jf1b0SHzUv\nKBds0pjBqAlkd25HN7rOrFleaJ1/ctaJxQZBKT5ZPt0m9STJEadao0xAH0ahmbWn\nOlFuhjuefXKnEgV4We0+UXgVCwOPjdAvBbI+e0ocS3MFEvzG6uBQE3xDk3SzynTn\njh8BCNAw1FtxNrQHusEwMFxIt4I7mKZ9YIqioymCzLq9gwQbooMDQaHWBfEbwrbw\nqHyGO0aoSCqI3Haadr8faqU9GY/rOPNk3sgrDQoo//fb4hVC1CLQJ13hef4Y53CI\nrU7m2Ys6xt0nUW7/vGT1M0NPAgMBAAGjQjBAMA4GA1UdDwEB/wQEAwIBBjAPBgNV\nHRMBAf8EBTADAQH/MB0GA1UdDgQWBBR5tFnme7bl5AFzgAiIyBpY9umbbjANBgkq\nhkiG9w0BAQsFAAOCAgEAVR9YqbyyqFDQDLHYGmkgJykIrGF1XIpu+ILlaS/V9lZL\nubhzEFnTIZd+50xx+7LSYK05qAvqFyFWhfFQDlnrzuBZ6brJFe+GnY+EgPbk6ZGQ\n3BebYhtF8GaV0nxvwuo77x/Py9auJ/GpsMiu/X1+mvoiBOv/2X/qkSsisRcOj/KK\nNFtY2PwByVS5uCbMiogziUwthDyC3+6WVwW6LLv3xLfHTjuCvjHIInNzktHCgKQ5\nORAzI4JMPJ+GslWYHb4phowim57iaztXOoJwTdwJx4nLCgdNbOhdjsnvzqvHu7Ur\nTkXWStAmzOVyyghqpZXjFaH3pO3JLF+l+/+sKAIuvtd7u+Nxe5AW0wdeRlN8NwdC\njNPElpzVmbUq4JUagEiuTDkHzsxHpFKVK7q4+63SM1N95R1NbdWhscdCb+ZAJzVc\noyi3B43njTOQ5yOf+1CceWxG1bQVs5ZufpsMljq4Ui0/1lvh+wjChP4kqKOJ2qxq\n4RgqsahDYVvTH9w7jXbyLeiNdd8XM2w9U/t7y0Ff/9yi0GE44Za4rF2LN9d11TPA\nmRGunUHBcnWEvgJBQl9nJEiU0Zsnvgc/ubhPgXRR4Xq37Z0j4r7g1SgEEzwxA57d\nemyPxgcYxn/eR44/KJ4EBs+lVDR3veyJm+kXQ99b21/+jh5Xos1AnX5iItreGCc=\n-----END CERTIFICATE-----\n)EOF";\n'+value_uart +value_wifi +value_line +value_mqtt ;</v>
       </c>
       <c r="G1" s="43"/>
       <c r="H1" t="s">
@@ -23374,7 +23392,7 @@
       </c>
       <c r="D3" s="5" t="str">
         <f>B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88</f>
-        <v>#include &lt;SoftwareSerial.h&gt;\n#include &lt;WiFi.h&gt;\n#include &lt;PubSubClient.h&gt;\n#include &lt;WiFiClientSecure.h&gt;\n//與Mega通訊\nconst char* MAP_SET = "mapSet";\nconst char* GOODS_LOAD = "goodsLoad";\nconst char* LINE_NOTIFY = "lineNotify";\nconst char* CAR_GPS = "carGps";\n//===設定程式碼input Start===\n//===設定程式碼input End===\n//Topic主題\nconst char* TOPIC_MAP_SET = "imiRobot/map/set";\nconst char* TOPIC_CAR_STANDBY = "imiRobot/car/standby";\nconst char* TOPIC_CAR_GPS = "imiRobot/car/gps";\nconst char* TOPIC_GOODS_LOAD = "imiRobot/goods/load";\nconst char* TOPIC_CAR_LOWPOWER = "imiRobot/car/lowPower";\n//發佈者 傳送的消息內容\nchar* mqttSendMsg = "";\n//訂閱者 接收的消息內容\nString mqttGetMsg = "";\nWiFiClientSecure espClient;\nPubSubClient client(espClient);\n// HiveMQ Cloud Let's Encrypt CA certificate\nstatic const char* root_ca PROGMEM = R"EOF(\n-----BEGIN CERTIFICATE-----\nMIIFazCCA1OgAwIBAgIRAIIQz7DSQONZRGPgu2OCiwAwDQYJKoZIhvcNAQELBQAw\nTzELMAkGA1UEBhMCVVMxKTAnBgNVBAoTIEludGVybmV0IFNlY3VyaXR5IFJlc2Vh\ncmNoIEdyb3VwMRUwEwYDVQQDEwxJU1JHIFJvb3QgWDEwHhcNMTUwNjA0MTEwNDM4\nWhcNMzUwNjA0MTEwNDM4WjBPMQswCQYDVQQGEwJVUzEpMCcGA1UEChMgSW50ZXJu\nZXQgU2VjdXJpdHkgUmVzZWFyY2ggR3JvdXAxFTATBgNVBAMTDElTUkcgUm9vdCBY\nMTCCAiIwDQYJKoZIhvcNAQEBBQADggIPADCCAgoCggIBAK3oJHP0FDfzm54rVygc\nh77ct984kIxuPOZXoHj3dcKi/vVqbvYATyjb3miGbESTtrFj/RQSa78f0uoxmyF+\n0TM8ukj13Xnfs7j/EvEhmkvBioZxaUpmZmyPfjxwv60pIgbz5MDmgK7iS4+3mX6U\nA5/TR5d8mUgjU+g4rk8Kb4Mu0UlXjIB0ttov0DiNewNwIRt18jA8+o+u3dpjq+sW\nT8KOEUt+zwvo/7V3LvSye0rgTBIlDHCNAymg4VMk7BPZ7hm/ELNKjD+Jo2FR3qyH\nB5T0Y3HsLuJvW5iB4YlcNHlsdu87kGJ55tukmi8mxdAQ4Q7e2RCOFvu396j3x+UC\nB5iPNgiV5+I3lg02dZ77DnKxHZu8A/lJBdiB3QW0KtZB6awBdpUKD9jf1b0SHzUv\nKBds0pjBqAlkd25HN7rOrFleaJ1/ctaJxQZBKT5ZPt0m9STJEadao0xAH0ahmbWn\nOlFuhjuefXKnEgV4We0+UXgVCwOPjdAvBbI+e0ocS3MFEvzG6uBQE3xDk3SzynTn\njh8BCNAw1FtxNrQHusEwMFxIt4I7mKZ9YIqioymCzLq9gwQbooMDQaHWBfEbwrbw\nqHyGO0aoSCqI3Haadr8faqU9GY/rOPNk3sgrDQoo//fb4hVC1CLQJ13hef4Y53CI\nrU7m2Ys6xt0nUW7/vGT1M0NPAgMBAAGjQjBAMA4GA1UdDwEB/wQEAwIBBjAPBgNV\nHRMBAf8EBTADAQH/MB0GA1UdDgQWBBR5tFnme7bl5AFzgAiIyBpY9umbbjANBgkq\nhkiG9w0BAQsFAAOCAgEAVR9YqbyyqFDQDLHYGmkgJykIrGF1XIpu+ILlaS/V9lZL\nubhzEFnTIZd+50xx+7LSYK05qAvqFyFWhfFQDlnrzuBZ6brJFe+GnY+EgPbk6ZGQ\n3BebYhtF8GaV0nxvwuo77x/Py9auJ/GpsMiu/X1+mvoiBOv/2X/qkSsisRcOj/KK\nNFtY2PwByVS5uCbMiogziUwthDyC3+6WVwW6LLv3xLfHTjuCvjHIInNzktHCgKQ5\nORAzI4JMPJ+GslWYHb4phowim57iaztXOoJwTdwJx4nLCgdNbOhdjsnvzqvHu7Ur\nTkXWStAmzOVyyghqpZXjFaH3pO3JLF+l+/+sKAIuvtd7u+Nxe5AW0wdeRlN8NwdC\njNPElpzVmbUq4JUagEiuTDkHzsxHpFKVK7q4+63SM1N95R1NbdWhscdCb+ZAJzVc\noyi3B43njTOQ5yOf+1CceWxG1bQVs5ZufpsMljq4Ui0/1lvh+wjChP4kqKOJ2qxq\n4RgqsahDYVvTH9w7jXbyLeiNdd8XM2w9U/t7y0Ff/9yi0GE44Za4rF2LN9d11TPA\nmRGunUHBcnWEvgJBQl9nJEiU0Zsnvgc/ubhPgXRR4Xq37Z0j4r7g1SgEEzwxA57d\nemyPxgcYxn/eR44/KJ4EBs+lVDR3veyJm+kXQ99b21/+jh5Xos1AnX5iItreGCc=\n-----END CERTIFICATE-----\n)EOF";\n</v>
+        <v>#include &lt;SoftwareSerial.h&gt;\n#include &lt;WiFi.h&gt;\n#include &lt;PubSubClient.h&gt;\n#include &lt;WiFiClientSecure.h&gt;\n//與Mega通訊\nconst char* MAP_SET = "mapSet";\nconst char* GOODS_LOAD = "goodsLoad";\nconst char* LINE_NOTIFY = "lineNotify";\nconst char* CAR_GPS = "carGps";\n//===設定程式碼input Start===\n//===設定程式碼input End===\n//Topic主題\nconst char* TOPIC_MAP_SET = "imiRobot/map/set";\nconst char* TOPIC_CAR_STANDBY = "imiRobot/car/standby";\nconst char* TOPIC_CAR_GPS = "imiRobot/car/gps";\nconst char* TOPIC_GOODS_LOAD = "imiRobot/goods/load";\nconst char* TOPIC_CAR_LOWPOWER = "imiRobot/car/lowPower";\n//發佈者 傳送的消息內容\nchar* mqttSendMsg = "";\n//訂閱者 接收的消息內容\nString mqttGetMsg = "";\nWiFiClientSecure espClient;\nPubSubClient client(espClient);\n// HiveMQ Cloud\nstatic const char* root_ca PROGMEM = R"EOF(\n-----BEGIN CERTIFICATE-----\nMIIFazCCA1OgAwIBAgIRAIIQz7DSQONZRGPgu2OCiwAwDQYJKoZIhvcNAQELBQAw\nTzELMAkGA1UEBhMCVVMxKTAnBgNVBAoTIEludGVybmV0IFNlY3VyaXR5IFJlc2Vh\ncmNoIEdyb3VwMRUwEwYDVQQDEwxJU1JHIFJvb3QgWDEwHhcNMTUwNjA0MTEwNDM4\nWhcNMzUwNjA0MTEwNDM4WjBPMQswCQYDVQQGEwJVUzEpMCcGA1UEChMgSW50ZXJu\nZXQgU2VjdXJpdHkgUmVzZWFyY2ggR3JvdXAxFTATBgNVBAMTDElTUkcgUm9vdCBY\nMTCCAiIwDQYJKoZIhvcNAQEBBQADggIPADCCAgoCggIBAK3oJHP0FDfzm54rVygc\nh77ct984kIxuPOZXoHj3dcKi/vVqbvYATyjb3miGbESTtrFj/RQSa78f0uoxmyF+\n0TM8ukj13Xnfs7j/EvEhmkvBioZxaUpmZmyPfjxwv60pIgbz5MDmgK7iS4+3mX6U\nA5/TR5d8mUgjU+g4rk8Kb4Mu0UlXjIB0ttov0DiNewNwIRt18jA8+o+u3dpjq+sW\nT8KOEUt+zwvo/7V3LvSye0rgTBIlDHCNAymg4VMk7BPZ7hm/ELNKjD+Jo2FR3qyH\nB5T0Y3HsLuJvW5iB4YlcNHlsdu87kGJ55tukmi8mxdAQ4Q7e2RCOFvu396j3x+UC\nB5iPNgiV5+I3lg02dZ77DnKxHZu8A/lJBdiB3QW0KtZB6awBdpUKD9jf1b0SHzUv\nKBds0pjBqAlkd25HN7rOrFleaJ1/ctaJxQZBKT5ZPt0m9STJEadao0xAH0ahmbWn\nOlFuhjuefXKnEgV4We0+UXgVCwOPjdAvBbI+e0ocS3MFEvzG6uBQE3xDk3SzynTn\njh8BCNAw1FtxNrQHusEwMFxIt4I7mKZ9YIqioymCzLq9gwQbooMDQaHWBfEbwrbw\nqHyGO0aoSCqI3Haadr8faqU9GY/rOPNk3sgrDQoo//fb4hVC1CLQJ13hef4Y53CI\nrU7m2Ys6xt0nUW7/vGT1M0NPAgMBAAGjQjBAMA4GA1UdDwEB/wQEAwIBBjAPBgNV\nHRMBAf8EBTADAQH/MB0GA1UdDgQWBBR5tFnme7bl5AFzgAiIyBpY9umbbjANBgkq\nhkiG9w0BAQsFAAOCAgEAVR9YqbyyqFDQDLHYGmkgJykIrGF1XIpu+ILlaS/V9lZL\nubhzEFnTIZd+50xx+7LSYK05qAvqFyFWhfFQDlnrzuBZ6brJFe+GnY+EgPbk6ZGQ\n3BebYhtF8GaV0nxvwuo77x/Py9auJ/GpsMiu/X1+mvoiBOv/2X/qkSsisRcOj/KK\nNFtY2PwByVS5uCbMiogziUwthDyC3+6WVwW6LLv3xLfHTjuCvjHIInNzktHCgKQ5\nORAzI4JMPJ+GslWYHb4phowim57iaztXOoJwTdwJx4nLCgdNbOhdjsnvzqvHu7Ur\nTkXWStAmzOVyyghqpZXjFaH3pO3JLF+l+/+sKAIuvtd7u+Nxe5AW0wdeRlN8NwdC\njNPElpzVmbUq4JUagEiuTDkHzsxHpFKVK7q4+63SM1N95R1NbdWhscdCb+ZAJzVc\noyi3B43njTOQ5yOf+1CceWxG1bQVs5ZufpsMljq4Ui0/1lvh+wjChP4kqKOJ2qxq\n4RgqsahDYVvTH9w7jXbyLeiNdd8XM2w9U/t7y0Ff/9yi0GE44Za4rF2LN9d11TPA\nmRGunUHBcnWEvgJBQl9nJEiU0Zsnvgc/ubhPgXRR4Xq37Z0j4r7g1SgEEzwxA57d\nemyPxgcYxn/eR44/KJ4EBs+lVDR3veyJm+kXQ99b21/+jh5Xos1AnX5iItreGCc=\n-----END CERTIFICATE-----\n)EOF";\n</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
@@ -23390,7 +23408,7 @@
         <v>#include &lt;PubSubClient.h&gt;\n</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D4" s="5" t="str">
         <f>變數!$C$2</f>
@@ -23408,7 +23426,7 @@
         <v>#include &lt;WiFiClientSecure.h&gt;\n</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D5" s="5" t="str">
         <f>變數!$C$3</f>
@@ -23423,7 +23441,7 @@
         <v/>
       </c>
       <c r="C6" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D6" s="5" t="str">
         <f>變數!$C$4</f>
@@ -23433,14 +23451,14 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B7" s="26" t="str">
         <f t="shared" si="0"/>
         <v>//與Mega通訊\n</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D7" s="5" t="str">
         <f>變數!$C$5</f>
@@ -23497,7 +23515,7 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B13" s="26" t="str">
         <f t="shared" si="0"/>
@@ -23520,7 +23538,7 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="23" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B16" s="26" t="str">
         <f t="shared" si="0"/>
@@ -23665,16 +23683,16 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="23" t="s">
-        <v>43</v>
+        <v>250</v>
       </c>
       <c r="B33" s="26" t="str">
         <f t="shared" si="0"/>
-        <v>// HiveMQ Cloud Let's Encrypt CA certificate\n</v>
+        <v>// HiveMQ Cloud\n</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B34" s="26" t="str">
         <f t="shared" si="0"/>
@@ -23683,7 +23701,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B35" s="26" t="str">
         <f t="shared" si="0"/>
@@ -23692,7 +23710,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B36" s="26" t="str">
         <f t="shared" si="0"/>
@@ -23701,7 +23719,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B37" s="26" t="str">
         <f t="shared" si="0"/>
@@ -23710,7 +23728,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B38" s="26" t="str">
         <f t="shared" si="0"/>
@@ -23719,7 +23737,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B39" s="26" t="str">
         <f t="shared" si="0"/>
@@ -23728,7 +23746,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B40" s="26" t="str">
         <f t="shared" si="0"/>
@@ -23737,7 +23755,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B41" s="26" t="str">
         <f t="shared" si="0"/>
@@ -23746,7 +23764,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B42" s="26" t="str">
         <f t="shared" si="0"/>
@@ -23755,7 +23773,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B43" s="26" t="str">
         <f t="shared" si="0"/>
@@ -23764,7 +23782,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="23" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B44" s="26" t="str">
         <f t="shared" si="0"/>
@@ -23773,7 +23791,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B45" s="26" t="str">
         <f t="shared" si="0"/>
@@ -23782,7 +23800,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B46" s="26" t="str">
         <f t="shared" si="0"/>
@@ -23791,7 +23809,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="23" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B47" s="26" t="str">
         <f t="shared" si="0"/>
@@ -23800,7 +23818,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B48" s="26" t="str">
         <f t="shared" si="0"/>
@@ -23809,7 +23827,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B49" s="26" t="str">
         <f t="shared" si="0"/>
@@ -23818,7 +23836,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B50" s="26" t="str">
         <f t="shared" si="0"/>
@@ -23827,7 +23845,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B51" s="26" t="str">
         <f t="shared" si="0"/>
@@ -23836,7 +23854,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B52" s="26" t="str">
         <f t="shared" si="0"/>
@@ -23845,7 +23863,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B53" s="26" t="str">
         <f t="shared" si="0"/>
@@ -23854,7 +23872,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="23" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B54" s="26" t="str">
         <f t="shared" si="0"/>
@@ -23863,7 +23881,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="23" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B55" s="26" t="str">
         <f t="shared" si="0"/>
@@ -23872,7 +23890,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="23" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B56" s="26" t="str">
         <f t="shared" si="0"/>
@@ -23881,7 +23899,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B57" s="26" t="str">
         <f t="shared" si="0"/>
@@ -23890,7 +23908,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B58" s="26" t="str">
         <f t="shared" si="0"/>
@@ -23899,7 +23917,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B59" s="26" t="str">
         <f t="shared" si="0"/>
@@ -23908,7 +23926,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B60" s="26" t="str">
         <f t="shared" si="0"/>
@@ -23917,7 +23935,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B61" s="26" t="str">
         <f t="shared" si="0"/>
@@ -23926,7 +23944,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B62" s="26" t="str">
         <f t="shared" si="0"/>
@@ -23935,7 +23953,7 @@
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B63" s="26" t="str">
         <f t="shared" si="0"/>
@@ -23944,7 +23962,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B64" s="26" t="str">
         <f t="shared" si="0"/>
@@ -23953,7 +23971,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B65" s="26" t="str">
         <f t="shared" si="0"/>
@@ -23962,7 +23980,7 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B66" s="26" t="str">
         <f t="shared" si="0"/>
@@ -24132,36 +24150,36 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G88"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
-    <col min="2" max="2" width="23.75" customWidth="1"/>
-    <col min="4" max="4" width="6.5" style="38" customWidth="1"/>
-    <col min="5" max="5" width="34.375" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" customWidth="1"/>
+    <col min="4" max="4" width="6.44140625" style="38" customWidth="1"/>
+    <col min="5" max="5" width="34.33203125" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B1" t="s">
         <v>173</v>
-      </c>
-      <c r="B1" t="s">
-        <v>174</v>
       </c>
       <c r="C1" s="7" t="str">
         <f>"var code ="&amp;B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88&amp;";"</f>
         <v>var code =;</v>
       </c>
       <c r="D1" s="38" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G1" s="7" t="str">
         <f>"var code ='"&amp;F2&amp;F3&amp;F4&amp;F5&amp;F6&amp;F7&amp;F8&amp;F9&amp;F10&amp;F11&amp;F12&amp;F13&amp;F14&amp;F15&amp;F16&amp;F17&amp;F18&amp;F19&amp;F20&amp;F21&amp;F22&amp;F23&amp;F24&amp;F25&amp;F26&amp;F27&amp;F28&amp;F29&amp;F30&amp;F31&amp;F32&amp;F33&amp;F34&amp;F35&amp;F36&amp;F37&amp;F38&amp;F39&amp;F40&amp;F41&amp;F42&amp;F43&amp;F44&amp;F45&amp;F46&amp;F47&amp;F48&amp;F49&amp;F50&amp;F51&amp;F52&amp;F53&amp;F54&amp;F55&amp;F56&amp;F57&amp;F58&amp;F59&amp;F60&amp;F61&amp;F62&amp;F63&amp;F64&amp;F65&amp;F66&amp;F67&amp;F68&amp;F69&amp;F70&amp;F71&amp;F72&amp;F73&amp;F74&amp;F75&amp;F76&amp;F77&amp;F78&amp;F79&amp;F80&amp;F81&amp;F82&amp;F83&amp;F84&amp;F85&amp;F86&amp;F87&amp;F88&amp;"';"</f>
@@ -25233,15 +25251,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F88"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
-    <col min="1" max="1" width="38.25" customWidth="1"/>
-    <col min="2" max="2" width="21.625" customWidth="1"/>
-    <col min="3" max="3" width="11.375" customWidth="1"/>
-    <col min="5" max="5" width="32.875" customWidth="1"/>
-    <col min="6" max="6" width="26.25" customWidth="1"/>
+    <col min="1" max="1" width="38.21875" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" customWidth="1"/>
+    <col min="5" max="5" width="32.88671875" customWidth="1"/>
+    <col min="6" max="6" width="26.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -25271,7 +25289,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B2" s="27" t="str">
         <f>IF(NOT(ISBLANK(A2)),A2&amp;"\n","")</f>
@@ -25289,14 +25307,14 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B3" s="27" t="str">
         <f t="shared" ref="B3:B66" si="0">IF(NOT(ISBLANK(A3)),A3&amp;"\n","")</f>
         <v xml:space="preserve">  Serial.begin(9600);\n</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D3" s="5" t="str">
         <f>B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88</f>
@@ -25310,7 +25328,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B4" s="27" t="str">
         <f t="shared" si="0"/>
@@ -25321,7 +25339,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="23" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B5" s="27" t="str">
         <f t="shared" si="0"/>
@@ -25335,7 +25353,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B6" s="27" t="str">
         <f t="shared" si="0"/>
@@ -25346,7 +25364,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="23" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B7" s="27" t="str">
         <f t="shared" si="0"/>
@@ -25369,7 +25387,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="24" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B9" s="27" t="str">
         <f t="shared" si="0"/>
@@ -25383,7 +25401,7 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="23" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B10" s="27" t="str">
         <f t="shared" si="0"/>
@@ -25394,7 +25412,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="23" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B11" s="27" t="str">
         <f t="shared" si="0"/>
@@ -25408,7 +25426,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B12" s="27" t="str">
         <f t="shared" si="0"/>
@@ -25419,7 +25437,7 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="23" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B13" s="27" t="str">
         <f t="shared" si="0"/>
@@ -25430,7 +25448,7 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="23" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B14" s="27" t="str">
         <f t="shared" si="0"/>
@@ -25983,17 +26001,17 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I88"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
-    <col min="1" max="1" width="38.25" customWidth="1"/>
-    <col min="2" max="2" width="19.25" customWidth="1"/>
+    <col min="1" max="1" width="38.21875" customWidth="1"/>
+    <col min="2" max="2" width="19.21875" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
     <col min="5" max="5" width="1" style="36" customWidth="1"/>
-    <col min="6" max="6" width="32.875" customWidth="1"/>
-    <col min="7" max="7" width="10.5" customWidth="1"/>
-    <col min="8" max="8" width="26.25" customWidth="1"/>
+    <col min="6" max="6" width="32.88671875" customWidth="1"/>
+    <col min="7" max="7" width="10.44140625" customWidth="1"/>
+    <col min="8" max="8" width="26.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -26034,7 +26052,7 @@
       </c>
       <c r="E2" s="35"/>
       <c r="F2" s="14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G2" s="27" t="str">
         <f>IF(NOT(ISBLANK(F2)),F2,"")</f>
@@ -26055,7 +26073,7 @@
         <v/>
       </c>
       <c r="C3" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D3" s="5" t="str">
         <f>B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88</f>
@@ -26068,7 +26086,7 @@
         <v/>
       </c>
       <c r="H3" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I3" s="5" t="str">
         <f>G2&amp;G3&amp;G4&amp;G5&amp;G6&amp;G7&amp;G8&amp;G9&amp;G10&amp;G11&amp;G12&amp;G13&amp;G14&amp;G15&amp;G16&amp;G17&amp;G18&amp;G19&amp;G20&amp;G21&amp;G22&amp;G23&amp;G24&amp;G25&amp;G26&amp;G27&amp;G28&amp;G29&amp;G30&amp;G31&amp;G32&amp;G33&amp;G34&amp;G35&amp;G36&amp;G37&amp;G38&amp;G39&amp;G40&amp;G41&amp;G42&amp;G43&amp;G44&amp;G45&amp;G46&amp;G47&amp;G48&amp;G49&amp;G50&amp;G51&amp;G52&amp;G53&amp;G54&amp;G55&amp;G56&amp;G57&amp;G58&amp;G59&amp;G60&amp;G61&amp;G62&amp;G63&amp;G64&amp;G65&amp;G66&amp;G67&amp;G68&amp;G69&amp;G70&amp;G71&amp;G72&amp;G73&amp;G74&amp;G75&amp;G76&amp;G77&amp;G78&amp;G79&amp;G80&amp;G81&amp;G82&amp;G83&amp;G84&amp;G85&amp;G86&amp;G87&amp;G88</f>
@@ -26087,7 +26105,7 @@
         <v/>
       </c>
       <c r="H4" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I4" s="4" t="str">
         <f>變數!$B$11</f>
@@ -26106,7 +26124,7 @@
         <v/>
       </c>
       <c r="H5" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I5" s="4"/>
     </row>
@@ -26122,7 +26140,7 @@
         <v/>
       </c>
       <c r="H6" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I6" s="4"/>
     </row>
@@ -27135,12 +27153,12 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
-    <col min="1" max="1" width="32.875" customWidth="1"/>
-    <col min="2" max="2" width="26.25" customWidth="1"/>
+    <col min="1" max="1" width="32.88671875" customWidth="1"/>
+    <col min="2" max="2" width="26.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -27271,13 +27289,13 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E88"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
-    <col min="1" max="1" width="64.25" customWidth="1"/>
-    <col min="2" max="2" width="23.75" customWidth="1"/>
-    <col min="4" max="4" width="16.375" customWidth="1"/>
+    <col min="1" max="1" width="64.21875" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -27297,7 +27315,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B2" s="27" t="str">
         <f>IF(NOT(ISBLANK(A2)),A2&amp;"\n","")</f>
@@ -27313,14 +27331,14 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B3" s="27" t="str">
         <f t="shared" ref="B3:B66" si="0">IF(NOT(ISBLANK(A3)),A3&amp;"\n","")</f>
         <v xml:space="preserve">  while (!client.connected()) {\n</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D3" s="5" t="str">
         <f>B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88</f>
@@ -27329,7 +27347,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B4" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27338,7 +27356,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B5" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27347,7 +27365,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B6" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27356,7 +27374,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B7" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27365,7 +27383,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B8" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27374,7 +27392,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="23" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B9" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27383,7 +27401,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B10" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27392,7 +27410,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B11" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27401,7 +27419,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B12" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27410,7 +27428,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B13" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27444,7 +27462,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B17" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27453,7 +27471,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B18" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27462,7 +27480,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="23" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B19" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27471,7 +27489,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B20" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27480,7 +27498,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B21" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27489,7 +27507,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B22" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27498,7 +27516,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B23" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27507,7 +27525,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B24" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27516,7 +27534,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B25" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27525,7 +27543,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B26" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27534,7 +27552,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="23" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B27" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27543,7 +27561,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B28" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27552,7 +27570,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B29" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27561,7 +27579,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B30" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27570,7 +27588,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="23" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B31" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27579,7 +27597,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B32" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27588,7 +27606,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="23" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B33" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27597,7 +27615,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="23" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B34" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27606,7 +27624,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="23" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B35" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27615,7 +27633,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="23" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B36" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27649,7 +27667,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B40" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27658,7 +27676,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B41" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27667,7 +27685,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B42" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27676,7 +27694,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="23" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B43" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27685,7 +27703,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B44" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27701,7 +27719,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B46" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27710,7 +27728,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B47" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27726,7 +27744,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B49" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27735,7 +27753,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B50" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27744,7 +27762,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="23" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B51" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27769,7 +27787,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="23" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B54" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27778,7 +27796,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="23" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B55" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27787,7 +27805,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="23" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B56" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27796,7 +27814,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="23" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B57" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27821,7 +27839,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="23" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B60" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27830,7 +27848,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="23" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B61" s="27" t="str">
         <f t="shared" si="0"/>
@@ -27839,7 +27857,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="23" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B62" s="27" t="str">
         <f t="shared" si="0"/>
@@ -28038,29 +28056,29 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L88"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="6" customWidth="1"/>
-    <col min="3" max="3" width="21.25" style="3" customWidth="1"/>
-    <col min="4" max="4" width="7.625" customWidth="1"/>
-    <col min="5" max="5" width="20.5" style="3" customWidth="1"/>
-    <col min="6" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="7" width="17.75" customWidth="1"/>
-    <col min="8" max="8" width="16.375" customWidth="1"/>
+    <col min="3" max="3" width="21.21875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="6.21875" customWidth="1"/>
+    <col min="7" max="7" width="17.77734375" customWidth="1"/>
+    <col min="8" max="8" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="G1" t="s">
         <v>10</v>
@@ -28072,21 +28090,21 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="23" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B2" s="27" t="str">
         <f>IF(NOT(ISBLANK(A2)),A2&amp;"\n ","")</f>
         <v xml:space="preserve">//接收訊息：Mega→ESP32\n </v>
       </c>
       <c r="C2" s="30" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D2" s="27" t="str">
         <f>IF(NOT(ISBLANK(C2)),C2,"")</f>
         <v>statements_msg</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F2" s="27" t="str">
         <f>IF(NOT(ISBLANK(E2)),E2&amp;"\n ","")</f>
@@ -28102,7 +28120,7 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="23" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B3" s="27" t="str">
         <f t="shared" ref="B3:B66" si="0">IF(NOT(ISBLANK(A3)),A3&amp;"\n ","")</f>
@@ -28121,7 +28139,7 @@
         <v xml:space="preserve">}\n </v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H3" s="5" t="str">
         <f>B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88</f>
@@ -28134,7 +28152,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="23" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B4" s="27" t="str">
         <f t="shared" si="0"/>
@@ -28151,7 +28169,7 @@
         <v/>
       </c>
       <c r="G4" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H4" s="4" t="str">
         <f>D2</f>
@@ -28160,7 +28178,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="23" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B5" s="27" t="str">
         <f t="shared" si="0"/>
@@ -28177,7 +28195,7 @@
         <v/>
       </c>
       <c r="G5" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H5" s="4" t="str">
         <f>F2&amp;F3&amp;F4&amp;F5&amp;F6&amp;F7&amp;F8&amp;F9&amp;F10&amp;F11&amp;F12&amp;F13&amp;F14&amp;F15&amp;F16&amp;F17&amp;F18&amp;F19&amp;F20&amp;F21&amp;F22&amp;F23&amp;F24&amp;F25&amp;F26&amp;F27&amp;F28&amp;F29&amp;F30&amp;F31&amp;F32&amp;F33&amp;F34&amp;F35&amp;F36&amp;F37&amp;F38&amp;F39&amp;F40&amp;F41&amp;F42&amp;F43&amp;F44&amp;F45&amp;F46&amp;F47&amp;F48&amp;F49&amp;F50&amp;F51&amp;F52&amp;F53&amp;F54&amp;F55&amp;F56&amp;F57&amp;F58&amp;F59&amp;F60&amp;F61&amp;F62&amp;F63&amp;F64&amp;F65&amp;F66&amp;F67&amp;F68&amp;F69&amp;F70&amp;F71&amp;F72&amp;F73&amp;F74&amp;F75&amp;F76&amp;F77&amp;F78&amp;F79&amp;F80&amp;F81&amp;F82&amp;F83&amp;F84&amp;F85&amp;F86&amp;F87&amp;F88</f>
@@ -28186,7 +28204,7 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="23" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B6" s="27" t="str">
         <f t="shared" si="0"/>
@@ -29606,29 +29624,29 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L88"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="6" customWidth="1"/>
-    <col min="3" max="3" width="21.25" style="3" customWidth="1"/>
-    <col min="4" max="4" width="7.625" customWidth="1"/>
-    <col min="5" max="5" width="20.5" style="3" customWidth="1"/>
-    <col min="6" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="7" width="17.75" customWidth="1"/>
-    <col min="8" max="8" width="16.375" customWidth="1"/>
+    <col min="3" max="3" width="21.21875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="6.21875" customWidth="1"/>
+    <col min="7" max="7" width="17.77734375" customWidth="1"/>
+    <col min="8" max="8" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="G1" t="s">
         <v>10</v>
@@ -29640,14 +29658,14 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="23" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B2" s="27" t="str">
         <f>IF(NOT(ISBLANK(A2)),A2&amp;"\n ","")</f>
         <v xml:space="preserve">//訂閱的主題回覆\n </v>
       </c>
       <c r="C2" s="30" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D2" s="27" t="str">
         <f>IF(NOT(ISBLANK(C2)),C2,"")</f>
@@ -29670,7 +29688,7 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B3" s="27" t="str">
         <f t="shared" ref="B3:B66" si="0">IF(NOT(ISBLANK(A3)),A3&amp;"\n ","")</f>
@@ -29687,7 +29705,7 @@
         <v/>
       </c>
       <c r="G3" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H3" s="5" t="str">
         <f>B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88</f>
@@ -29700,7 +29718,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="23" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B4" s="27" t="str">
         <f t="shared" si="0"/>
@@ -29717,7 +29735,7 @@
         <v/>
       </c>
       <c r="G4" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H4" s="4" t="str">
         <f>D2</f>
@@ -29726,7 +29744,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B5" s="27" t="str">
         <f t="shared" si="0"/>
@@ -29743,7 +29761,7 @@
         <v/>
       </c>
       <c r="G5" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H5" s="4" t="str">
         <f>F2&amp;F3&amp;F4&amp;F5&amp;F6&amp;F7&amp;F8&amp;F9&amp;F10&amp;F11&amp;F12&amp;F13&amp;F14&amp;F15&amp;F16&amp;F17&amp;F18&amp;F19&amp;F20&amp;F21&amp;F22&amp;F23&amp;F24&amp;F25&amp;F26&amp;F27&amp;F28&amp;F29&amp;F30&amp;F31&amp;F32&amp;F33&amp;F34&amp;F35&amp;F36&amp;F37&amp;F38&amp;F39&amp;F40&amp;F41&amp;F42&amp;F43&amp;F44&amp;F45&amp;F46&amp;F47&amp;F48&amp;F49&amp;F50&amp;F51&amp;F52&amp;F53&amp;F54&amp;F55&amp;F56&amp;F57&amp;F58&amp;F59&amp;F60&amp;F61&amp;F62&amp;F63&amp;F64&amp;F65&amp;F66&amp;F67&amp;F68&amp;F69&amp;F70&amp;F71&amp;F72&amp;F73&amp;F74&amp;F75&amp;F76&amp;F77&amp;F78&amp;F79&amp;F80&amp;F81&amp;F82&amp;F83&amp;F84&amp;F85&amp;F86&amp;F87&amp;F88</f>
@@ -29752,7 +29770,7 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="23" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B6" s="27" t="str">
         <f t="shared" si="0"/>
@@ -29790,7 +29808,7 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B8" s="27" t="str">
         <f t="shared" si="0"/>
@@ -29809,7 +29827,7 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="23" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B9" s="27" t="str">
         <f t="shared" si="0"/>
@@ -29828,7 +29846,7 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="23" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B10" s="27" t="str">
         <f t="shared" si="0"/>
@@ -31180,19 +31198,19 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E88"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
-    <col min="2" max="2" width="23.75" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" customWidth="1"/>
     <col min="4" max="4" width="27" customWidth="1"/>
     <col min="5" max="5" width="42" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C1" s="7" t="str">
         <f>"var code ='"&amp;B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88&amp;"';"</f>
@@ -31208,7 +31226,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="23" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B2" s="27" t="str">
         <f>IF(NOT(ISBLANK(A2)),A2&amp;"\n","")</f>
@@ -31219,7 +31237,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="23" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B3" s="27" t="str">
         <f t="shared" ref="B3:B66" si="0">IF(NOT(ISBLANK(A3)),A3&amp;"\n","")</f>
@@ -31239,7 +31257,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="24" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B5" s="27" t="str">
         <f t="shared" si="0"/>
@@ -31250,7 +31268,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="23" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B6" s="27" t="str">
         <f t="shared" si="0"/>

--- a/tools/myCustomBlockly/製作積木教學/iMi/完整ino程式依積木分割/ESP32Car/ESP32Car3產生積木程式碼.xlsx
+++ b/tools/myCustomBlockly/製作積木教學/iMi/完整ino程式依積木分割/ESP32Car/ESP32Car3產生積木程式碼.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\maker\ArduinoMaster\tools\myCustomBlockly\製作積木教學\iMi\完整ino程式依積木分割\ESP32Car\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0862E62-327E-4CDE-92CD-89FFC777BD40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D79C893-1662-4672-9DD2-9601CAF158ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" tabRatio="737" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" tabRatio="737" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="變數" sheetId="5" r:id="rId1"/>
-    <sheet name="S" sheetId="2" r:id="rId2"/>
-    <sheet name="S(變)" sheetId="7" r:id="rId3"/>
-    <sheet name="F" sheetId="4" r:id="rId4"/>
-    <sheet name="c" sheetId="19" r:id="rId5"/>
-    <sheet name="01D" sheetId="1" r:id="rId6"/>
+    <sheet name="S(變)" sheetId="7" r:id="rId2"/>
+    <sheet name="c" sheetId="19" r:id="rId3"/>
+    <sheet name="01D" sheetId="1" r:id="rId4"/>
+    <sheet name="01S" sheetId="2" r:id="rId5"/>
+    <sheet name="01F" sheetId="4" r:id="rId6"/>
     <sheet name="02-05c" sheetId="27" r:id="rId7"/>
     <sheet name="06L" sheetId="12" r:id="rId8"/>
     <sheet name="07F" sheetId="13" r:id="rId9"/>
@@ -35,7 +35,8 @@
     <sheet name="18c" sheetId="26" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'01D'!$A$2:$P$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'01D'!$A$2:$P$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'01S'!$A$2:$K$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'02-05c'!$D$1:$E$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'06L'!$D$1:$E$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'08S'!$A$2:$M$3</definedName>
@@ -48,9 +49,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'16c'!$D$1:$E$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'17c'!$D$1:$E$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'18c'!$D$1:$E$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'c'!$D$1:$E$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">S!$A$2:$K$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'S(變)'!$A$2:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'c'!$D$1:$E$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'S(變)'!$A$2:$G$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -76,7 +76,7 @@
     <author>AMANI</author>
   </authors>
   <commentList>
-    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
       <text>
         <r>
           <rPr>
@@ -101,7 +101,7 @@
     <author>AMANI</author>
   </authors>
   <commentList>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
+    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -126,7 +126,7 @@
     <author>AMANI</author>
   </authors>
   <commentList>
-    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -365,9 +365,6 @@
     <t>const char* TOPIC_CAR_GPS = "imiRobot/car/gps";</t>
   </si>
   <si>
-    <t>const char* TOPIC_GOODS_LOAD = "imiRobot/goods/load";</t>
-  </si>
-  <si>
     <t>const char* TOPIC_CAR_LOWPOWER = "imiRobot/car/lowPower";</t>
   </si>
   <si>
@@ -602,9 +599,6 @@
   </si>
   <si>
     <t xml:space="preserve">  myMsg.replace("§", "&amp;");</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  myMsg.replace("\\n", "\n");</t>
   </si>
   <si>
     <t xml:space="preserve">  if (line_client.connect("notify-api.line.me", 443)) {</t>
@@ -2017,18 +2011,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">value_uart </t>
-  </si>
-  <si>
-    <t xml:space="preserve">value_wifi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">value_line </t>
-  </si>
-  <si>
-    <t xml:space="preserve">value_mqtt </t>
-  </si>
-  <si>
     <t>嵌入區塊</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2401,62 +2383,6 @@
   </si>
   <si>
     <t>刪除最後面+號</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>01imi_esp32car_init</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>06imi_esp32car_loop</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>07imi_esp32car_getArduino_func</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>08imi_esp32car_submqtt</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>09imi_esp32car_mqttcallback_func</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10imi_esp32car_ismqtttopic</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>11imi_esp32car_sendarduino_mapset</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>12imi_esp32car_pubmqtt_carstandby</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>13imi_esp32car_sendarduino_goodsload</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>14imi_esp32car_isarduinomsg</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>15imi_esp32car_getarduino_recipient</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>16imi_esp32car_line_recipient</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>17imi_esp32car_getarduino_gps</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>18imi_esp32car_pubmqtt_cargps</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2983,6 +2909,72 @@
       </rPr>
       <t>'</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">  myMsg.replace("\\\\n", "\\n");</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>const char* TOPIC_GOODS_LOAD = "imiRobot/goods/load";</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">statements_uart </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">statements_wifi </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">statements_line </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">statements_mqtt </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>_01imi_esp32car_init</t>
+  </si>
+  <si>
+    <t>_06imi_esp32car_loop</t>
+  </si>
+  <si>
+    <t>_07imi_esp32car_getArduino_func</t>
+  </si>
+  <si>
+    <t>_08imi_esp32car_submqtt</t>
+  </si>
+  <si>
+    <t>_09imi_esp32car_mqttcallback_func</t>
+  </si>
+  <si>
+    <t>_10imi_esp32car_ismqtttopic</t>
+  </si>
+  <si>
+    <t>_11imi_esp32car_sendarduino_mapset</t>
+  </si>
+  <si>
+    <t>_12imi_esp32car_pubmqtt_carstandby</t>
+  </si>
+  <si>
+    <t>_13imi_esp32car_sendarduino_goodsload</t>
+  </si>
+  <si>
+    <t>_14imi_esp32car_isarduinomsg</t>
+  </si>
+  <si>
+    <t>_15imi_esp32car_getarduino_recipient</t>
+  </si>
+  <si>
+    <t>_16imi_esp32car_line_recipient</t>
+  </si>
+  <si>
+    <t>_17imi_esp32car_getarduino_gps</t>
+  </si>
+  <si>
+    <t>_18imi_esp32car_pubmqtt_cargps</t>
   </si>
 </sst>
 </file>
@@ -11608,122 +11600,122 @@
         <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.25" thickBot="1">
       <c r="A2" s="17" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B2" s="20" t="s">
         <v>19</v>
       </c>
       <c r="C2" s="42" t="s">
-        <v>208</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1">
       <c r="A3" s="28" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B3" s="20" t="s">
         <v>20</v>
       </c>
       <c r="C3" s="42" t="s">
-        <v>209</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="28" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>21</v>
       </c>
       <c r="C4" s="42" t="s">
-        <v>210</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.25" thickBot="1">
       <c r="A5" s="28" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>211</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.25" thickBot="1">
       <c r="A6" s="28" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="28" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="28" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="28" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="28" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="28" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="28" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="28" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="28" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="28" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -11756,7 +11748,7 @@
       </c>
       <c r="D1" s="8" t="str">
         <f>"Blockly.Arduino.setups_['"&amp;D2&amp;"'] = '"&amp;D3&amp;"';"</f>
-        <v>Blockly.Arduino.setups_['08imi_esp32car_submqtt'] = '';</v>
+        <v>Blockly.Arduino.setups_['_08imi_esp32car_submqtt'] = '';</v>
       </c>
       <c r="E1" s="34"/>
       <c r="F1" t="s">
@@ -11767,7 +11759,7 @@
       </c>
       <c r="I1" s="8" t="str">
         <f>"Blockly.Arduino.setups_['"&amp;I2&amp;"'+"&amp;I4&amp;"] = "&amp;I3&amp;";"</f>
-        <v>Blockly.Arduino.setups_['08imi_esp32car_submqtt'+dropdown_mqtt_topic] = 'client.subscribe('+dropdown_mqtt_topic+');\n';</v>
+        <v>Blockly.Arduino.setups_['_08imi_esp32car_submqtt'+dropdown_mqtt_topic] = 'client.subscribe('+dropdown_mqtt_topic+');\n';</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -11781,11 +11773,11 @@
       </c>
       <c r="D2" s="5" t="str">
         <f>變數!$A$5</f>
-        <v>08imi_esp32car_submqtt</v>
+        <v>_08imi_esp32car_submqtt</v>
       </c>
       <c r="E2" s="35"/>
       <c r="F2" s="14" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="G2" s="27" t="str">
         <f>IF(NOT(ISBLANK(F2)),F2,"")</f>
@@ -11796,7 +11788,7 @@
       </c>
       <c r="I2" s="5" t="str">
         <f>變數!$A$5</f>
-        <v>08imi_esp32car_submqtt</v>
+        <v>_08imi_esp32car_submqtt</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -11806,7 +11798,7 @@
         <v/>
       </c>
       <c r="C3" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D3" s="5" t="str">
         <f>B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88</f>
@@ -11819,7 +11811,7 @@
         <v/>
       </c>
       <c r="H3" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="I3" s="5" t="str">
         <f>G2&amp;G3&amp;G4&amp;G5&amp;G6&amp;G7&amp;G8&amp;G9&amp;G10&amp;G11&amp;G12&amp;G13&amp;G14&amp;G15&amp;G16&amp;G17&amp;G18&amp;G19&amp;G20&amp;G21&amp;G22&amp;G23&amp;G24&amp;G25&amp;G26&amp;G27&amp;G28&amp;G29&amp;G30&amp;G31&amp;G32&amp;G33&amp;G34&amp;G35&amp;G36&amp;G37&amp;G38&amp;G39&amp;G40&amp;G41&amp;G42&amp;G43&amp;G44&amp;G45&amp;G46&amp;G47&amp;G48&amp;G49&amp;G50&amp;G51&amp;G52&amp;G53&amp;G54&amp;G55&amp;G56&amp;G57&amp;G58&amp;G59&amp;G60&amp;G61&amp;G62&amp;G63&amp;G64&amp;G65&amp;G66&amp;G67&amp;G68&amp;G69&amp;G70&amp;G71&amp;G72&amp;G73&amp;G74&amp;G75&amp;G76&amp;G77&amp;G78&amp;G79&amp;G80&amp;G81&amp;G82&amp;G83&amp;G84&amp;G85&amp;G86&amp;G87&amp;G88</f>
@@ -11838,7 +11830,7 @@
         <v/>
       </c>
       <c r="H4" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I4" s="4" t="str">
         <f>變數!$B$11</f>
@@ -11857,7 +11849,7 @@
         <v/>
       </c>
       <c r="H5" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I5" s="4"/>
     </row>
@@ -11873,7 +11865,7 @@
         <v/>
       </c>
       <c r="H6" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I6" s="4"/>
     </row>
@@ -12902,32 +12894,32 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="E1" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G1" t="s">
         <v>10</v>
       </c>
       <c r="H1" s="8" t="str">
         <f>"Blockly.Arduino.functions_['"&amp;H2&amp;"'] = '"&amp;H3&amp;"' + "&amp;H4&amp;" + '"&amp;H5&amp;"';"</f>
-        <v>Blockly.Arduino.functions_['09imi_esp32car_mqttcallback_func'] = '//訂閱的主題回覆\n void callback(char* topic, byte* payload, unsigned int length) {\n   mqttGetMsg = "";\n   for (int i = 0; i &lt; length; i++) {\n     mqttGetMsg += (char)payload[i];\n   }\n   mqttGetMsg.trim();\n   Serial.println(String(topic));\n   Serial.println(mqttGetMsg);\n ' + statements_msg + '}\n ';</v>
+        <v>Blockly.Arduino.functions_['_09imi_esp32car_mqttcallback_func'] = '//訂閱的主題回覆\n void callback(char* topic, byte* payload, unsigned int length) {\n   mqttGetMsg = "";\n   for (int i = 0; i &lt; length; i++) {\n     mqttGetMsg += (char)payload[i];\n   }\n   mqttGetMsg.trim();\n   Serial.println(String(topic));\n   Serial.println(mqttGetMsg);\n ' + statements_msg + '}\n ';</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="23" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B2" s="27" t="str">
         <f>IF(NOT(ISBLANK(A2)),A2&amp;"\n ","")</f>
         <v xml:space="preserve">//訂閱的主題回覆\n </v>
       </c>
       <c r="C2" s="30" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D2" s="27" t="str">
         <f>IF(NOT(ISBLANK(C2)),C2,"")</f>
@@ -12945,12 +12937,12 @@
       </c>
       <c r="H2" s="5" t="str">
         <f>變數!$A$6</f>
-        <v>09imi_esp32car_mqttcallback_func</v>
+        <v>_09imi_esp32car_mqttcallback_func</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="23" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B3" s="27" t="str">
         <f t="shared" ref="B3:B66" si="0">IF(NOT(ISBLANK(A3)),A3&amp;"\n ","")</f>
@@ -12967,7 +12959,7 @@
         <v/>
       </c>
       <c r="G3" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H3" s="5" t="str">
         <f>B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88</f>
@@ -12980,7 +12972,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="23" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B4" s="27" t="str">
         <f t="shared" si="0"/>
@@ -12997,7 +12989,7 @@
         <v/>
       </c>
       <c r="G4" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H4" s="4" t="str">
         <f>D2</f>
@@ -13006,7 +12998,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="23" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B5" s="27" t="str">
         <f t="shared" si="0"/>
@@ -13023,7 +13015,7 @@
         <v/>
       </c>
       <c r="G5" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H5" s="4" t="str">
         <f>F2&amp;F3&amp;F4&amp;F5&amp;F6&amp;F7&amp;F8&amp;F9&amp;F10&amp;F11&amp;F12&amp;F13&amp;F14&amp;F15&amp;F16&amp;F17&amp;F18&amp;F19&amp;F20&amp;F21&amp;F22&amp;F23&amp;F24&amp;F25&amp;F26&amp;F27&amp;F28&amp;F29&amp;F30&amp;F31&amp;F32&amp;F33&amp;F34&amp;F35&amp;F36&amp;F37&amp;F38&amp;F39&amp;F40&amp;F41&amp;F42&amp;F43&amp;F44&amp;F45&amp;F46&amp;F47&amp;F48&amp;F49&amp;F50&amp;F51&amp;F52&amp;F53&amp;F54&amp;F55&amp;F56&amp;F57&amp;F58&amp;F59&amp;F60&amp;F61&amp;F62&amp;F63&amp;F64&amp;F65&amp;F66&amp;F67&amp;F68&amp;F69&amp;F70&amp;F71&amp;F72&amp;F73&amp;F74&amp;F75&amp;F76&amp;F77&amp;F78&amp;F79&amp;F80&amp;F81&amp;F82&amp;F83&amp;F84&amp;F85&amp;F86&amp;F87&amp;F88</f>
@@ -13032,7 +13024,7 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="23" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B6" s="27" t="str">
         <f t="shared" si="0"/>
@@ -13070,7 +13062,7 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="23" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B8" s="27" t="str">
         <f t="shared" si="0"/>
@@ -13089,7 +13081,7 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="23" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B9" s="27" t="str">
         <f t="shared" si="0"/>
@@ -13108,7 +13100,7 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="23" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B10" s="27" t="str">
         <f t="shared" si="0"/>
@@ -14473,23 +14465,23 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C1" s="7" t="str">
         <f>"var code ="&amp;B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88&amp;";"</f>
         <v>var code ='String(topic) ==' +dropdown_mqtt_topic;</v>
       </c>
       <c r="D1" s="38" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1" t="s">
         <v>168</v>
-      </c>
-      <c r="F1" t="s">
-        <v>170</v>
       </c>
       <c r="G1" s="7" t="str">
         <f>"var code ='"&amp;F2&amp;F3&amp;F4&amp;F5&amp;F6&amp;F7&amp;F8&amp;F9&amp;F10&amp;F11&amp;F12&amp;F13&amp;F14&amp;F15&amp;F16&amp;F17&amp;F18&amp;F19&amp;F20&amp;F21&amp;F22&amp;F23&amp;F24&amp;F25&amp;F26&amp;F27&amp;F28&amp;F29&amp;F30&amp;F31&amp;F32&amp;F33&amp;F34&amp;F35&amp;F36&amp;F37&amp;F38&amp;F39&amp;F40&amp;F41&amp;F42&amp;F43&amp;F44&amp;F45&amp;F46&amp;F47&amp;F48&amp;F49&amp;F50&amp;F51&amp;F52&amp;F53&amp;F54&amp;F55&amp;F56&amp;F57&amp;F58&amp;F59&amp;F60&amp;F61&amp;F62&amp;F63&amp;F64&amp;F65&amp;F66&amp;F67&amp;F68&amp;F69&amp;F70&amp;F71&amp;F72&amp;F73&amp;F74&amp;F75&amp;F76&amp;F77&amp;F78&amp;F79&amp;F80&amp;F81&amp;F82&amp;F83&amp;F84&amp;F85&amp;F86&amp;F87&amp;F88&amp;"';"</f>
@@ -14498,7 +14490,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="14" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B2" s="27" t="str">
         <f>IF(NOT(ISBLANK(A2)),A2,"")</f>
@@ -15577,23 +15569,23 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C1" s="7" t="str">
         <f>"var code ="&amp;B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88&amp;";"</f>
         <v>var code =;</v>
       </c>
       <c r="D1" s="38" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1" t="s">
         <v>168</v>
-      </c>
-      <c r="F1" t="s">
-        <v>170</v>
       </c>
       <c r="G1" s="7" t="str">
         <f>"var code ='"&amp;F2&amp;F3&amp;F4&amp;F5&amp;F6&amp;F7&amp;F8&amp;F9&amp;F10&amp;F11&amp;F12&amp;F13&amp;F14&amp;F15&amp;F16&amp;F17&amp;F18&amp;F19&amp;F20&amp;F21&amp;F22&amp;F23&amp;F24&amp;F25&amp;F26&amp;F27&amp;F28&amp;F29&amp;F30&amp;F31&amp;F32&amp;F33&amp;F34&amp;F35&amp;F36&amp;F37&amp;F38&amp;F39&amp;F40&amp;F41&amp;F42&amp;F43&amp;F44&amp;F45&amp;F46&amp;F47&amp;F48&amp;F49&amp;F50&amp;F51&amp;F52&amp;F53&amp;F54&amp;F55&amp;F56&amp;F57&amp;F58&amp;F59&amp;F60&amp;F61&amp;F62&amp;F63&amp;F64&amp;F65&amp;F66&amp;F67&amp;F68&amp;F69&amp;F70&amp;F71&amp;F72&amp;F73&amp;F74&amp;F75&amp;F76&amp;F77&amp;F78&amp;F79&amp;F80&amp;F81&amp;F82&amp;F83&amp;F84&amp;F85&amp;F86&amp;F87&amp;F88&amp;"';"</f>
@@ -15608,7 +15600,7 @@
       </c>
       <c r="D2" s="39"/>
       <c r="E2" s="24" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F2" s="27" t="str">
         <f>IF(NOT(ISBLANK(E2)),E2&amp;"\n ","")</f>
@@ -15623,7 +15615,7 @@
       </c>
       <c r="D3" s="40"/>
       <c r="E3" s="24" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F3" s="27" t="str">
         <f t="shared" ref="F3:F66" si="1">IF(NOT(ISBLANK(E3)),E3&amp;"\n ","")</f>
@@ -15638,7 +15630,7 @@
       </c>
       <c r="D4" s="39"/>
       <c r="E4" s="24" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F4" s="27" t="str">
         <f t="shared" si="1"/>
@@ -16685,23 +16677,23 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C1" s="7" t="str">
         <f>"var code ="&amp;B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88&amp;";"</f>
         <v>var code =;</v>
       </c>
       <c r="D1" s="38" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1" t="s">
         <v>168</v>
-      </c>
-      <c r="F1" t="s">
-        <v>170</v>
       </c>
       <c r="G1" s="7" t="str">
         <f>"var code ='"&amp;F2&amp;F3&amp;F4&amp;F5&amp;F6&amp;F7&amp;F8&amp;F9&amp;F10&amp;F11&amp;F12&amp;F13&amp;F14&amp;F15&amp;F16&amp;F17&amp;F18&amp;F19&amp;F20&amp;F21&amp;F22&amp;F23&amp;F24&amp;F25&amp;F26&amp;F27&amp;F28&amp;F29&amp;F30&amp;F31&amp;F32&amp;F33&amp;F34&amp;F35&amp;F36&amp;F37&amp;F38&amp;F39&amp;F40&amp;F41&amp;F42&amp;F43&amp;F44&amp;F45&amp;F46&amp;F47&amp;F48&amp;F49&amp;F50&amp;F51&amp;F52&amp;F53&amp;F54&amp;F55&amp;F56&amp;F57&amp;F58&amp;F59&amp;F60&amp;F61&amp;F62&amp;F63&amp;F64&amp;F65&amp;F66&amp;F67&amp;F68&amp;F69&amp;F70&amp;F71&amp;F72&amp;F73&amp;F74&amp;F75&amp;F76&amp;F77&amp;F78&amp;F79&amp;F80&amp;F81&amp;F82&amp;F83&amp;F84&amp;F85&amp;F86&amp;F87&amp;F88&amp;"';"</f>
@@ -16716,7 +16708,7 @@
       </c>
       <c r="D2" s="39"/>
       <c r="E2" s="24" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F2" s="27" t="str">
         <f>IF(NOT(ISBLANK(E2)),E2&amp;"\n ","")</f>
@@ -16731,7 +16723,7 @@
       </c>
       <c r="D3" s="40"/>
       <c r="E3" s="24" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F3" s="27" t="str">
         <f t="shared" ref="F3:F66" si="1">IF(NOT(ISBLANK(E3)),E3&amp;"\n ","")</f>
@@ -16746,7 +16738,7 @@
       </c>
       <c r="D4" s="39"/>
       <c r="E4" s="24" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F4" s="27" t="str">
         <f t="shared" si="1"/>
@@ -17793,23 +17785,23 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C1" s="7" t="str">
         <f>"var code ="&amp;B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88&amp;";"</f>
         <v>var code =;</v>
       </c>
       <c r="D1" s="38" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1" t="s">
         <v>168</v>
-      </c>
-      <c r="F1" t="s">
-        <v>170</v>
       </c>
       <c r="G1" s="7" t="str">
         <f>"var code ='"&amp;F2&amp;F3&amp;F4&amp;F5&amp;F6&amp;F7&amp;F8&amp;F9&amp;F10&amp;F11&amp;F12&amp;F13&amp;F14&amp;F15&amp;F16&amp;F17&amp;F18&amp;F19&amp;F20&amp;F21&amp;F22&amp;F23&amp;F24&amp;F25&amp;F26&amp;F27&amp;F28&amp;F29&amp;F30&amp;F31&amp;F32&amp;F33&amp;F34&amp;F35&amp;F36&amp;F37&amp;F38&amp;F39&amp;F40&amp;F41&amp;F42&amp;F43&amp;F44&amp;F45&amp;F46&amp;F47&amp;F48&amp;F49&amp;F50&amp;F51&amp;F52&amp;F53&amp;F54&amp;F55&amp;F56&amp;F57&amp;F58&amp;F59&amp;F60&amp;F61&amp;F62&amp;F63&amp;F64&amp;F65&amp;F66&amp;F67&amp;F68&amp;F69&amp;F70&amp;F71&amp;F72&amp;F73&amp;F74&amp;F75&amp;F76&amp;F77&amp;F78&amp;F79&amp;F80&amp;F81&amp;F82&amp;F83&amp;F84&amp;F85&amp;F86&amp;F87&amp;F88&amp;"';"</f>
@@ -17824,7 +17816,7 @@
       </c>
       <c r="D2" s="39"/>
       <c r="E2" s="24" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F2" s="27" t="str">
         <f>IF(NOT(ISBLANK(E2)),E2&amp;"\n ","")</f>
@@ -17839,7 +17831,7 @@
       </c>
       <c r="D3" s="40"/>
       <c r="E3" s="24" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F3" s="27" t="str">
         <f t="shared" ref="F3:F66" si="1">IF(NOT(ISBLANK(E3)),E3&amp;"\n ","")</f>
@@ -18899,23 +18891,23 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C1" s="7" t="str">
         <f>"var code ="&amp;B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88&amp;";"</f>
         <v>var code ='str.indexOf('+dropdown_uart_topic+') != -1';</v>
       </c>
       <c r="D1" s="38" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1" t="s">
         <v>168</v>
-      </c>
-      <c r="F1" t="s">
-        <v>170</v>
       </c>
       <c r="G1" s="7" t="str">
         <f>"var code ='"&amp;F2&amp;F3&amp;F4&amp;F5&amp;F6&amp;F7&amp;F8&amp;F9&amp;F10&amp;F11&amp;F12&amp;F13&amp;F14&amp;F15&amp;F16&amp;F17&amp;F18&amp;F19&amp;F20&amp;F21&amp;F22&amp;F23&amp;F24&amp;F25&amp;F26&amp;F27&amp;F28&amp;F29&amp;F30&amp;F31&amp;F32&amp;F33&amp;F34&amp;F35&amp;F36&amp;F37&amp;F38&amp;F39&amp;F40&amp;F41&amp;F42&amp;F43&amp;F44&amp;F45&amp;F46&amp;F47&amp;F48&amp;F49&amp;F50&amp;F51&amp;F52&amp;F53&amp;F54&amp;F55&amp;F56&amp;F57&amp;F58&amp;F59&amp;F60&amp;F61&amp;F62&amp;F63&amp;F64&amp;F65&amp;F66&amp;F67&amp;F68&amp;F69&amp;F70&amp;F71&amp;F72&amp;F73&amp;F74&amp;F75&amp;F76&amp;F77&amp;F78&amp;F79&amp;F80&amp;F81&amp;F82&amp;F83&amp;F84&amp;F85&amp;F86&amp;F87&amp;F88&amp;"';"</f>
@@ -18924,7 +18916,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="14" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B2" s="27" t="str">
         <f>IF(NOT(ISBLANK(A2)),A2,"")</f>
@@ -20003,23 +19995,23 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C1" s="7" t="str">
         <f>"var code ="&amp;B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88&amp;";"</f>
         <v>var code =;</v>
       </c>
       <c r="D1" s="38" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1" t="s">
         <v>168</v>
-      </c>
-      <c r="F1" t="s">
-        <v>170</v>
       </c>
       <c r="G1" s="7" t="str">
         <f>"var code ='"&amp;F2&amp;F3&amp;F4&amp;F5&amp;F6&amp;F7&amp;F8&amp;F9&amp;F10&amp;F11&amp;F12&amp;F13&amp;F14&amp;F15&amp;F16&amp;F17&amp;F18&amp;F19&amp;F20&amp;F21&amp;F22&amp;F23&amp;F24&amp;F25&amp;F26&amp;F27&amp;F28&amp;F29&amp;F30&amp;F31&amp;F32&amp;F33&amp;F34&amp;F35&amp;F36&amp;F37&amp;F38&amp;F39&amp;F40&amp;F41&amp;F42&amp;F43&amp;F44&amp;F45&amp;F46&amp;F47&amp;F48&amp;F49&amp;F50&amp;F51&amp;F52&amp;F53&amp;F54&amp;F55&amp;F56&amp;F57&amp;F58&amp;F59&amp;F60&amp;F61&amp;F62&amp;F63&amp;F64&amp;F65&amp;F66&amp;F67&amp;F68&amp;F69&amp;F70&amp;F71&amp;F72&amp;F73&amp;F74&amp;F75&amp;F76&amp;F77&amp;F78&amp;F79&amp;F80&amp;F81&amp;F82&amp;F83&amp;F84&amp;F85&amp;F86&amp;F87&amp;F88&amp;"';"</f>
@@ -20034,7 +20026,7 @@
       </c>
       <c r="D2" s="39"/>
       <c r="E2" s="24" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F2" s="27" t="str">
         <f>IF(NOT(ISBLANK(E2)),E2&amp;"\n ","")</f>
@@ -20049,7 +20041,7 @@
       </c>
       <c r="D3" s="40"/>
       <c r="E3" s="24" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F3" s="27" t="str">
         <f t="shared" ref="F3:F66" si="1">IF(NOT(ISBLANK(E3)),E3&amp;"\n ","")</f>
@@ -20064,7 +20056,7 @@
       </c>
       <c r="D4" s="39"/>
       <c r="E4" s="24" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F4" s="27" t="str">
         <f t="shared" si="1"/>
@@ -20079,7 +20071,7 @@
       </c>
       <c r="D5" s="40"/>
       <c r="E5" s="24" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F5" s="27" t="str">
         <f t="shared" si="1"/>
@@ -20094,7 +20086,7 @@
       </c>
       <c r="D6" s="40"/>
       <c r="E6" s="24" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F6" s="27" t="str">
         <f t="shared" si="1"/>
@@ -20109,7 +20101,7 @@
       </c>
       <c r="D7" s="40"/>
       <c r="E7" s="24" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F7" s="27" t="str">
         <f t="shared" si="1"/>
@@ -20124,7 +20116,7 @@
       </c>
       <c r="D8" s="40"/>
       <c r="E8" s="24" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F8" s="27" t="str">
         <f t="shared" si="1"/>
@@ -20139,7 +20131,7 @@
       </c>
       <c r="D9" s="40"/>
       <c r="E9" s="24" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F9" s="27" t="str">
         <f t="shared" si="1"/>
@@ -20154,7 +20146,7 @@
       </c>
       <c r="D10" s="40"/>
       <c r="E10" s="24" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F10" s="27" t="str">
         <f t="shared" si="1"/>
@@ -21123,23 +21115,23 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C1" s="7" t="str">
         <f>"var code ="&amp;B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88&amp;";"</f>
         <v>var code =;</v>
       </c>
       <c r="D1" s="38" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1" t="s">
         <v>168</v>
-      </c>
-      <c r="F1" t="s">
-        <v>170</v>
       </c>
       <c r="G1" s="7" t="str">
         <f>"var code ='"&amp;F2&amp;F3&amp;F4&amp;F5&amp;F6&amp;F7&amp;F8&amp;F9&amp;F10&amp;F11&amp;F12&amp;F13&amp;F14&amp;F15&amp;F16&amp;F17&amp;F18&amp;F19&amp;F20&amp;F21&amp;F22&amp;F23&amp;F24&amp;F25&amp;F26&amp;F27&amp;F28&amp;F29&amp;F30&amp;F31&amp;F32&amp;F33&amp;F34&amp;F35&amp;F36&amp;F37&amp;F38&amp;F39&amp;F40&amp;F41&amp;F42&amp;F43&amp;F44&amp;F45&amp;F46&amp;F47&amp;F48&amp;F49&amp;F50&amp;F51&amp;F52&amp;F53&amp;F54&amp;F55&amp;F56&amp;F57&amp;F58&amp;F59&amp;F60&amp;F61&amp;F62&amp;F63&amp;F64&amp;F65&amp;F66&amp;F67&amp;F68&amp;F69&amp;F70&amp;F71&amp;F72&amp;F73&amp;F74&amp;F75&amp;F76&amp;F77&amp;F78&amp;F79&amp;F80&amp;F81&amp;F82&amp;F83&amp;F84&amp;F85&amp;F86&amp;F87&amp;F88&amp;"';"</f>
@@ -21154,7 +21146,7 @@
       </c>
       <c r="D2" s="39"/>
       <c r="E2" s="24" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F2" s="27" t="str">
         <f>IF(NOT(ISBLANK(E2)),E2&amp;"\n ","")</f>
@@ -21169,7 +21161,7 @@
       </c>
       <c r="D3" s="40"/>
       <c r="E3" s="24" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F3" s="27" t="str">
         <f t="shared" ref="F3:F66" si="1">IF(NOT(ISBLANK(E3)),E3&amp;"\n ","")</f>
@@ -22229,23 +22221,23 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C1" s="7" t="str">
         <f>"var code ="&amp;B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88&amp;";"</f>
         <v>var code =;</v>
       </c>
       <c r="D1" s="38" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1" t="s">
         <v>168</v>
-      </c>
-      <c r="F1" t="s">
-        <v>170</v>
       </c>
       <c r="G1" s="7" t="str">
         <f>"var code ='"&amp;F2&amp;F3&amp;F4&amp;F5&amp;F6&amp;F7&amp;F8&amp;F9&amp;F10&amp;F11&amp;F12&amp;F13&amp;F14&amp;F15&amp;F16&amp;F17&amp;F18&amp;F19&amp;F20&amp;F21&amp;F22&amp;F23&amp;F24&amp;F25&amp;F26&amp;F27&amp;F28&amp;F29&amp;F30&amp;F31&amp;F32&amp;F33&amp;F34&amp;F35&amp;F36&amp;F37&amp;F38&amp;F39&amp;F40&amp;F41&amp;F42&amp;F43&amp;F44&amp;F45&amp;F46&amp;F47&amp;F48&amp;F49&amp;F50&amp;F51&amp;F52&amp;F53&amp;F54&amp;F55&amp;F56&amp;F57&amp;F58&amp;F59&amp;F60&amp;F61&amp;F62&amp;F63&amp;F64&amp;F65&amp;F66&amp;F67&amp;F68&amp;F69&amp;F70&amp;F71&amp;F72&amp;F73&amp;F74&amp;F75&amp;F76&amp;F77&amp;F78&amp;F79&amp;F80&amp;F81&amp;F82&amp;F83&amp;F84&amp;F85&amp;F86&amp;F87&amp;F88&amp;"';"</f>
@@ -22260,7 +22252,7 @@
       </c>
       <c r="D2" s="39"/>
       <c r="E2" s="24" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F2" s="27" t="str">
         <f>IF(NOT(ISBLANK(E2)),E2&amp;"\n ","")</f>
@@ -22275,7 +22267,7 @@
       </c>
       <c r="D3" s="40"/>
       <c r="E3" s="24" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F3" s="27" t="str">
         <f t="shared" ref="F3:F66" si="1">IF(NOT(ISBLANK(E3)),E3&amp;"\n ","")</f>
@@ -22290,7 +22282,7 @@
       </c>
       <c r="D4" s="39"/>
       <c r="E4" s="24" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F4" s="27" t="str">
         <f t="shared" si="1"/>
@@ -22305,7 +22297,7 @@
       </c>
       <c r="D5" s="40"/>
       <c r="E5" s="24" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F5" s="27" t="str">
         <f t="shared" si="1"/>
@@ -22320,7 +22312,7 @@
       </c>
       <c r="D6" s="40"/>
       <c r="E6" s="24" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F6" s="27" t="str">
         <f t="shared" si="1"/>
@@ -22335,7 +22327,7 @@
       </c>
       <c r="D7" s="40"/>
       <c r="E7" s="24" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F7" s="27" t="str">
         <f t="shared" si="1"/>
@@ -22350,7 +22342,7 @@
       </c>
       <c r="D8" s="40"/>
       <c r="E8" s="24" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F8" s="27" t="str">
         <f t="shared" si="1"/>
@@ -22365,7 +22357,7 @@
       </c>
       <c r="D9" s="40"/>
       <c r="E9" s="24" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F9" s="27" t="str">
         <f t="shared" si="1"/>
@@ -22380,7 +22372,7 @@
       </c>
       <c r="D10" s="40"/>
       <c r="E10" s="24" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F10" s="27" t="str">
         <f t="shared" si="1"/>
@@ -23336,746 +23328,132 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F88"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="38.25" customWidth="1"/>
-    <col min="2" max="2" width="21.625" customWidth="1"/>
-    <col min="3" max="3" width="11.375" customWidth="1"/>
-    <col min="5" max="5" width="32.875" customWidth="1"/>
-    <col min="6" max="6" width="26.25" customWidth="1"/>
+    <col min="1" max="1" width="32.875" customWidth="1"/>
+    <col min="2" max="2" width="26.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="8" t="str">
-        <f>"Blockly.Arduino.setups_['"&amp;D2&amp;"'] = '"&amp;D3&amp;"';"</f>
-        <v>Blockly.Arduino.setups_['01imi_esp32car_init'] = '  delay(500);\n  Serial.begin(9600);\n  delay(500);\n  MegaSerial.begin(9600);\n  delay(500);\n  setup_wifi();\n  //MQTT初始\n  espClient.setCACert(root_ca);\n  client.setServer(mqtt_server, mqtt_port);\n  client.setCallback(callback);\n  if (!client.connected()) {\n    reconnect();\n  }\n';</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="7" t="str">
-        <f>"Blockly.Arduino.setups_['"&amp;
-變數!$A$2 &amp;"' + "&amp;
-變數!B2 &amp;" + "&amp;
-變數!B3 &amp;
-"] = "&amp;
-S!F3 &amp; S!F5
+        <v>16</v>
+      </c>
+      <c r="B1" s="7" t="str">
+        <f>"Blockly.Arduino.setups_['"&amp;變數!$A$2&amp;"'] = "&amp;
+'S(變)'!B3 &amp; 'S(變)'!B5
 &amp;";"</f>
-        <v>Blockly.Arduino.setups_['01imi_esp32car_init' + value_rx + value_tx] = ++++++++++++++;</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="24" t="s">
-        <v>106</v>
-      </c>
-      <c r="B2" s="27" t="str">
-        <f>IF(NOT(ISBLANK(A2)),A2&amp;"\n","")</f>
-        <v xml:space="preserve">  delay(500);\n</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="5" t="str">
-        <f>變數!$A$2</f>
-        <v>01imi_esp32car_init</v>
-      </c>
-      <c r="E2" s="14"/>
-      <c r="F2" s="11"/>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="B3" s="27" t="str">
-        <f t="shared" ref="B3:B66" si="0">IF(NOT(ISBLANK(A3)),A3&amp;"\n","")</f>
-        <v xml:space="preserve">  Serial.begin(9600);\n</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="D3" s="5" t="str">
-        <f>B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88</f>
-        <v xml:space="preserve">  delay(500);\n  Serial.begin(9600);\n  delay(500);\n  MegaSerial.begin(9600);\n  delay(500);\n  setup_wifi();\n  //MQTT初始\n  espClient.setCACert(root_ca);\n  client.setServer(mqtt_server, mqtt_port);\n  client.setCallback(callback);\n  if (!client.connected()) {\n    reconnect();\n  }\n</v>
-      </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="12" t="str">
-        <f>F2&amp;"+"&amp;G2&amp;"+"&amp;H2&amp;"+"&amp;I2&amp;"+"&amp;J2&amp;"+"&amp;K2&amp;"+"&amp;L2&amp;"+"&amp;M2</f>
+        <v>Blockly.Arduino.setups_['_01imi_esp32car_init'] = ''pinMode('+value_swpin+', INPUT_PULLUP);\n '++++++++++++;</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="9"/>
+      <c r="B3" s="12" t="str">
+        <f>B2&amp;"+"&amp;C2&amp;"+"&amp;D2&amp;"+"&amp;E2&amp;"+"&amp;F2&amp;"+"&amp;G2&amp;"+"&amp;H2&amp;"+"&amp;I2</f>
+        <v>''pinMode('+value_swpin+', INPUT_PULLUP);\n '+++++</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="18"/>
+      <c r="B4" s="13"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="9"/>
+      <c r="B5" s="12" t="str">
+        <f>B4&amp;"+"&amp;C4&amp;"+"&amp;D4&amp;"+"&amp;E4&amp;"+"&amp;F4&amp;"+"&amp;G4&amp;"+"&amp;H4&amp;"+"&amp;I4</f>
         <v>+++++++</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="B4" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">  delay(500);\n</v>
-      </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="13"/>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="B5" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">  MegaSerial.begin(9600);\n</v>
-      </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="12" t="str">
-        <f>F4&amp;"+"&amp;G4&amp;"+"&amp;H4&amp;"+"&amp;I4&amp;"+"&amp;J4&amp;"+"&amp;K4&amp;"+"&amp;L4&amp;"+"&amp;M4</f>
+    <row r="6" spans="1:4">
+      <c r="A6" s="10"/>
+      <c r="B6" s="9"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="9"/>
+      <c r="B7" s="12" t="str">
+        <f>B6&amp;"+"&amp;C6&amp;"+"&amp;D6&amp;"+"&amp;E6&amp;"+"&amp;F6&amp;"+"&amp;G6&amp;"+"&amp;H6&amp;"+"&amp;I6</f>
         <v>+++++++</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="B6" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">  delay(500);\n</v>
-      </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="9"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="B7" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">  setup_wifi();\n</v>
-      </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="12" t="str">
-        <f>F6&amp;"+"&amp;G6&amp;"+"&amp;H6&amp;"+"&amp;I6&amp;"+"&amp;J6&amp;"+"&amp;K6&amp;"+"&amp;L6&amp;"+"&amp;M6</f>
+    <row r="8" spans="1:4">
+      <c r="A8" s="10"/>
+      <c r="B8" s="9"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="9"/>
+      <c r="B9" s="12" t="str">
+        <f>B8&amp;"+"&amp;C8&amp;"+"&amp;D8&amp;"+"&amp;E8&amp;"+"&amp;F8&amp;"+"&amp;G8&amp;"+"&amp;H8&amp;"+"&amp;I8</f>
         <v>+++++++</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="24"/>
-      <c r="B8" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="9"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="24" t="s">
-        <v>111</v>
-      </c>
-      <c r="B9" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">  //MQTT初始\n</v>
-      </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="12" t="str">
-        <f>F8&amp;"+"&amp;G8&amp;"+"&amp;H8&amp;"+"&amp;I8&amp;"+"&amp;J8&amp;"+"&amp;K8&amp;"+"&amp;L8&amp;"+"&amp;M8</f>
+    <row r="10" spans="1:4">
+      <c r="A10" s="10"/>
+      <c r="B10" s="9"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="9"/>
+      <c r="B11" s="12" t="str">
+        <f>B10&amp;"+"&amp;C10&amp;"+"&amp;D10&amp;"+"&amp;E10&amp;"+"&amp;F10&amp;"+"&amp;G10&amp;"+"&amp;H10&amp;"+"&amp;I10</f>
         <v>+++++++</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="B10" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">  espClient.setCACert(root_ca);\n</v>
-      </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="9"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="B11" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">  client.setServer(mqtt_server, mqtt_port);\n</v>
-      </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="12" t="str">
-        <f>F10&amp;"+"&amp;G10&amp;"+"&amp;H10&amp;"+"&amp;I10&amp;"+"&amp;J10&amp;"+"&amp;K10&amp;"+"&amp;L10&amp;"+"&amp;M10</f>
-        <v>+++++++</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="B12" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">  client.setCallback(callback);\n</v>
-      </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="B13" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">  if (!client.connected()) {\n</v>
-      </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="B14" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    reconnect();\n</v>
-      </c>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">  }\n</v>
-      </c>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3"/>
-      <c r="B16" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="3"/>
-      <c r="B17" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="3"/>
-      <c r="B18" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="3"/>
-      <c r="B19" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="3"/>
-      <c r="B20" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="3"/>
-      <c r="B21" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="3"/>
-      <c r="B22" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E22" s="9"/>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="3"/>
-      <c r="B23" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="3"/>
-      <c r="B24" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="3"/>
-      <c r="B25" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="3"/>
-      <c r="B26" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="3"/>
-      <c r="B27" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="3"/>
-      <c r="B28" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="3"/>
-      <c r="B29" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="3"/>
-      <c r="B30" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="3"/>
-      <c r="B31" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="3"/>
-      <c r="B32" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="3"/>
-      <c r="B33" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="3"/>
-      <c r="B34" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="3"/>
-      <c r="B35" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="3"/>
-      <c r="B36" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="3"/>
-      <c r="B37" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="3"/>
-      <c r="B38" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="3"/>
-      <c r="B39" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="3"/>
-      <c r="B40" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="3"/>
-      <c r="B41" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="3"/>
-      <c r="B42" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="3"/>
-      <c r="B43" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="3"/>
-      <c r="B44" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" s="3"/>
-      <c r="B45" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="3"/>
-      <c r="B46" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" s="3"/>
-      <c r="B47" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" s="3"/>
-      <c r="B48" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" s="3"/>
-      <c r="B49" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" s="3"/>
-      <c r="B50" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" s="3"/>
-      <c r="B51" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" s="3"/>
-      <c r="B52" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" s="3"/>
-      <c r="B53" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="3"/>
-      <c r="B54" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" s="3"/>
-      <c r="B55" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56" s="3"/>
-      <c r="B56" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" s="3"/>
-      <c r="B57" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58" s="3"/>
-      <c r="B58" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59" s="3"/>
-      <c r="B59" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60" s="3"/>
-      <c r="B60" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61" s="3"/>
-      <c r="B61" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62" s="3"/>
-      <c r="B62" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63" s="3"/>
-      <c r="B63" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64" s="3"/>
-      <c r="B64" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="A65" s="3"/>
-      <c r="B65" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
-      <c r="A66" s="3"/>
-      <c r="B66" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
-      <c r="A67" s="3"/>
-      <c r="B67" s="27" t="str">
-        <f t="shared" ref="B67:B88" si="1">IF(NOT(ISBLANK(A67)),A67&amp;"\n","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="A68" s="3"/>
-      <c r="B68" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
-      <c r="A69" s="3"/>
-      <c r="B69" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
-      <c r="A70" s="3"/>
-      <c r="B70" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
-      <c r="A71" s="3"/>
-      <c r="B71" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
-      <c r="A72" s="3"/>
-      <c r="B72" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
-      <c r="A73" s="3"/>
-      <c r="B73" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="74" spans="1:2">
-      <c r="A74" s="3"/>
-      <c r="B74" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="75" spans="1:2">
-      <c r="A75" s="3"/>
-      <c r="B75" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="76" spans="1:2">
-      <c r="A76" s="3"/>
-      <c r="B76" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="77" spans="1:2">
-      <c r="A77" s="3"/>
-      <c r="B77" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="78" spans="1:2">
-      <c r="A78" s="3"/>
-      <c r="B78" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="79" spans="1:2">
-      <c r="A79" s="3"/>
-      <c r="B79" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="80" spans="1:2">
-      <c r="A80" s="3"/>
-      <c r="B80" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="81" spans="1:2">
-      <c r="A81" s="3"/>
-      <c r="B81" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="82" spans="1:2">
-      <c r="A82" s="3"/>
-      <c r="B82" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="83" spans="1:2">
-      <c r="A83" s="3"/>
-      <c r="B83" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="84" spans="1:2">
-      <c r="A84" s="3"/>
-      <c r="B84" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="85" spans="1:2">
-      <c r="A85" s="3"/>
-      <c r="B85" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="86" spans="1:2">
-      <c r="A86" s="3"/>
-      <c r="B86" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="87" spans="1:2">
-      <c r="A87" s="3"/>
-      <c r="B87" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="88" spans="1:2">
-      <c r="A88" s="3"/>
-      <c r="B88" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+    <row r="12" spans="1:4">
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -24099,23 +23477,23 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C1" s="7" t="str">
         <f>"var code ="&amp;B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88&amp;";"</f>
         <v>var code =;</v>
       </c>
       <c r="D1" s="38" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1" t="s">
         <v>168</v>
-      </c>
-      <c r="F1" t="s">
-        <v>170</v>
       </c>
       <c r="G1" s="7" t="str">
         <f>"var code ='"&amp;F2&amp;F3&amp;F4&amp;F5&amp;F6&amp;F7&amp;F8&amp;F9&amp;F10&amp;F11&amp;F12&amp;F13&amp;F14&amp;F15&amp;F16&amp;F17&amp;F18&amp;F19&amp;F20&amp;F21&amp;F22&amp;F23&amp;F24&amp;F25&amp;F26&amp;F27&amp;F28&amp;F29&amp;F30&amp;F31&amp;F32&amp;F33&amp;F34&amp;F35&amp;F36&amp;F37&amp;F38&amp;F39&amp;F40&amp;F41&amp;F42&amp;F43&amp;F44&amp;F45&amp;F46&amp;F47&amp;F48&amp;F49&amp;F50&amp;F51&amp;F52&amp;F53&amp;F54&amp;F55&amp;F56&amp;F57&amp;F58&amp;F59&amp;F60&amp;F61&amp;F62&amp;F63&amp;F64&amp;F65&amp;F66&amp;F67&amp;F68&amp;F69&amp;F70&amp;F71&amp;F72&amp;F73&amp;F74&amp;F75&amp;F76&amp;F77&amp;F78&amp;F79&amp;F80&amp;F81&amp;F82&amp;F83&amp;F84&amp;F85&amp;F86&amp;F87&amp;F88&amp;"';"</f>
@@ -24130,7 +23508,7 @@
       </c>
       <c r="D2" s="39"/>
       <c r="E2" s="24" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F2" s="27" t="str">
         <f>IF(NOT(ISBLANK(E2)),E2&amp;"\n ","")</f>
@@ -24145,7 +23523,7 @@
       </c>
       <c r="D3" s="40"/>
       <c r="E3" s="24" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F3" s="27" t="str">
         <f t="shared" ref="F3:F66" si="1">IF(NOT(ISBLANK(E3)),E3&amp;"\n ","")</f>
@@ -24160,7 +23538,7 @@
       </c>
       <c r="D4" s="39"/>
       <c r="E4" s="24" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F4" s="27" t="str">
         <f t="shared" si="1"/>
@@ -24175,7 +23553,7 @@
       </c>
       <c r="D5" s="40"/>
       <c r="E5" s="24" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F5" s="27" t="str">
         <f t="shared" si="1"/>
@@ -24190,7 +23568,7 @@
       </c>
       <c r="D6" s="40"/>
       <c r="E6" s="24" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F6" s="27" t="str">
         <f t="shared" si="1"/>
@@ -24205,7 +23583,7 @@
       </c>
       <c r="D7" s="40"/>
       <c r="E7" s="24" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F7" s="27" t="str">
         <f t="shared" si="1"/>
@@ -24220,7 +23598,7 @@
       </c>
       <c r="D8" s="40"/>
       <c r="E8" s="24" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F8" s="27" t="str">
         <f t="shared" si="1"/>
@@ -24248,7 +23626,7 @@
       </c>
       <c r="D10" s="40"/>
       <c r="E10" s="24" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F10" s="27" t="str">
         <f t="shared" si="1"/>
@@ -25204,909 +24582,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
-  <cols>
-    <col min="1" max="1" width="32.875" customWidth="1"/>
-    <col min="2" max="2" width="26.25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="7" t="str">
-        <f>"Blockly.Arduino.setups_['"&amp;變數!$A$2&amp;"'] = "&amp;
-'S(變)'!B3 &amp; 'S(變)'!B5
-&amp;";"</f>
-        <v>Blockly.Arduino.setups_['01imi_esp32car_init'] = ''pinMode('+value_swpin+', INPUT_PULLUP);\n '++++++++++++;</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="9"/>
-      <c r="B3" s="12" t="str">
-        <f>B2&amp;"+"&amp;C2&amp;"+"&amp;D2&amp;"+"&amp;E2&amp;"+"&amp;F2&amp;"+"&amp;G2&amp;"+"&amp;H2&amp;"+"&amp;I2</f>
-        <v>''pinMode('+value_swpin+', INPUT_PULLUP);\n '+++++</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="18"/>
-      <c r="B4" s="13"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="9"/>
-      <c r="B5" s="12" t="str">
-        <f>B4&amp;"+"&amp;C4&amp;"+"&amp;D4&amp;"+"&amp;E4&amp;"+"&amp;F4&amp;"+"&amp;G4&amp;"+"&amp;H4&amp;"+"&amp;I4</f>
-        <v>+++++++</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="10"/>
-      <c r="B6" s="9"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="9"/>
-      <c r="B7" s="12" t="str">
-        <f>B6&amp;"+"&amp;C6&amp;"+"&amp;D6&amp;"+"&amp;E6&amp;"+"&amp;F6&amp;"+"&amp;G6&amp;"+"&amp;H6&amp;"+"&amp;I6</f>
-        <v>+++++++</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="10"/>
-      <c r="B8" s="9"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="9"/>
-      <c r="B9" s="12" t="str">
-        <f>B8&amp;"+"&amp;C8&amp;"+"&amp;D8&amp;"+"&amp;E8&amp;"+"&amp;F8&amp;"+"&amp;G8&amp;"+"&amp;H8&amp;"+"&amp;I8</f>
-        <v>+++++++</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="10"/>
-      <c r="B10" s="9"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="9"/>
-      <c r="B11" s="12" t="str">
-        <f>B10&amp;"+"&amp;C10&amp;"+"&amp;D10&amp;"+"&amp;E10&amp;"+"&amp;F10&amp;"+"&amp;G10&amp;"+"&amp;H10&amp;"+"&amp;I10</f>
-        <v>+++++++</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="9"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:E88"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
-  <cols>
-    <col min="1" max="1" width="64.25" customWidth="1"/>
-    <col min="2" max="2" width="23.75" customWidth="1"/>
-    <col min="4" max="4" width="16.375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="8" t="str">
-        <f>"Blockly.Arduino.functions_['"&amp;D2&amp;"'] = '"&amp;D3&amp;"';"</f>
-        <v>Blockly.Arduino.functions_['01imi_esp32car_init'] = 'void reconnect() {\n  while (!client.connected()) {\n    Serial.print("Attempting MQTT connection… ");\n    String clientId = "ESP32Client";\n    if (client.connect(clientId.c_str(), mqtt_username, mqtt_password)) {\n      Serial.println("connected!");\n    } else {\n      Serial.print("failed, rc = ");\n      Serial.print(client.state());\n      Serial.println(" try again in 5 seconds");\n      delay(5000);\n    }\n  }\n}\nvoid sendLineMsg(String myMsg) {\n  static WiFiClientSecure line_client;\n  line_client.setInsecure();\n  myMsg.replace("%", "%25");\n  myMsg.replace("&amp;", "%26");\n  myMsg.replace("§", "&amp;");\n  myMsg.replace("\\n", "\n");\n  if (line_client.connect("notify-api.line.me", 443)) {\n    line_client.println("POST /api/notify HTTP/1.1");\n    line_client.println("Connection: close");\n    line_client.println("Host: notify-api.line.me");\n    line_client.println("Authorization: Bearer " + lineToken);\n    line_client.println("Content-Type: application/x-www-form-urlencoded");\n    line_client.println("Content-Length: " + String(myMsg.length()));\n    line_client.println();\n    line_client.println(myMsg);\n    line_client.println();\n    line_client.stop();\n  } else {\n    Serial.println("Line Notify failed");\n  }\n}\nvoid setup_wifi() {\n  delay(10);\n  Serial.println();\n  Serial.print("Connecting to ");\n  Serial.println(ssid);\n  WiFi.mode(WIFI_STA);\n  WiFi.begin(ssid, password);\n  while (WiFi.status() != WL_CONNECTED) {\n    delay(500);\n    Serial.print(".");\n  }\n  Serial.println("");\n  Serial.println("WiFi connected");\n  Serial.println("IP address: ");\n  Serial.println(WiFi.localIP());\n}\n//傳送訊息：ESP32→Mega\nvoid UartSentToMega(String msg) {\n  MegaSerial.print(msg);\n}\n';</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="B2" s="27" t="str">
-        <f>IF(NOT(ISBLANK(A2)),A2&amp;"\n","")</f>
-        <v>void reconnect() {\n</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="5" t="str">
-        <f>變數!$A$2</f>
-        <v>01imi_esp32car_init</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="B3" s="27" t="str">
-        <f t="shared" ref="B3:B66" si="0">IF(NOT(ISBLANK(A3)),A3&amp;"\n","")</f>
-        <v xml:space="preserve">  while (!client.connected()) {\n</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D3" s="5" t="str">
-        <f>B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88</f>
-        <v>void reconnect() {\n  while (!client.connected()) {\n    Serial.print("Attempting MQTT connection… ");\n    String clientId = "ESP32Client";\n    if (client.connect(clientId.c_str(), mqtt_username, mqtt_password)) {\n      Serial.println("connected!");\n    } else {\n      Serial.print("failed, rc = ");\n      Serial.print(client.state());\n      Serial.println(" try again in 5 seconds");\n      delay(5000);\n    }\n  }\n}\nvoid sendLineMsg(String myMsg) {\n  static WiFiClientSecure line_client;\n  line_client.setInsecure();\n  myMsg.replace("%", "%25");\n  myMsg.replace("&amp;", "%26");\n  myMsg.replace("§", "&amp;");\n  myMsg.replace("\\n", "\n");\n  if (line_client.connect("notify-api.line.me", 443)) {\n    line_client.println("POST /api/notify HTTP/1.1");\n    line_client.println("Connection: close");\n    line_client.println("Host: notify-api.line.me");\n    line_client.println("Authorization: Bearer " + lineToken);\n    line_client.println("Content-Type: application/x-www-form-urlencoded");\n    line_client.println("Content-Length: " + String(myMsg.length()));\n    line_client.println();\n    line_client.println(myMsg);\n    line_client.println();\n    line_client.stop();\n  } else {\n    Serial.println("Line Notify failed");\n  }\n}\nvoid setup_wifi() {\n  delay(10);\n  Serial.println();\n  Serial.print("Connecting to ");\n  Serial.println(ssid);\n  WiFi.mode(WIFI_STA);\n  WiFi.begin(ssid, password);\n  while (WiFi.status() != WL_CONNECTED) {\n    delay(500);\n    Serial.print(".");\n  }\n  Serial.println("");\n  Serial.println("WiFi connected");\n  Serial.println("IP address: ");\n  Serial.println(WiFi.localIP());\n}\n//傳送訊息：ESP32→Mega\nvoid UartSentToMega(String msg) {\n  MegaSerial.print(msg);\n}\n</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="B4" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    Serial.print("Attempting MQTT connection… ");\n</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    String clientId = "ESP32Client";\n</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="B6" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    if (client.connect(clientId.c_str(), mqtt_username, mqtt_password)) {\n</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="B7" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">      Serial.println("connected!");\n</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="B8" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    } else {\n</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="B9" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">      Serial.print("failed, rc = ");\n</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="B10" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">      Serial.print(client.state());\n</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="B11" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">      Serial.println(" try again in 5 seconds");\n</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="B12" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">      delay(5000);\n</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="B13" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    }\n</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">  }\n</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v>}\n</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="24"/>
-      <c r="B16" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="B17" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v>void sendLineMsg(String myMsg) {\n</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="B18" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">  static WiFiClientSecure line_client;\n</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="B19" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">  line_client.setInsecure();\n</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="B20" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">  myMsg.replace("%", "%25");\n</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="B21" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">  myMsg.replace("&amp;", "%26");\n</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="B22" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">  myMsg.replace("§", "&amp;");\n</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="23" t="s">
-        <v>93</v>
-      </c>
-      <c r="B23" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">  myMsg.replace("\\n", "\n");\n</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B24" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">  if (line_client.connect("notify-api.line.me", 443)) {\n</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="B25" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    line_client.println("POST /api/notify HTTP/1.1");\n</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="B26" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    line_client.println("Connection: close");\n</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="B27" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    line_client.println("Host: notify-api.line.me");\n</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="23" t="s">
-        <v>98</v>
-      </c>
-      <c r="B28" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    line_client.println("Authorization: Bearer " + lineToken);\n</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="B29" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    line_client.println("Content-Type: application/x-www-form-urlencoded");\n</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="B30" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    line_client.println("Content-Length: " + String(myMsg.length()));\n</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="23" t="s">
-        <v>101</v>
-      </c>
-      <c r="B31" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    line_client.println();\n</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="B32" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    line_client.println(myMsg);\n</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="23" t="s">
-        <v>101</v>
-      </c>
-      <c r="B33" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    line_client.println();\n</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="B34" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    line_client.stop();\n</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="B35" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">  } else {\n</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="B36" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    Serial.println("Line Notify failed");\n</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="B37" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">  }\n</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="B38" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v>}\n</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="3"/>
-      <c r="B39" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="23" t="s">
-        <v>121</v>
-      </c>
-      <c r="B40" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v>void setup_wifi() {\n</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="23" t="s">
-        <v>122</v>
-      </c>
-      <c r="B41" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">  delay(10);\n</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="B42" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">  Serial.println();\n</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="23" t="s">
-        <v>124</v>
-      </c>
-      <c r="B43" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">  Serial.print("Connecting to ");\n</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="B44" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">  Serial.println(ssid);\n</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" s="23"/>
-      <c r="B45" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="B46" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">  WiFi.mode(WIFI_STA);\n</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" s="23" t="s">
-        <v>127</v>
-      </c>
-      <c r="B47" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">  WiFi.begin(ssid, password);\n</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" s="23"/>
-      <c r="B48" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="B49" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">  while (WiFi.status() != WL_CONNECTED) {\n</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="B50" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    delay(500);\n</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="B51" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">    Serial.print(".");\n</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="B52" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">  }\n</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" s="23"/>
-      <c r="B53" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="23" t="s">
-        <v>131</v>
-      </c>
-      <c r="B54" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">  Serial.println("");\n</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="B55" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">  Serial.println("WiFi connected");\n</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="B56" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">  Serial.println("IP address: ");\n</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="B57" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">  Serial.println(WiFi.localIP());\n</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="B58" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v>}\n</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59" s="3"/>
-      <c r="B59" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="B60" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v>//傳送訊息：ESP32→Mega\n</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="B61" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v>void UartSentToMega(String msg) {\n</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="B62" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">  MegaSerial.print(msg);\n</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="B63" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v>}\n</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64" s="3"/>
-      <c r="B64" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="A65" s="3"/>
-      <c r="B65" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
-      <c r="A66" s="3"/>
-      <c r="B66" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
-      <c r="A67" s="3"/>
-      <c r="B67" s="27" t="str">
-        <f t="shared" ref="B67:B88" si="1">IF(NOT(ISBLANK(A67)),A67&amp;"\n","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="A68" s="3"/>
-      <c r="B68" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
-      <c r="A69" s="3"/>
-      <c r="B69" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
-      <c r="A70" s="3"/>
-      <c r="B70" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
-      <c r="A71" s="3"/>
-      <c r="B71" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
-      <c r="A72" s="3"/>
-      <c r="B72" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
-      <c r="A73" s="3"/>
-      <c r="B73" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="74" spans="1:2">
-      <c r="A74" s="3"/>
-      <c r="B74" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="75" spans="1:2">
-      <c r="A75" s="3"/>
-      <c r="B75" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="76" spans="1:2">
-      <c r="A76" s="3"/>
-      <c r="B76" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="77" spans="1:2">
-      <c r="A77" s="3"/>
-      <c r="B77" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="78" spans="1:2">
-      <c r="A78" s="3"/>
-      <c r="B78" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="79" spans="1:2">
-      <c r="A79" s="3"/>
-      <c r="B79" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="80" spans="1:2">
-      <c r="A80" s="3"/>
-      <c r="B80" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="81" spans="1:2">
-      <c r="A81" s="3"/>
-      <c r="B81" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="82" spans="1:2">
-      <c r="A82" s="3"/>
-      <c r="B82" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="83" spans="1:2">
-      <c r="A83" s="3"/>
-      <c r="B83" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="84" spans="1:2">
-      <c r="A84" s="3"/>
-      <c r="B84" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="85" spans="1:2">
-      <c r="A85" s="3"/>
-      <c r="B85" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="86" spans="1:2">
-      <c r="A86" s="3"/>
-      <c r="B86" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="87" spans="1:2">
-      <c r="A87" s="3"/>
-      <c r="B87" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="88" spans="1:2">
-      <c r="A88" s="3"/>
-      <c r="B88" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:G88"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
@@ -26120,23 +24595,23 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C1" s="7" t="str">
         <f>"var code ="&amp;B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88&amp;";"</f>
         <v>var code =;</v>
       </c>
       <c r="D1" s="38" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1" t="s">
         <v>168</v>
-      </c>
-      <c r="F1" t="s">
-        <v>170</v>
       </c>
       <c r="G1" s="7" t="str">
         <f>"var code ='"&amp;F2&amp;F3&amp;F4&amp;F5&amp;F6&amp;F7&amp;F8&amp;F9&amp;F10&amp;F11&amp;F12&amp;F13&amp;F14&amp;F15&amp;F16&amp;F17&amp;F18&amp;F19&amp;F20&amp;F21&amp;F22&amp;F23&amp;F24&amp;F25&amp;F26&amp;F27&amp;F28&amp;F29&amp;F30&amp;F31&amp;F32&amp;F33&amp;F34&amp;F35&amp;F36&amp;F37&amp;F38&amp;F39&amp;F40&amp;F41&amp;F42&amp;F43&amp;F44&amp;F45&amp;F46&amp;F47&amp;F48&amp;F49&amp;F50&amp;F51&amp;F52&amp;F53&amp;F54&amp;F55&amp;F56&amp;F57&amp;F58&amp;F59&amp;F60&amp;F61&amp;F62&amp;F63&amp;F64&amp;F65&amp;F66&amp;F67&amp;F68&amp;F69&amp;F70&amp;F71&amp;F72&amp;F73&amp;F74&amp;F75&amp;F76&amp;F77&amp;F78&amp;F79&amp;F80&amp;F81&amp;F82&amp;F83&amp;F84&amp;F85&amp;F86&amp;F87&amp;F88&amp;"';"</f>
@@ -27207,7 +25682,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I88"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
@@ -27232,14 +25707,14 @@
       </c>
       <c r="D1" s="8" t="str">
         <f>"Blockly.Arduino.definitions_['"&amp;D2&amp;"'] = '"&amp;D3&amp;"';"</f>
-        <v>Blockly.Arduino.definitions_['01imi_esp32car_init'] = '#include &lt;SoftwareSerial.h&gt;\n#include &lt;WiFi.h&gt;\n#include &lt;PubSubClient.h&gt;\n#include &lt;WiFiClientSecure.h&gt;\n//與Mega通訊\nconst char* MAP_SET = "mapSet";\nconst char* GOODS_LOAD = "goodsLoad";\nconst char* LINE_NOTIFY = "lineNotify";\nconst char* CAR_GPS = "carGps";\n//===設定程式碼input Start===\n//===設定程式碼input End===\n//Topic主題\nconst char* TOPIC_MAP_SET = "imiRobot/map/set";\nconst char* TOPIC_CAR_STANDBY = "imiRobot/car/standby";\nconst char* TOPIC_CAR_GPS = "imiRobot/car/gps";\nconst char* TOPIC_GOODS_LOAD = "imiRobot/goods/load";\nconst char* TOPIC_CAR_LOWPOWER = "imiRobot/car/lowPower";\n//發佈者 傳送的消息內容\nchar* mqttSendMsg = "";\n//訂閱者 接收的消息內容\nString mqttGetMsg = "";\nWiFiClientSecure espClient;\nPubSubClient client(espClient);\n// HiveMQ Cloud\nstatic const char* root_ca PROGMEM = R"EOF(\n-----BEGIN CERTIFICATE-----\nMIIFazCCA1OgAwIBAgIRAIIQz7DSQONZRGPgu2OCiwAwDQYJKoZIhvcNAQELBQAw\nTzELMAkGA1UEBhMCVVMxKTAnBgNVBAoTIEludGVybmV0IFNlY3VyaXR5IFJlc2Vh\ncmNoIEdyb3VwMRUwEwYDVQQDEwxJU1JHIFJvb3QgWDEwHhcNMTUwNjA0MTEwNDM4\nWhcNMzUwNjA0MTEwNDM4WjBPMQswCQYDVQQGEwJVUzEpMCcGA1UEChMgSW50ZXJu\nZXQgU2VjdXJpdHkgUmVzZWFyY2ggR3JvdXAxFTATBgNVBAMTDElTUkcgUm9vdCBY\nMTCCAiIwDQYJKoZIhvcNAQEBBQADggIPADCCAgoCggIBAK3oJHP0FDfzm54rVygc\nh77ct984kIxuPOZXoHj3dcKi/vVqbvYATyjb3miGbESTtrFj/RQSa78f0uoxmyF+\n0TM8ukj13Xnfs7j/EvEhmkvBioZxaUpmZmyPfjxwv60pIgbz5MDmgK7iS4+3mX6U\nA5/TR5d8mUgjU+g4rk8Kb4Mu0UlXjIB0ttov0DiNewNwIRt18jA8+o+u3dpjq+sW\nT8KOEUt+zwvo/7V3LvSye0rgTBIlDHCNAymg4VMk7BPZ7hm/ELNKjD+Jo2FR3qyH\nB5T0Y3HsLuJvW5iB4YlcNHlsdu87kGJ55tukmi8mxdAQ4Q7e2RCOFvu396j3x+UC\nB5iPNgiV5+I3lg02dZ77DnKxHZu8A/lJBdiB3QW0KtZB6awBdpUKD9jf1b0SHzUv\nKBds0pjBqAlkd25HN7rOrFleaJ1/ctaJxQZBKT5ZPt0m9STJEadao0xAH0ahmbWn\nOlFuhjuefXKnEgV4We0+UXgVCwOPjdAvBbI+e0ocS3MFEvzG6uBQE3xDk3SzynTn\njh8BCNAw1FtxNrQHusEwMFxIt4I7mKZ9YIqioymCzLq9gwQbooMDQaHWBfEbwrbw\nqHyGO0aoSCqI3Haadr8faqU9GY/rOPNk3sgrDQoo//fb4hVC1CLQJ13hef4Y53CI\nrU7m2Ys6xt0nUW7/vGT1M0NPAgMBAAGjQjBAMA4GA1UdDwEB/wQEAwIBBjAPBgNV\nHRMBAf8EBTADAQH/MB0GA1UdDgQWBBR5tFnme7bl5AFzgAiIyBpY9umbbjANBgkq\nhkiG9w0BAQsFAAOCAgEAVR9YqbyyqFDQDLHYGmkgJykIrGF1XIpu+ILlaS/V9lZL\nubhzEFnTIZd+50xx+7LSYK05qAvqFyFWhfFQDlnrzuBZ6brJFe+GnY+EgPbk6ZGQ\n3BebYhtF8GaV0nxvwuo77x/Py9auJ/GpsMiu/X1+mvoiBOv/2X/qkSsisRcOj/KK\nNFtY2PwByVS5uCbMiogziUwthDyC3+6WVwW6LLv3xLfHTjuCvjHIInNzktHCgKQ5\nORAzI4JMPJ+GslWYHb4phowim57iaztXOoJwTdwJx4nLCgdNbOhdjsnvzqvHu7Ur\nTkXWStAmzOVyyghqpZXjFaH3pO3JLF+l+/+sKAIuvtd7u+Nxe5AW0wdeRlN8NwdC\njNPElpzVmbUq4JUagEiuTDkHzsxHpFKVK7q4+63SM1N95R1NbdWhscdCb+ZAJzVc\noyi3B43njTOQ5yOf+1CceWxG1bQVs5ZufpsMljq4Ui0/1lvh+wjChP4kqKOJ2qxq\n4RgqsahDYVvTH9w7jXbyLeiNdd8XM2w9U/t7y0Ff/9yi0GE44Za4rF2LN9d11TPA\nmRGunUHBcnWEvgJBQl9nJEiU0Zsnvgc/ubhPgXRR4Xq37Z0j4r7g1SgEEzwxA57d\nemyPxgcYxn/eR44/KJ4EBs+lVDR3veyJm+kXQ99b21/+jh5Xos1AnX5iItreGCc=\n-----END CERTIFICATE-----\n)EOF";\n';</v>
+        <v>Blockly.Arduino.definitions_['_01imi_esp32car_init'] = '#include &lt;SoftwareSerial.h&gt;\n#include &lt;WiFi.h&gt;\n#include &lt;PubSubClient.h&gt;\n#include &lt;WiFiClientSecure.h&gt;\n//與Mega通訊\nconst char* MAP_SET = "mapSet";\nconst char* GOODS_LOAD = "goodsLoad";\nconst char* LINE_NOTIFY = "lineNotify";\nconst char* CAR_GPS = "carGps";\n//===設定程式碼input Start===\n//===設定程式碼input End===\n//Topic主題\nconst char* TOPIC_MAP_SET = "imiRobot/map/set";\nconst char* TOPIC_CAR_STANDBY = "imiRobot/car/standby";\nconst char* TOPIC_CAR_GPS = "imiRobot/car/gps";\nconst char* TOPIC_GOODS_LOAD = "imiRobot/goods/load";\nconst char* TOPIC_CAR_LOWPOWER = "imiRobot/car/lowPower";\n//發佈者 傳送的消息內容\nchar* mqttSendMsg = "";\n//訂閱者 接收的消息內容\nString mqttGetMsg = "";\nWiFiClientSecure espClient;\nPubSubClient client(espClient);\n// HiveMQ Cloud\nstatic const char* root_ca PROGMEM = R"EOF(\n-----BEGIN CERTIFICATE-----\nMIIFazCCA1OgAwIBAgIRAIIQz7DSQONZRGPgu2OCiwAwDQYJKoZIhvcNAQELBQAw\nTzELMAkGA1UEBhMCVVMxKTAnBgNVBAoTIEludGVybmV0IFNlY3VyaXR5IFJlc2Vh\ncmNoIEdyb3VwMRUwEwYDVQQDEwxJU1JHIFJvb3QgWDEwHhcNMTUwNjA0MTEwNDM4\nWhcNMzUwNjA0MTEwNDM4WjBPMQswCQYDVQQGEwJVUzEpMCcGA1UEChMgSW50ZXJu\nZXQgU2VjdXJpdHkgUmVzZWFyY2ggR3JvdXAxFTATBgNVBAMTDElTUkcgUm9vdCBY\nMTCCAiIwDQYJKoZIhvcNAQEBBQADggIPADCCAgoCggIBAK3oJHP0FDfzm54rVygc\nh77ct984kIxuPOZXoHj3dcKi/vVqbvYATyjb3miGbESTtrFj/RQSa78f0uoxmyF+\n0TM8ukj13Xnfs7j/EvEhmkvBioZxaUpmZmyPfjxwv60pIgbz5MDmgK7iS4+3mX6U\nA5/TR5d8mUgjU+g4rk8Kb4Mu0UlXjIB0ttov0DiNewNwIRt18jA8+o+u3dpjq+sW\nT8KOEUt+zwvo/7V3LvSye0rgTBIlDHCNAymg4VMk7BPZ7hm/ELNKjD+Jo2FR3qyH\nB5T0Y3HsLuJvW5iB4YlcNHlsdu87kGJ55tukmi8mxdAQ4Q7e2RCOFvu396j3x+UC\nB5iPNgiV5+I3lg02dZ77DnKxHZu8A/lJBdiB3QW0KtZB6awBdpUKD9jf1b0SHzUv\nKBds0pjBqAlkd25HN7rOrFleaJ1/ctaJxQZBKT5ZPt0m9STJEadao0xAH0ahmbWn\nOlFuhjuefXKnEgV4We0+UXgVCwOPjdAvBbI+e0ocS3MFEvzG6uBQE3xDk3SzynTn\njh8BCNAw1FtxNrQHusEwMFxIt4I7mKZ9YIqioymCzLq9gwQbooMDQaHWBfEbwrbw\nqHyGO0aoSCqI3Haadr8faqU9GY/rOPNk3sgrDQoo//fb4hVC1CLQJ13hef4Y53CI\nrU7m2Ys6xt0nUW7/vGT1M0NPAgMBAAGjQjBAMA4GA1UdDwEB/wQEAwIBBjAPBgNV\nHRMBAf8EBTADAQH/MB0GA1UdDgQWBBR5tFnme7bl5AFzgAiIyBpY9umbbjANBgkq\nhkiG9w0BAQsFAAOCAgEAVR9YqbyyqFDQDLHYGmkgJykIrGF1XIpu+ILlaS/V9lZL\nubhzEFnTIZd+50xx+7LSYK05qAvqFyFWhfFQDlnrzuBZ6brJFe+GnY+EgPbk6ZGQ\n3BebYhtF8GaV0nxvwuo77x/Py9auJ/GpsMiu/X1+mvoiBOv/2X/qkSsisRcOj/KK\nNFtY2PwByVS5uCbMiogziUwthDyC3+6WVwW6LLv3xLfHTjuCvjHIInNzktHCgKQ5\nORAzI4JMPJ+GslWYHb4phowim57iaztXOoJwTdwJx4nLCgdNbOhdjsnvzqvHu7Ur\nTkXWStAmzOVyyghqpZXjFaH3pO3JLF+l+/+sKAIuvtd7u+Nxe5AW0wdeRlN8NwdC\njNPElpzVmbUq4JUagEiuTDkHzsxHpFKVK7q4+63SM1N95R1NbdWhscdCb+ZAJzVc\noyi3B43njTOQ5yOf+1CceWxG1bQVs5ZufpsMljq4Ui0/1lvh+wjChP4kqKOJ2qxq\n4RgqsahDYVvTH9w7jXbyLeiNdd8XM2w9U/t7y0Ff/9yi0GE44Za4rF2LN9d11TPA\nmRGunUHBcnWEvgJBQl9nJEiU0Zsnvgc/ubhPgXRR4Xq37Z0j4r7g1SgEEzwxA57d\nemyPxgcYxn/eR44/KJ4EBs+lVDR3veyJm+kXQ99b21/+jh5Xos1AnX5iItreGCc=\n-----END CERTIFICATE-----\n)EOF";\n';</v>
       </c>
       <c r="E1" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="F1" s="8" t="str">
         <f>"Blockly.Arduino.definitions_['"&amp;D2&amp;"'] = '"&amp;D3&amp;"'"&amp;"+"&amp;D4&amp;"+"&amp;D5&amp;"+"&amp;D6&amp;"+"&amp;D7&amp;";"</f>
-        <v>Blockly.Arduino.definitions_['01imi_esp32car_init'] = '#include &lt;SoftwareSerial.h&gt;\n#include &lt;WiFi.h&gt;\n#include &lt;PubSubClient.h&gt;\n#include &lt;WiFiClientSecure.h&gt;\n//與Mega通訊\nconst char* MAP_SET = "mapSet";\nconst char* GOODS_LOAD = "goodsLoad";\nconst char* LINE_NOTIFY = "lineNotify";\nconst char* CAR_GPS = "carGps";\n//===設定程式碼input Start===\n//===設定程式碼input End===\n//Topic主題\nconst char* TOPIC_MAP_SET = "imiRobot/map/set";\nconst char* TOPIC_CAR_STANDBY = "imiRobot/car/standby";\nconst char* TOPIC_CAR_GPS = "imiRobot/car/gps";\nconst char* TOPIC_GOODS_LOAD = "imiRobot/goods/load";\nconst char* TOPIC_CAR_LOWPOWER = "imiRobot/car/lowPower";\n//發佈者 傳送的消息內容\nchar* mqttSendMsg = "";\n//訂閱者 接收的消息內容\nString mqttGetMsg = "";\nWiFiClientSecure espClient;\nPubSubClient client(espClient);\n// HiveMQ Cloud\nstatic const char* root_ca PROGMEM = R"EOF(\n-----BEGIN CERTIFICATE-----\nMIIFazCCA1OgAwIBAgIRAIIQz7DSQONZRGPgu2OCiwAwDQYJKoZIhvcNAQELBQAw\nTzELMAkGA1UEBhMCVVMxKTAnBgNVBAoTIEludGVybmV0IFNlY3VyaXR5IFJlc2Vh\ncmNoIEdyb3VwMRUwEwYDVQQDEwxJU1JHIFJvb3QgWDEwHhcNMTUwNjA0MTEwNDM4\nWhcNMzUwNjA0MTEwNDM4WjBPMQswCQYDVQQGEwJVUzEpMCcGA1UEChMgSW50ZXJu\nZXQgU2VjdXJpdHkgUmVzZWFyY2ggR3JvdXAxFTATBgNVBAMTDElTUkcgUm9vdCBY\nMTCCAiIwDQYJKoZIhvcNAQEBBQADggIPADCCAgoCggIBAK3oJHP0FDfzm54rVygc\nh77ct984kIxuPOZXoHj3dcKi/vVqbvYATyjb3miGbESTtrFj/RQSa78f0uoxmyF+\n0TM8ukj13Xnfs7j/EvEhmkvBioZxaUpmZmyPfjxwv60pIgbz5MDmgK7iS4+3mX6U\nA5/TR5d8mUgjU+g4rk8Kb4Mu0UlXjIB0ttov0DiNewNwIRt18jA8+o+u3dpjq+sW\nT8KOEUt+zwvo/7V3LvSye0rgTBIlDHCNAymg4VMk7BPZ7hm/ELNKjD+Jo2FR3qyH\nB5T0Y3HsLuJvW5iB4YlcNHlsdu87kGJ55tukmi8mxdAQ4Q7e2RCOFvu396j3x+UC\nB5iPNgiV5+I3lg02dZ77DnKxHZu8A/lJBdiB3QW0KtZB6awBdpUKD9jf1b0SHzUv\nKBds0pjBqAlkd25HN7rOrFleaJ1/ctaJxQZBKT5ZPt0m9STJEadao0xAH0ahmbWn\nOlFuhjuefXKnEgV4We0+UXgVCwOPjdAvBbI+e0ocS3MFEvzG6uBQE3xDk3SzynTn\njh8BCNAw1FtxNrQHusEwMFxIt4I7mKZ9YIqioymCzLq9gwQbooMDQaHWBfEbwrbw\nqHyGO0aoSCqI3Haadr8faqU9GY/rOPNk3sgrDQoo//fb4hVC1CLQJ13hef4Y53CI\nrU7m2Ys6xt0nUW7/vGT1M0NPAgMBAAGjQjBAMA4GA1UdDwEB/wQEAwIBBjAPBgNV\nHRMBAf8EBTADAQH/MB0GA1UdDgQWBBR5tFnme7bl5AFzgAiIyBpY9umbbjANBgkq\nhkiG9w0BAQsFAAOCAgEAVR9YqbyyqFDQDLHYGmkgJykIrGF1XIpu+ILlaS/V9lZL\nubhzEFnTIZd+50xx+7LSYK05qAvqFyFWhfFQDlnrzuBZ6brJFe+GnY+EgPbk6ZGQ\n3BebYhtF8GaV0nxvwuo77x/Py9auJ/GpsMiu/X1+mvoiBOv/2X/qkSsisRcOj/KK\nNFtY2PwByVS5uCbMiogziUwthDyC3+6WVwW6LLv3xLfHTjuCvjHIInNzktHCgKQ5\nORAzI4JMPJ+GslWYHb4phowim57iaztXOoJwTdwJx4nLCgdNbOhdjsnvzqvHu7Ur\nTkXWStAmzOVyyghqpZXjFaH3pO3JLF+l+/+sKAIuvtd7u+Nxe5AW0wdeRlN8NwdC\njNPElpzVmbUq4JUagEiuTDkHzsxHpFKVK7q4+63SM1N95R1NbdWhscdCb+ZAJzVc\noyi3B43njTOQ5yOf+1CceWxG1bQVs5ZufpsMljq4Ui0/1lvh+wjChP4kqKOJ2qxq\n4RgqsahDYVvTH9w7jXbyLeiNdd8XM2w9U/t7y0Ff/9yi0GE44Za4rF2LN9d11TPA\nmRGunUHBcnWEvgJBQl9nJEiU0Zsnvgc/ubhPgXRR4Xq37Z0j4r7g1SgEEzwxA57d\nemyPxgcYxn/eR44/KJ4EBs+lVDR3veyJm+kXQ99b21/+jh5Xos1AnX5iItreGCc=\n-----END CERTIFICATE-----\n)EOF";\n'+value_uart +value_wifi +value_line +value_mqtt ;</v>
+        <v>Blockly.Arduino.definitions_['_01imi_esp32car_init'] = '#include &lt;SoftwareSerial.h&gt;\n#include &lt;WiFi.h&gt;\n#include &lt;PubSubClient.h&gt;\n#include &lt;WiFiClientSecure.h&gt;\n//與Mega通訊\nconst char* MAP_SET = "mapSet";\nconst char* GOODS_LOAD = "goodsLoad";\nconst char* LINE_NOTIFY = "lineNotify";\nconst char* CAR_GPS = "carGps";\n//===設定程式碼input Start===\n//===設定程式碼input End===\n//Topic主題\nconst char* TOPIC_MAP_SET = "imiRobot/map/set";\nconst char* TOPIC_CAR_STANDBY = "imiRobot/car/standby";\nconst char* TOPIC_CAR_GPS = "imiRobot/car/gps";\nconst char* TOPIC_GOODS_LOAD = "imiRobot/goods/load";\nconst char* TOPIC_CAR_LOWPOWER = "imiRobot/car/lowPower";\n//發佈者 傳送的消息內容\nchar* mqttSendMsg = "";\n//訂閱者 接收的消息內容\nString mqttGetMsg = "";\nWiFiClientSecure espClient;\nPubSubClient client(espClient);\n// HiveMQ Cloud\nstatic const char* root_ca PROGMEM = R"EOF(\n-----BEGIN CERTIFICATE-----\nMIIFazCCA1OgAwIBAgIRAIIQz7DSQONZRGPgu2OCiwAwDQYJKoZIhvcNAQELBQAw\nTzELMAkGA1UEBhMCVVMxKTAnBgNVBAoTIEludGVybmV0IFNlY3VyaXR5IFJlc2Vh\ncmNoIEdyb3VwMRUwEwYDVQQDEwxJU1JHIFJvb3QgWDEwHhcNMTUwNjA0MTEwNDM4\nWhcNMzUwNjA0MTEwNDM4WjBPMQswCQYDVQQGEwJVUzEpMCcGA1UEChMgSW50ZXJu\nZXQgU2VjdXJpdHkgUmVzZWFyY2ggR3JvdXAxFTATBgNVBAMTDElTUkcgUm9vdCBY\nMTCCAiIwDQYJKoZIhvcNAQEBBQADggIPADCCAgoCggIBAK3oJHP0FDfzm54rVygc\nh77ct984kIxuPOZXoHj3dcKi/vVqbvYATyjb3miGbESTtrFj/RQSa78f0uoxmyF+\n0TM8ukj13Xnfs7j/EvEhmkvBioZxaUpmZmyPfjxwv60pIgbz5MDmgK7iS4+3mX6U\nA5/TR5d8mUgjU+g4rk8Kb4Mu0UlXjIB0ttov0DiNewNwIRt18jA8+o+u3dpjq+sW\nT8KOEUt+zwvo/7V3LvSye0rgTBIlDHCNAymg4VMk7BPZ7hm/ELNKjD+Jo2FR3qyH\nB5T0Y3HsLuJvW5iB4YlcNHlsdu87kGJ55tukmi8mxdAQ4Q7e2RCOFvu396j3x+UC\nB5iPNgiV5+I3lg02dZ77DnKxHZu8A/lJBdiB3QW0KtZB6awBdpUKD9jf1b0SHzUv\nKBds0pjBqAlkd25HN7rOrFleaJ1/ctaJxQZBKT5ZPt0m9STJEadao0xAH0ahmbWn\nOlFuhjuefXKnEgV4We0+UXgVCwOPjdAvBbI+e0ocS3MFEvzG6uBQE3xDk3SzynTn\njh8BCNAw1FtxNrQHusEwMFxIt4I7mKZ9YIqioymCzLq9gwQbooMDQaHWBfEbwrbw\nqHyGO0aoSCqI3Haadr8faqU9GY/rOPNk3sgrDQoo//fb4hVC1CLQJ13hef4Y53CI\nrU7m2Ys6xt0nUW7/vGT1M0NPAgMBAAGjQjBAMA4GA1UdDwEB/wQEAwIBBjAPBgNV\nHRMBAf8EBTADAQH/MB0GA1UdDgQWBBR5tFnme7bl5AFzgAiIyBpY9umbbjANBgkq\nhkiG9w0BAQsFAAOCAgEAVR9YqbyyqFDQDLHYGmkgJykIrGF1XIpu+ILlaS/V9lZL\nubhzEFnTIZd+50xx+7LSYK05qAvqFyFWhfFQDlnrzuBZ6brJFe+GnY+EgPbk6ZGQ\n3BebYhtF8GaV0nxvwuo77x/Py9auJ/GpsMiu/X1+mvoiBOv/2X/qkSsisRcOj/KK\nNFtY2PwByVS5uCbMiogziUwthDyC3+6WVwW6LLv3xLfHTjuCvjHIInNzktHCgKQ5\nORAzI4JMPJ+GslWYHb4phowim57iaztXOoJwTdwJx4nLCgdNbOhdjsnvzqvHu7Ur\nTkXWStAmzOVyyghqpZXjFaH3pO3JLF+l+/+sKAIuvtd7u+Nxe5AW0wdeRlN8NwdC\njNPElpzVmbUq4JUagEiuTDkHzsxHpFKVK7q4+63SM1N95R1NbdWhscdCb+ZAJzVc\noyi3B43njTOQ5yOf+1CceWxG1bQVs5ZufpsMljq4Ui0/1lvh+wjChP4kqKOJ2qxq\n4RgqsahDYVvTH9w7jXbyLeiNdd8XM2w9U/t7y0Ff/9yi0GE44Za4rF2LN9d11TPA\nmRGunUHBcnWEvgJBQl9nJEiU0Zsnvgc/ubhPgXRR4Xq37Z0j4r7g1SgEEzwxA57d\nemyPxgcYxn/eR44/KJ4EBs+lVDR3veyJm+kXQ99b21/+jh5Xos1AnX5iItreGCc=\n-----END CERTIFICATE-----\n)EOF";\n'+statements_uart +statements_wifi +statements_line +statements_mqtt ;</v>
       </c>
       <c r="G1" s="43"/>
       <c r="H1" t="s">
@@ -27247,7 +25722,7 @@
       </c>
       <c r="I1" s="7" t="str">
         <f>"Blockly.Arduino.definitions_['"&amp;變數!A2&amp;"'] = "&amp;'01D'!I3&amp;I5&amp;I7&amp;";"</f>
-        <v>Blockly.Arduino.definitions_['01imi_esp32car_init'] = ;</v>
+        <v>Blockly.Arduino.definitions_['_01imi_esp32car_init'] = ;</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -27263,7 +25738,7 @@
       </c>
       <c r="D2" s="5" t="str">
         <f>變數!$A$2</f>
-        <v>01imi_esp32car_init</v>
+        <v>_01imi_esp32car_init</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
@@ -27299,11 +25774,11 @@
         <v>#include &lt;PubSubClient.h&gt;\n</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="D4" s="5" t="str">
         <f>變數!$C$2</f>
-        <v xml:space="preserve">value_uart </v>
+        <v xml:space="preserve">statements_uart </v>
       </c>
       <c r="H4" s="16"/>
       <c r="I4" s="19"/>
@@ -27317,11 +25792,11 @@
         <v>#include &lt;WiFiClientSecure.h&gt;\n</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="D5" s="5" t="str">
         <f>變數!$C$3</f>
-        <v xml:space="preserve">value_wifi </v>
+        <v xml:space="preserve">statements_wifi </v>
       </c>
       <c r="I5" s="6"/>
     </row>
@@ -27332,28 +25807,28 @@
         <v/>
       </c>
       <c r="C6" s="4" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="D6" s="5" t="str">
         <f>變數!$C$4</f>
-        <v xml:space="preserve">value_line </v>
+        <v xml:space="preserve">statements_line </v>
       </c>
       <c r="H6" s="16"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="23" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B7" s="26" t="str">
         <f t="shared" si="0"/>
         <v>//與Mega通訊\n</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D7" s="5" t="str">
         <f>變數!$C$5</f>
-        <v xml:space="preserve">value_mqtt </v>
+        <v xml:space="preserve">statements_mqtt </v>
       </c>
       <c r="I7" s="6"/>
     </row>
@@ -27406,7 +25881,7 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="23" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B13" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27429,7 +25904,7 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="23" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B16" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27481,7 +25956,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="23" t="s">
-        <v>34</v>
+        <v>233</v>
       </c>
       <c r="B22" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27490,7 +25965,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B23" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27506,7 +25981,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B25" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27515,7 +25990,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B26" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27524,7 +25999,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B27" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27533,7 +26008,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B28" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27549,7 +26024,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B30" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27558,7 +26033,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B31" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27574,7 +26049,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="23" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B33" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27583,7 +26058,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B34" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27592,7 +26067,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B35" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27601,7 +26076,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B36" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27610,7 +26085,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B37" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27619,7 +26094,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B38" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27628,7 +26103,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27637,7 +26112,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B40" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27646,7 +26121,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B41" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27655,7 +26130,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B42" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27664,7 +26139,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B43" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27673,7 +26148,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B44" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27682,7 +26157,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B45" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27691,7 +26166,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="23" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B46" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27700,7 +26175,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B47" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27709,7 +26184,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B48" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27718,7 +26193,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="23" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B49" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27727,7 +26202,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B50" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27736,7 +26211,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B51" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27745,7 +26220,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B52" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27754,7 +26229,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B53" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27763,7 +26238,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B54" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27772,7 +26247,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B55" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27781,7 +26256,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="23" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B56" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27790,7 +26265,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="23" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B57" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27799,7 +26274,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="23" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B58" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27808,7 +26283,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B59" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27817,7 +26292,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B60" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27826,7 +26301,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B61" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27835,7 +26310,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B62" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27844,7 +26319,7 @@
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B63" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27853,7 +26328,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B64" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27862,7 +26337,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B65" s="26" t="str">
         <f t="shared" si="0"/>
@@ -27871,7 +26346,7 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B66" s="26" t="str">
         <f t="shared" si="0"/>
@@ -28037,6 +26512,1523 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:F88"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="38.25" customWidth="1"/>
+    <col min="2" max="2" width="21.625" customWidth="1"/>
+    <col min="3" max="3" width="11.375" customWidth="1"/>
+    <col min="5" max="5" width="32.875" customWidth="1"/>
+    <col min="6" max="6" width="26.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="8" t="str">
+        <f>"Blockly.Arduino.setups_['"&amp;D2&amp;"'] = '"&amp;D3&amp;"';"</f>
+        <v>Blockly.Arduino.setups_['_01imi_esp32car_init'] = '  delay(500);\n  Serial.begin(9600);\n  delay(500);\n  MegaSerial.begin(9600);\n  delay(500);\n  setup_wifi();\n  //MQTT初始\n  espClient.setCACert(root_ca);\n  client.setServer(mqtt_server, mqtt_port);\n  client.setCallback(callback);\n  if (!client.connected()) {\n    reconnect();\n  }\n';</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="7" t="str">
+        <f>"Blockly.Arduino.setups_['"&amp;
+變數!$A$2 &amp;"' + "&amp;
+變數!B2 &amp;" + "&amp;
+變數!B3 &amp;
+"] = "&amp;
+'01S'!F3 &amp; '01S'!F5
+&amp;";"</f>
+        <v>Blockly.Arduino.setups_['_01imi_esp32car_init' + value_rx + value_tx] = ++++++++++++++;</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" s="27" t="str">
+        <f>IF(NOT(ISBLANK(A2)),A2&amp;"\n","")</f>
+        <v xml:space="preserve">  delay(500);\n</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="5" t="str">
+        <f>變數!$A$2</f>
+        <v>_01imi_esp32car_init</v>
+      </c>
+      <c r="E2" s="14"/>
+      <c r="F2" s="11"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" s="27" t="str">
+        <f t="shared" ref="B3:B66" si="0">IF(NOT(ISBLANK(A3)),A3&amp;"\n","")</f>
+        <v xml:space="preserve">  Serial.begin(9600);\n</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D3" s="5" t="str">
+        <f>B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88</f>
+        <v xml:space="preserve">  delay(500);\n  Serial.begin(9600);\n  delay(500);\n  MegaSerial.begin(9600);\n  delay(500);\n  setup_wifi();\n  //MQTT初始\n  espClient.setCACert(root_ca);\n  client.setServer(mqtt_server, mqtt_port);\n  client.setCallback(callback);\n  if (!client.connected()) {\n    reconnect();\n  }\n</v>
+      </c>
+      <c r="E3" s="9"/>
+      <c r="F3" s="12" t="str">
+        <f>F2&amp;"+"&amp;G2&amp;"+"&amp;H2&amp;"+"&amp;I2&amp;"+"&amp;J2&amp;"+"&amp;K2&amp;"+"&amp;L2&amp;"+"&amp;M2</f>
+        <v>+++++++</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="B4" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  delay(500);\n</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="13"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="B5" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  MegaSerial.begin(9600);\n</v>
+      </c>
+      <c r="E5" s="9"/>
+      <c r="F5" s="12" t="str">
+        <f>F4&amp;"+"&amp;G4&amp;"+"&amp;H4&amp;"+"&amp;I4&amp;"+"&amp;J4&amp;"+"&amp;K4&amp;"+"&amp;L4&amp;"+"&amp;M4</f>
+        <v>+++++++</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="B6" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  delay(500);\n</v>
+      </c>
+      <c r="E6" s="10"/>
+      <c r="F6" s="9"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  setup_wifi();\n</v>
+      </c>
+      <c r="E7" s="9"/>
+      <c r="F7" s="12" t="str">
+        <f>F6&amp;"+"&amp;G6&amp;"+"&amp;H6&amp;"+"&amp;I6&amp;"+"&amp;J6&amp;"+"&amp;K6&amp;"+"&amp;L6&amp;"+"&amp;M6</f>
+        <v>+++++++</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="24"/>
+      <c r="B8" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E8" s="10"/>
+      <c r="F8" s="9"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="B9" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  //MQTT初始\n</v>
+      </c>
+      <c r="E9" s="9"/>
+      <c r="F9" s="12" t="str">
+        <f>F8&amp;"+"&amp;G8&amp;"+"&amp;H8&amp;"+"&amp;I8&amp;"+"&amp;J8&amp;"+"&amp;K8&amp;"+"&amp;L8&amp;"+"&amp;M8</f>
+        <v>+++++++</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="B10" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  espClient.setCACert(root_ca);\n</v>
+      </c>
+      <c r="E10" s="10"/>
+      <c r="F10" s="9"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="B11" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  client.setServer(mqtt_server, mqtt_port);\n</v>
+      </c>
+      <c r="E11" s="9"/>
+      <c r="F11" s="12" t="str">
+        <f>F10&amp;"+"&amp;G10&amp;"+"&amp;H10&amp;"+"&amp;I10&amp;"+"&amp;J10&amp;"+"&amp;K10&amp;"+"&amp;L10&amp;"+"&amp;M10</f>
+        <v>+++++++</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="B12" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  client.setCallback(callback);\n</v>
+      </c>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="B13" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  if (!client.connected()) {\n</v>
+      </c>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="B14" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    reconnect();\n</v>
+      </c>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  }\n</v>
+      </c>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3"/>
+      <c r="B16" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="3"/>
+      <c r="B17" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="3"/>
+      <c r="B18" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="3"/>
+      <c r="B19" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="3"/>
+      <c r="B20" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="3"/>
+      <c r="B21" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="3"/>
+      <c r="B22" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E22" s="9"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="3"/>
+      <c r="B23" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="3"/>
+      <c r="B24" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="3"/>
+      <c r="B25" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="3"/>
+      <c r="B26" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="3"/>
+      <c r="B27" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="3"/>
+      <c r="B28" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="3"/>
+      <c r="B29" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="3"/>
+      <c r="B30" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="3"/>
+      <c r="B31" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="3"/>
+      <c r="B32" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="3"/>
+      <c r="B33" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="3"/>
+      <c r="B34" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="3"/>
+      <c r="B35" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="3"/>
+      <c r="B36" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="3"/>
+      <c r="B37" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="3"/>
+      <c r="B38" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="3"/>
+      <c r="B39" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="3"/>
+      <c r="B40" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="3"/>
+      <c r="B41" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="3"/>
+      <c r="B42" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="3"/>
+      <c r="B43" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="3"/>
+      <c r="B44" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="3"/>
+      <c r="B45" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="3"/>
+      <c r="B46" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="3"/>
+      <c r="B47" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="3"/>
+      <c r="B48" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="3"/>
+      <c r="B49" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="3"/>
+      <c r="B50" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="3"/>
+      <c r="B51" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="3"/>
+      <c r="B52" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="3"/>
+      <c r="B53" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="3"/>
+      <c r="B54" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="3"/>
+      <c r="B55" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="3"/>
+      <c r="B56" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="3"/>
+      <c r="B57" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="3"/>
+      <c r="B58" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="3"/>
+      <c r="B59" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="3"/>
+      <c r="B60" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="3"/>
+      <c r="B61" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="3"/>
+      <c r="B62" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="3"/>
+      <c r="B63" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="3"/>
+      <c r="B64" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="3"/>
+      <c r="B65" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="3"/>
+      <c r="B66" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="3"/>
+      <c r="B67" s="27" t="str">
+        <f t="shared" ref="B67:B88" si="1">IF(NOT(ISBLANK(A67)),A67&amp;"\n","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="3"/>
+      <c r="B68" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="3"/>
+      <c r="B69" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="3"/>
+      <c r="B70" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="3"/>
+      <c r="B71" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="3"/>
+      <c r="B72" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="3"/>
+      <c r="B73" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="3"/>
+      <c r="B74" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="3"/>
+      <c r="B75" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="3"/>
+      <c r="B76" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="3"/>
+      <c r="B77" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="3"/>
+      <c r="B78" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="3"/>
+      <c r="B79" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="3"/>
+      <c r="B80" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="3"/>
+      <c r="B81" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="3"/>
+      <c r="B82" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="3"/>
+      <c r="B83" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="3"/>
+      <c r="B84" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="3"/>
+      <c r="B85" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="3"/>
+      <c r="B86" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" s="3"/>
+      <c r="B87" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" s="3"/>
+      <c r="B88" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:E88"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="64.25" customWidth="1"/>
+    <col min="2" max="2" width="23.75" customWidth="1"/>
+    <col min="4" max="4" width="16.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="8" t="str">
+        <f>"Blockly.Arduino.functions_['"&amp;D2&amp;"'] = '"&amp;D3&amp;"';"</f>
+        <v>Blockly.Arduino.functions_['_01imi_esp32car_init'] = 'void reconnect() {\n  while (!client.connected()) {\n    Serial.print("Attempting MQTT connection… ");\n    String clientId = "ESP32Client";\n    if (client.connect(clientId.c_str(), mqtt_username, mqtt_password)) {\n      Serial.println("connected!");\n    } else {\n      Serial.print("failed, rc = ");\n      Serial.print(client.state());\n      Serial.println(" try again in 5 seconds");\n      delay(5000);\n    }\n  }\n}\nvoid sendLineMsg(String myMsg) {\n  static WiFiClientSecure line_client;\n  line_client.setInsecure();\n  myMsg.replace("%", "%25");\n  myMsg.replace("&amp;", "%26");\n  myMsg.replace("§", "&amp;");\n  myMsg.replace("\\\\n", "\\n");\n  if (line_client.connect("notify-api.line.me", 443)) {\n    line_client.println("POST /api/notify HTTP/1.1");\n    line_client.println("Connection: close");\n    line_client.println("Host: notify-api.line.me");\n    line_client.println("Authorization: Bearer " + lineToken);\n    line_client.println("Content-Type: application/x-www-form-urlencoded");\n    line_client.println("Content-Length: " + String(myMsg.length()));\n    line_client.println();\n    line_client.println(myMsg);\n    line_client.println();\n    line_client.stop();\n  } else {\n    Serial.println("Line Notify failed");\n  }\n}\nvoid setup_wifi() {\n  delay(10);\n  Serial.println();\n  Serial.print("Connecting to ");\n  Serial.println(ssid);\n  WiFi.mode(WIFI_STA);\n  WiFi.begin(ssid, password);\n  while (WiFi.status() != WL_CONNECTED) {\n    delay(500);\n    Serial.print(".");\n  }\n  Serial.println("");\n  Serial.println("WiFi connected");\n  Serial.println("IP address: ");\n  Serial.println(WiFi.localIP());\n}\n//傳送訊息：ESP32→Mega\nvoid UartSentToMega(String msg) {\n  MegaSerial.print(msg);\n}\n';</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" s="27" t="str">
+        <f>IF(NOT(ISBLANK(A2)),A2&amp;"\n","")</f>
+        <v>void reconnect() {\n</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="5" t="str">
+        <f>變數!$A$2</f>
+        <v>_01imi_esp32car_init</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="27" t="str">
+        <f t="shared" ref="B3:B66" si="0">IF(NOT(ISBLANK(A3)),A3&amp;"\n","")</f>
+        <v xml:space="preserve">  while (!client.connected()) {\n</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D3" s="5" t="str">
+        <f>B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88</f>
+        <v>void reconnect() {\n  while (!client.connected()) {\n    Serial.print("Attempting MQTT connection… ");\n    String clientId = "ESP32Client";\n    if (client.connect(clientId.c_str(), mqtt_username, mqtt_password)) {\n      Serial.println("connected!");\n    } else {\n      Serial.print("failed, rc = ");\n      Serial.print(client.state());\n      Serial.println(" try again in 5 seconds");\n      delay(5000);\n    }\n  }\n}\nvoid sendLineMsg(String myMsg) {\n  static WiFiClientSecure line_client;\n  line_client.setInsecure();\n  myMsg.replace("%", "%25");\n  myMsg.replace("&amp;", "%26");\n  myMsg.replace("§", "&amp;");\n  myMsg.replace("\\\\n", "\\n");\n  if (line_client.connect("notify-api.line.me", 443)) {\n    line_client.println("POST /api/notify HTTP/1.1");\n    line_client.println("Connection: close");\n    line_client.println("Host: notify-api.line.me");\n    line_client.println("Authorization: Bearer " + lineToken);\n    line_client.println("Content-Type: application/x-www-form-urlencoded");\n    line_client.println("Content-Length: " + String(myMsg.length()));\n    line_client.println();\n    line_client.println(myMsg);\n    line_client.println();\n    line_client.stop();\n  } else {\n    Serial.println("Line Notify failed");\n  }\n}\nvoid setup_wifi() {\n  delay(10);\n  Serial.println();\n  Serial.print("Connecting to ");\n  Serial.println(ssid);\n  WiFi.mode(WIFI_STA);\n  WiFi.begin(ssid, password);\n  while (WiFi.status() != WL_CONNECTED) {\n    delay(500);\n    Serial.print(".");\n  }\n  Serial.println("");\n  Serial.println("WiFi connected");\n  Serial.println("IP address: ");\n  Serial.println(WiFi.localIP());\n}\n//傳送訊息：ESP32→Mega\nvoid UartSentToMega(String msg) {\n  MegaSerial.print(msg);\n}\n</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    Serial.print("Attempting MQTT connection… ");\n</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    String clientId = "ESP32Client";\n</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    if (client.connect(clientId.c_str(), mqtt_username, mqtt_password)) {\n</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      Serial.println("connected!");\n</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    } else {\n</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      Serial.print("failed, rc = ");\n</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      Serial.print(client.state());\n</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      Serial.println(" try again in 5 seconds");\n</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">      delay(5000);\n</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    }\n</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  }\n</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v>}\n</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="24"/>
+      <c r="B16" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v>void sendLineMsg(String myMsg) {\n</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  static WiFiClientSecure line_client;\n</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="B19" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  line_client.setInsecure();\n</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  myMsg.replace("%", "%25");\n</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="B21" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  myMsg.replace("&amp;", "%26");\n</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="B22" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  myMsg.replace("§", "&amp;");\n</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="23" t="s">
+        <v>232</v>
+      </c>
+      <c r="B23" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  myMsg.replace("\\\\n", "\\n");\n</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  if (line_client.connect("notify-api.line.me", 443)) {\n</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    line_client.println("POST /api/notify HTTP/1.1");\n</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    line_client.println("Connection: close");\n</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="B27" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    line_client.println("Host: notify-api.line.me");\n</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="B28" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    line_client.println("Authorization: Bearer " + lineToken);\n</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="B29" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    line_client.println("Content-Type: application/x-www-form-urlencoded");\n</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="B30" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    line_client.println("Content-Length: " + String(myMsg.length()));\n</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="B31" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    line_client.println();\n</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="B32" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    line_client.println(myMsg);\n</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="B33" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    line_client.println();\n</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="B34" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    line_client.stop();\n</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B35" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  } else {\n</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="B36" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    Serial.println("Line Notify failed");\n</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  }\n</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v>}\n</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="3"/>
+      <c r="B39" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="B40" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v>void setup_wifi() {\n</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="B41" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  delay(10);\n</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="B42" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  Serial.println();\n</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="B43" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  Serial.print("Connecting to ");\n</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="B44" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  Serial.println(ssid);\n</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="23"/>
+      <c r="B45" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="B46" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  WiFi.mode(WIFI_STA);\n</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="B47" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  WiFi.begin(ssid, password);\n</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="23"/>
+      <c r="B48" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="B49" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  while (WiFi.status() != WL_CONNECTED) {\n</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="B50" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    delay(500);\n</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="B51" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    Serial.print(".");\n</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B52" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  }\n</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="23"/>
+      <c r="B53" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="B54" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  Serial.println("");\n</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="B55" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  Serial.println("WiFi connected");\n</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="B56" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  Serial.println("IP address: ");\n</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="B57" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  Serial.println(WiFi.localIP());\n</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B58" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v>}\n</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="3"/>
+      <c r="B59" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="B60" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v>//傳送訊息：ESP32→Mega\n</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="B61" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v>void UartSentToMega(String msg) {\n</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="B62" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">  MegaSerial.print(msg);\n</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B63" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v>}\n</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="3"/>
+      <c r="B64" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="3"/>
+      <c r="B65" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="3"/>
+      <c r="B66" s="27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="3"/>
+      <c r="B67" s="27" t="str">
+        <f t="shared" ref="B67:B88" si="1">IF(NOT(ISBLANK(A67)),A67&amp;"\n","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="3"/>
+      <c r="B68" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="3"/>
+      <c r="B69" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="3"/>
+      <c r="B70" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="3"/>
+      <c r="B71" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="3"/>
+      <c r="B72" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="3"/>
+      <c r="B73" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="3"/>
+      <c r="B74" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="3"/>
+      <c r="B75" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="3"/>
+      <c r="B76" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="3"/>
+      <c r="B77" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="3"/>
+      <c r="B78" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="3"/>
+      <c r="B79" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="3"/>
+      <c r="B80" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="3"/>
+      <c r="B81" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="3"/>
+      <c r="B82" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="3"/>
+      <c r="B83" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="3"/>
+      <c r="B84" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="3"/>
+      <c r="B85" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="3"/>
+      <c r="B86" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" s="3"/>
+      <c r="B87" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" s="3"/>
+      <c r="B88" s="27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -28057,33 +28049,33 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B1" s="41" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C1" s="7" t="str">
         <f>"var code ="&amp;B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88&amp;";"</f>
         <v>var code =;</v>
       </c>
       <c r="D1" s="38" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1" s="41" t="s">
         <v>168</v>
-      </c>
-      <c r="F1" s="41" t="s">
-        <v>170</v>
       </c>
       <c r="G1" s="7" t="str">
         <f>"var code ='"&amp;F2&amp;F3&amp;F4&amp;F5&amp;F6&amp;F7&amp;F8&amp;F9&amp;F10&amp;F11&amp;F12&amp;F13&amp;F14&amp;F15&amp;F16&amp;F17&amp;F18&amp;F19&amp;F20&amp;F21&amp;F22&amp;F23&amp;F24&amp;F25&amp;F26&amp;F27&amp;F28&amp;F29&amp;F30&amp;F31&amp;F32&amp;F33&amp;F34&amp;F35&amp;F36&amp;F37&amp;F38&amp;F39&amp;F40&amp;F41&amp;F42&amp;F43&amp;F44&amp;F45&amp;F46&amp;F47&amp;F48&amp;F49&amp;F50&amp;F51&amp;F52&amp;F53&amp;F54&amp;F55&amp;F56&amp;F57&amp;F58&amp;F59&amp;F60&amp;F61&amp;F62&amp;F63&amp;F64&amp;F65&amp;F66&amp;F67&amp;F68&amp;F69&amp;F70&amp;F71&amp;F72&amp;F73&amp;F74&amp;F75&amp;F76&amp;F77&amp;F78&amp;F79&amp;F80&amp;F81&amp;F82&amp;F83&amp;F84&amp;F85&amp;F86&amp;F87&amp;F88&amp;"';"</f>
         <v>var code ='';</v>
       </c>
       <c r="I1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J1" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="K1" s="7" t="str">
         <f>"var code ="&amp;J2&amp;J3&amp;";"</f>
@@ -28103,7 +28095,7 @@
         <v/>
       </c>
       <c r="I2" s="14" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J2" s="27" t="str">
         <f>IF(NOT(ISBLANK(I2)),I2&amp;"+'\n '+","")</f>
@@ -28123,7 +28115,7 @@
         <v/>
       </c>
       <c r="I3" s="14" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J3" s="27" t="str">
         <f t="shared" ref="J3:J66" si="2">IF(NOT(ISBLANK(I3)),I3&amp;"+'\n '+","")</f>
@@ -28183,7 +28175,7 @@
         <v/>
       </c>
       <c r="I6" s="14" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="J6" s="27" t="str">
         <f t="shared" si="2"/>
@@ -28203,7 +28195,7 @@
         <v/>
       </c>
       <c r="I7" s="14" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="J7" s="27" t="str">
         <f t="shared" si="2"/>
@@ -28223,7 +28215,7 @@
         <v/>
       </c>
       <c r="I8" s="14" t="s">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="J8" s="27" t="str">
         <f t="shared" si="2"/>
@@ -28265,7 +28257,7 @@
         <v/>
       </c>
       <c r="I10" s="14" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="J10" s="27" t="str">
         <f t="shared" si="2"/>
@@ -28285,7 +28277,7 @@
         <v/>
       </c>
       <c r="I11" s="14" t="s">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="J11" s="27" t="str">
         <f t="shared" si="2"/>
@@ -28327,7 +28319,7 @@
         <v/>
       </c>
       <c r="I13" s="14" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J13" s="27" t="str">
         <f t="shared" si="2"/>
@@ -28347,7 +28339,7 @@
         <v/>
       </c>
       <c r="I14" s="14" t="s">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="J14" s="27" t="str">
         <f t="shared" si="2"/>
@@ -28366,7 +28358,7 @@
         <v/>
       </c>
       <c r="I15" s="14" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="J15" s="27" t="str">
         <f t="shared" si="2"/>
@@ -28385,7 +28377,7 @@
         <v/>
       </c>
       <c r="I16" s="14" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="J16" s="27" t="str">
         <f t="shared" si="2"/>
@@ -28404,7 +28396,7 @@
         <v/>
       </c>
       <c r="I17" s="14" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="J17" s="27" t="str">
         <f t="shared" si="2"/>
@@ -28517,7 +28509,7 @@
         <v/>
       </c>
       <c r="L23" s="45" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -29646,7 +29638,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C1" s="7" t="str">
         <f>"var code ='"&amp;B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88&amp;"';"</f>
@@ -29662,7 +29654,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="23" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B2" s="27" t="str">
         <f>IF(NOT(ISBLANK(A2)),A2&amp;"\n","")</f>
@@ -29673,7 +29665,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="23" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B3" s="27" t="str">
         <f t="shared" ref="B3:B66" si="0">IF(NOT(ISBLANK(A3)),A3&amp;"\n","")</f>
@@ -29693,7 +29685,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="24" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B5" s="27" t="str">
         <f t="shared" si="0"/>
@@ -29704,7 +29696,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="23" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B6" s="27" t="str">
         <f t="shared" si="0"/>
@@ -30328,39 +30320,39 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="E1" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G1" t="s">
         <v>10</v>
       </c>
       <c r="H1" s="8" t="str">
         <f>"Blockly.Arduino.functions_['"&amp;H2&amp;"'] = '"&amp;H3&amp;"' + "&amp;H4&amp;" + '"&amp;H5&amp;"';"</f>
-        <v>Blockly.Arduino.functions_['07imi_esp32car_getArduino_func'] = '//接收訊息：Mega→ESP32\n void UartGetFromMega() {  \n   while (MegaSerial.available()) {\n     String str = MegaSerial.readString();\n     Serial.println(str);\n ' + statements_msg + '}//while\n }\n ';</v>
+        <v>Blockly.Arduino.functions_['_07imi_esp32car_getArduino_func'] = '//接收訊息：Mega→ESP32\n void UartGetFromMega() {  \n   while (MegaSerial.available()) {\n     String str = MegaSerial.readString();\n     Serial.println(str);\n ' + statements_msg + '}//while\n }\n ';</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="23" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B2" s="27" t="str">
         <f>IF(NOT(ISBLANK(A2)),A2&amp;"\n ","")</f>
         <v xml:space="preserve">//接收訊息：Mega→ESP32\n </v>
       </c>
       <c r="C2" s="30" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D2" s="27" t="str">
         <f>IF(NOT(ISBLANK(C2)),C2,"")</f>
         <v>statements_msg</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F2" s="27" t="str">
         <f>IF(NOT(ISBLANK(E2)),E2&amp;"\n ","")</f>
@@ -30371,12 +30363,12 @@
       </c>
       <c r="H2" s="5" t="str">
         <f>變數!$A$4</f>
-        <v>07imi_esp32car_getArduino_func</v>
+        <v>_07imi_esp32car_getArduino_func</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="23" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B3" s="27" t="str">
         <f t="shared" ref="B3:B66" si="0">IF(NOT(ISBLANK(A3)),A3&amp;"\n ","")</f>
@@ -30395,7 +30387,7 @@
         <v xml:space="preserve">}\n </v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H3" s="5" t="str">
         <f>B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88</f>
@@ -30408,7 +30400,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="23" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B4" s="27" t="str">
         <f t="shared" si="0"/>
@@ -30425,7 +30417,7 @@
         <v/>
       </c>
       <c r="G4" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H4" s="4" t="str">
         <f>D2</f>
@@ -30434,7 +30426,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="23" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B5" s="27" t="str">
         <f t="shared" si="0"/>
@@ -30451,7 +30443,7 @@
         <v/>
       </c>
       <c r="G5" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H5" s="4" t="str">
         <f>F2&amp;F3&amp;F4&amp;F5&amp;F6&amp;F7&amp;F8&amp;F9&amp;F10&amp;F11&amp;F12&amp;F13&amp;F14&amp;F15&amp;F16&amp;F17&amp;F18&amp;F19&amp;F20&amp;F21&amp;F22&amp;F23&amp;F24&amp;F25&amp;F26&amp;F27&amp;F28&amp;F29&amp;F30&amp;F31&amp;F32&amp;F33&amp;F34&amp;F35&amp;F36&amp;F37&amp;F38&amp;F39&amp;F40&amp;F41&amp;F42&amp;F43&amp;F44&amp;F45&amp;F46&amp;F47&amp;F48&amp;F49&amp;F50&amp;F51&amp;F52&amp;F53&amp;F54&amp;F55&amp;F56&amp;F57&amp;F58&amp;F59&amp;F60&amp;F61&amp;F62&amp;F63&amp;F64&amp;F65&amp;F66&amp;F67&amp;F68&amp;F69&amp;F70&amp;F71&amp;F72&amp;F73&amp;F74&amp;F75&amp;F76&amp;F77&amp;F78&amp;F79&amp;F80&amp;F81&amp;F82&amp;F83&amp;F84&amp;F85&amp;F86&amp;F87&amp;F88</f>
@@ -30460,7 +30452,7 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="23" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B6" s="27" t="str">
         <f t="shared" si="0"/>
